--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/05-custo-hora.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/05-custo-hora.xlsx
@@ -889,7 +889,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Copie "Como chegamos ao número" e peça à IA para explicar o custo-hora ao sócio em linguagem simples, ou para sugerir o que fazer se a ocupação estiver abaixo de 50%.</t>
+          <t>Copie "Como chegamos ao número" e use o prompt "Honorários 01 · Entender o meu custo-hora" da biblioteca do kit para explicar o custo-hora ao sócio em linguagem simples, ou para sugerir o que fazer se a ocupação estiver abaixo de 50%.</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Excel 2019 ou mais novo, Microsoft 365 ou Google Sheets. No celular abre nos aplicativos; para preencher, use o computador.</t>
+          <t>Excel 2016 ou mais novo, Microsoft 365 ou Google Sheets (só funções do Excel 2007+; nada de MÍNIMOSES, MÁXIMOSES ou UNIRTEXTO). No celular abre nos aplicativos; para preencher, use o computador.</t>
         </is>
       </c>
     </row>
@@ -993,9 +993,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5">
+      <c r="A1" s="5" t="str">
         <f>Config!$B$4&amp;" · Custo-hora · "&amp;Config!$B$5</f>
-        <v/>
+        <v>Ferraz &amp; Lima Advocacia (exemplo fictício) · Custo-hora · Setembro de 2026</v>
       </c>
     </row>
     <row r="2">
@@ -1032,7 +1032,7 @@
       <c r="H4" s="12" t="n"/>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>Ocupação da equipe</t>
+          <t>Tempo faturável (planejado)</t>
         </is>
       </c>
       <c r="J4" s="8" t="n"/>
@@ -1040,27 +1040,27 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="13">
         <f>B11</f>
-        <v/>
+        <v>18500</v>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="14">
         <f>B12</f>
-        <v/>
+        <v>280</v>
       </c>
       <c r="D5" s="8" t="n"/>
       <c r="E5" s="15">
         <f>B13</f>
-        <v/>
+        <v>66.0714285714286</v>
       </c>
       <c r="F5" s="10" t="n"/>
       <c r="G5" s="16">
         <f>B17</f>
-        <v/>
+        <v>110</v>
       </c>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="17">
         <f>B21</f>
-        <v/>
+        <v>0.636363636363636</v>
       </c>
       <c r="J5" s="8" t="n"/>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="B9" s="21">
         <f>'Custos fixos'!B36</f>
-        <v/>
+        <v>6500</v>
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="B10" s="21">
         <f>SUMIFS(Pessoas!$C$5:$C$14,Pessoas!$D$5:$D$14,"Não")</f>
-        <v/>
+        <v>12000</v>
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B11" s="25">
         <f>B9+B10</f>
-        <v/>
+        <v>18500</v>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B12" s="26">
         <f>SUM(Pessoas!$F$5:$F$14)</f>
-        <v/>
+        <v>280</v>
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="B13" s="25">
         <f>IF(B12=0,"",B11/B12)</f>
-        <v/>
+        <v>66.0714285714286</v>
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B14" s="27">
         <f>Config!$B$7</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="C14" s="22" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B15" s="27">
         <f>Config!$B$8</f>
-        <v/>
+        <v>0.08</v>
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="B16" s="21">
         <f>IF(B13="","",IFERROR(B13/(1-Config!$B$7-Config!$B$8),""))</f>
-        <v/>
+        <v>106.566820276498</v>
       </c>
       <c r="C16" s="22" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B17" s="25">
         <f>IF(B16="","",CEILING(B16,Config!$B$9))</f>
-        <v/>
+        <v>110</v>
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="B18" s="21">
         <f>B9-SUMIFS(Pessoas!$C$5:$C$14,Pessoas!$D$5:$D$14,"Sim")</f>
-        <v/>
+        <v>5100</v>
       </c>
       <c r="C18" s="22" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B19" s="21">
         <f>IF(B12=0,0,B18/B12)</f>
-        <v/>
+        <v>18.2142857142857</v>
       </c>
       <c r="C19" s="22" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="B20" s="26">
         <f>SUM(Pessoas!$E$5:$E$14)</f>
-        <v/>
+        <v>440</v>
       </c>
       <c r="C20" s="22" t="inlineStr">
         <is>
@@ -1307,16 +1307,16 @@
     <row r="21">
       <c r="A21" s="20" t="inlineStr">
         <is>
-          <t>Ocupação da equipe (faturáveis ÷ trabalho)</t>
+          <t>Tempo faturável planejado (horas faturáveis ÷ horas de trabalho)</t>
         </is>
       </c>
       <c r="B21" s="27">
         <f>IF(B20=0,"",B12/B20)</f>
-        <v/>
+        <v>0.636363636363636</v>
       </c>
       <c r="C21" s="22" t="inlineStr">
         <is>
-          <t>Quanto do tempo pago vira hora cobrável</t>
+          <t>Quanto do tempo pago vira hora cobrável (a planilha 16 mede o realizado contra a meta)</t>
         </is>
       </c>
       <c r="D21" s="23" t="n"/>
@@ -1367,93 +1367,93 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20">
+      <c r="A26" s="20" t="str">
         <f>IF(Pessoas!$A$5="","",Pessoas!$A$5)</f>
-        <v/>
-      </c>
-      <c r="B26" s="20">
+        <v>Marina Ferraz</v>
+      </c>
+      <c r="B26" s="20" t="str">
         <f>IF(Pessoas!$A$5="","",Pessoas!$B$5)</f>
-        <v/>
+        <v>Sócia · cível e empresarial</v>
       </c>
       <c r="C26" s="26">
         <f>IF(Pessoas!$A$5="","",Pessoas!$F$5)</f>
-        <v/>
+        <v>110</v>
       </c>
       <c r="D26" s="27">
         <f>IF(Pessoas!$A$5="","",Pessoas!$G$5)</f>
-        <v/>
+        <v>0.6875</v>
       </c>
       <c r="E26" s="21">
         <f>IF(Pessoas!$A$5="","",Pessoas!$H$5)</f>
-        <v/>
+        <v>54.5454545454546</v>
       </c>
       <c r="F26" s="21">
         <f>IF(Pessoas!$A$5="","",Pessoas!$I$5)</f>
-        <v/>
+        <v>72.7597402597403</v>
       </c>
       <c r="G26" s="21">
         <f>IF(Pessoas!$A$5="","",Pessoas!$J$5)</f>
-        <v/>
+        <v>117.354419773775</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20">
+      <c r="A27" s="20" t="str">
         <f>IF(Pessoas!$A$6="","",Pessoas!$A$6)</f>
-        <v/>
-      </c>
-      <c r="B27" s="20">
+        <v>Rafael Lima</v>
+      </c>
+      <c r="B27" s="20" t="str">
         <f>IF(Pessoas!$A$6="","",Pessoas!$B$6)</f>
-        <v/>
+        <v>Sócio · trabalhista e previdenciário</v>
       </c>
       <c r="C27" s="26">
         <f>IF(Pessoas!$A$6="","",Pessoas!$F$6)</f>
-        <v/>
+        <v>110</v>
       </c>
       <c r="D27" s="27">
         <f>IF(Pessoas!$A$6="","",Pessoas!$G$6)</f>
-        <v/>
+        <v>0.6875</v>
       </c>
       <c r="E27" s="21">
         <f>IF(Pessoas!$A$6="","",Pessoas!$H$6)</f>
-        <v/>
+        <v>54.5454545454546</v>
       </c>
       <c r="F27" s="21">
         <f>IF(Pessoas!$A$6="","",Pessoas!$I$6)</f>
-        <v/>
+        <v>72.7597402597403</v>
       </c>
       <c r="G27" s="21">
         <f>IF(Pessoas!$A$6="","",Pessoas!$J$6)</f>
-        <v/>
+        <v>117.354419773775</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="20">
+      <c r="A28" s="20" t="str">
         <f>IF(Pessoas!$A$7="","",Pessoas!$A$7)</f>
-        <v/>
-      </c>
-      <c r="B28" s="20">
+        <v>Júlia Prado</v>
+      </c>
+      <c r="B28" s="20" t="str">
         <f>IF(Pessoas!$A$7="","",Pessoas!$B$7)</f>
-        <v/>
+        <v>Estagiária</v>
       </c>
       <c r="C28" s="26">
         <f>IF(Pessoas!$A$7="","",Pessoas!$F$7)</f>
-        <v/>
+        <v>60</v>
       </c>
       <c r="D28" s="27">
         <f>IF(Pessoas!$A$7="","",Pessoas!$G$7)</f>
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="E28" s="21">
         <f>IF(Pessoas!$A$7="","",Pessoas!$H$7)</f>
-        <v/>
+        <v>23.3333333333333</v>
       </c>
       <c r="F28" s="21">
         <f>IF(Pessoas!$A$7="","",Pessoas!$I$7)</f>
-        <v/>
+        <v>41.5476190476191</v>
       </c>
       <c r="G28" s="21">
         <f>IF(Pessoas!$A$7="","",Pessoas!$J$7)</f>
-        <v/>
+        <v>67.0122887864823</v>
       </c>
     </row>
     <row r="29">
@@ -1730,94 +1730,94 @@
       </c>
       <c r="C41" s="26">
         <f>$B$12*(1-B41)</f>
-        <v/>
+        <v>280</v>
       </c>
       <c r="D41" s="21">
         <f>IF(C41=0,"",$B$11/C41)</f>
-        <v/>
+        <v>66.0714285714286</v>
       </c>
       <c r="E41" s="21">
         <f>IF(D41="","",IFERROR(D41/(1-Config!$B$7-Config!$B$8),""))</f>
-        <v/>
+        <v>106.566820276498</v>
       </c>
       <c r="F41" s="21">
         <f>IF(D41="","",D41-$D$41)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="20">
+      <c r="A42" s="20" t="str">
         <f>"Queda de "&amp;ROUND(B42*100,0)&amp;"%"</f>
-        <v/>
+        <v>Queda de 10%</v>
       </c>
       <c r="B42" s="29" t="n">
         <v>0.1</v>
       </c>
       <c r="C42" s="26">
         <f>$B$12*(1-B42)</f>
-        <v/>
+        <v>252</v>
       </c>
       <c r="D42" s="21">
         <f>IF(C42=0,"",$B$11/C42)</f>
-        <v/>
+        <v>73.4126984126984</v>
       </c>
       <c r="E42" s="21">
         <f>IF(D42="","",IFERROR(D42/(1-Config!$B$7-Config!$B$8),""))</f>
-        <v/>
+        <v>118.407578084997</v>
       </c>
       <c r="F42" s="21">
         <f>IF(D42="","",D42-$D$41)</f>
-        <v/>
+        <v>7.34126984126985</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="20">
+      <c r="A43" s="20" t="str">
         <f>"Queda de "&amp;ROUND(B43*100,0)&amp;"%"</f>
-        <v/>
+        <v>Queda de 20%</v>
       </c>
       <c r="B43" s="29" t="n">
         <v>0.2</v>
       </c>
       <c r="C43" s="26">
         <f>$B$12*(1-B43)</f>
-        <v/>
+        <v>224</v>
       </c>
       <c r="D43" s="21">
         <f>IF(C43=0,"",$B$11/C43)</f>
-        <v/>
+        <v>82.5892857142857</v>
       </c>
       <c r="E43" s="21">
         <f>IF(D43="","",IFERROR(D43/(1-Config!$B$7-Config!$B$8),""))</f>
-        <v/>
+        <v>133.208525345622</v>
       </c>
       <c r="F43" s="21">
         <f>IF(D43="","",D43-$D$41)</f>
-        <v/>
+        <v>16.5178571428571</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="20">
+      <c r="A44" s="20" t="str">
         <f>"Queda de "&amp;ROUND(B44*100,0)&amp;"%"</f>
-        <v/>
+        <v>Queda de 30%</v>
       </c>
       <c r="B44" s="29" t="n">
         <v>0.3</v>
       </c>
       <c r="C44" s="26">
         <f>$B$12*(1-B44)</f>
-        <v/>
+        <v>196</v>
       </c>
       <c r="D44" s="21">
         <f>IF(C44=0,"",$B$11/C44)</f>
-        <v/>
+        <v>94.3877551020408</v>
       </c>
       <c r="E44" s="21">
         <f>IF(D44="","",IFERROR(D44/(1-Config!$B$7-Config!$B$8),""))</f>
-        <v/>
+        <v>152.238314680711</v>
       </c>
       <c r="F44" s="21">
         <f>IF(D44="","",D44-$D$41)</f>
-        <v/>
+        <v>28.3163265306122</v>
       </c>
     </row>
   </sheetData>
@@ -1865,7 +1865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="B6" s="32">
         <f>TODAY()</f>
-        <v/>
+        <v>46279.0</v>
       </c>
     </row>
     <row r="7">
@@ -1971,6 +1971,13 @@
       <c r="A11" s="28" t="inlineStr">
         <is>
           <t>A hora mínima a cobrar é: custo-hora ÷ (1 − margem − impostos). Assim a margem é calculada sobre o preço, e não sobre o custo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>Esta é a hora mínima do kit (no exemplo: R$ 106,57, arredondada para R$ 110). A planilha 06 usa a mesma conta; a planilha 08 acrescenta uma folga de 20 % para horas não previstas e por isso mostra um valor maior ("hora mínima com folga").</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2246,7 @@
       </c>
       <c r="B36" s="25">
         <f>SUM(B5:B34)</f>
-        <v/>
+        <v>6500</v>
       </c>
     </row>
     <row r="38">
@@ -2373,19 +2380,19 @@
       </c>
       <c r="G5" s="27">
         <f>IF(OR(A5="",E5="",E5=0),"",F5/E5)</f>
-        <v/>
+        <v>0.6875</v>
       </c>
       <c r="H5" s="21">
         <f>IF(OR(A5="",F5="",F5=0),"",C5/F5)</f>
-        <v/>
+        <v>54.5454545454546</v>
       </c>
       <c r="I5" s="21">
         <f>IF(H5="","",H5+Painel!$B$19)</f>
-        <v/>
+        <v>72.7597402597403</v>
       </c>
       <c r="J5" s="21">
         <f>IF(I5="","",IFERROR(I5/(1-Config!$B$7-Config!$B$8),""))</f>
-        <v/>
+        <v>117.354419773775</v>
       </c>
     </row>
     <row r="6">
@@ -2415,19 +2422,19 @@
       </c>
       <c r="G6" s="27">
         <f>IF(OR(A6="",E6="",E6=0),"",F6/E6)</f>
-        <v/>
+        <v>0.6875</v>
       </c>
       <c r="H6" s="21">
         <f>IF(OR(A6="",F6="",F6=0),"",C6/F6)</f>
-        <v/>
+        <v>54.5454545454546</v>
       </c>
       <c r="I6" s="21">
         <f>IF(H6="","",H6+Painel!$B$19)</f>
-        <v/>
+        <v>72.7597402597403</v>
       </c>
       <c r="J6" s="21">
         <f>IF(I6="","",IFERROR(I6/(1-Config!$B$7-Config!$B$8),""))</f>
-        <v/>
+        <v>117.354419773775</v>
       </c>
     </row>
     <row r="7">
@@ -2457,19 +2464,19 @@
       </c>
       <c r="G7" s="27">
         <f>IF(OR(A7="",E7="",E7=0),"",F7/E7)</f>
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="H7" s="21">
         <f>IF(OR(A7="",F7="",F7=0),"",C7/F7)</f>
-        <v/>
+        <v>23.3333333333333</v>
       </c>
       <c r="I7" s="21">
         <f>IF(H7="","",H7+Painel!$B$19)</f>
-        <v/>
+        <v>41.5476190476191</v>
       </c>
       <c r="J7" s="21">
         <f>IF(I7="","",IFERROR(I7/(1-Config!$B$7-Config!$B$8),""))</f>
-        <v/>
+        <v>67.0122887864823</v>
       </c>
     </row>
     <row r="8">

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/05-custo-hora.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/05-custo-hora.xlsx
@@ -865,7 +865,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Em Painel: custo-hora do escritório, hora mínima a cobrar, custo-hora de cada pessoa e a sensibilidade. Use a hora mínima nas planilhas 06 (Simulador) e 08 (Tabela de referência).</t>
+          <t>Em Painel: custo-hora do escritório, hora mínima a cobrar, custo-hora de cada pessoa e a sensibilidade. Leve o CUSTO-HORA do escritório (Painel B13) como entrada das planilhas 06 (Simulador) e 08 (Tabela de referência): é sobre ele que elas aplicam imposto e margem. A hora mínima serve para comparar preço, não como entrada — usá-la no lugar do custo-hora aplica margem e imposto duas vezes.</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="B6" s="32">
         <f>TODAY()</f>
-        <v>46279.0</v>
+        <v>46282.0</v>
       </c>
     </row>
     <row r="7">

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/05-custo-hora.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/05-custo-hora.xlsx
@@ -20,10 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
-    <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
+    <numFmt numFmtId="167" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -241,16 +242,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -261,13 +262,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -285,14 +286,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -788,7 +789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -949,17 +950,29 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar. Datas de prazo do exemplo são relativas a hoje.</t>
+          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -1917,9 +1930,8 @@
           <t>Data de referência</t>
         </is>
       </c>
-      <c r="B6" s="32">
-        <f>TODAY()</f>
-        <v>46282.0</v>
+      <c r="B6" s="32" t="n">
+        <v>46279</v>
       </c>
     </row>
     <row r="7">

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/05-custo-hora.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/05-custo-hora.xlsx
@@ -938,7 +938,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/05-custo-hora.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/05-custo-hora.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
     <numFmt numFmtId="167" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,6 +66,17 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00B0A6C4"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="007A1F1F"/>
       <sz val="10"/>
     </font>
     <font>
@@ -216,29 +227,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -251,13 +262,16 @@
     <xf numFmtId="167" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -306,6 +320,7 @@
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1077,765 +1092,771 @@
       </c>
       <c r="J5" s="8" t="n"/>
     </row>
+    <row r="6">
+      <c r="A6" s="18">
+        <f>IF(SUM(Pessoas!$K$5:$K$14)=0,"","Atenção: "&amp;SUM(Pessoas!$K$5:$K$14)&amp;" pessoa(s) na aba Pessoas sem pró-labore ou sem horas faturáveis. O custo do mês, o custo-hora e a hora mínima ficam como 'cadastro incompleto' até você completar: uma soma parcial daria um custo-hora MENOR do que o real.")</f>
+        <v/>
+      </c>
+    </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>Como chegamos ao número</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Passo</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>De onde vem</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>Custos fixos do mês</t>
         </is>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="22">
         <f>'Custos fixos'!B36</f>
         <v>6500</v>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>Aba Custos fixos</t>
         </is>
       </c>
-      <c r="D9" s="23" t="n"/>
-      <c r="E9" s="24" t="n"/>
+      <c r="D9" s="24" t="n"/>
+      <c r="E9" s="25" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>Pró-labore e salários fora dos custos fixos</t>
         </is>
       </c>
-      <c r="B10" s="21">
-        <f>SUMIFS(Pessoas!$C$5:$C$14,Pessoas!$D$5:$D$14,"Não")</f>
+      <c r="B10" s="22">
+        <f>IF(SUM(Pessoas!$K$5:$K$14)&gt;0,"cadastro incompleto",SUMIFS(Pessoas!$C$5:$C$14,Pessoas!$D$5:$D$14,"Não"))</f>
         <v>12000</v>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>Aba Pessoas, quem está marcado "Não"</t>
         </is>
       </c>
-      <c r="D10" s="23" t="n"/>
-      <c r="E10" s="24" t="n"/>
+      <c r="D10" s="24" t="n"/>
+      <c r="E10" s="25" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>Custo total do mês</t>
         </is>
       </c>
-      <c r="B11" s="25">
-        <f>B9+B10</f>
+      <c r="B11" s="26">
+        <f>IF(SUM(Pessoas!$K$5:$K$14)&gt;0,"cadastro incompleto",B9+B10)</f>
         <v>18500</v>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>Soma dos dois acima</t>
         </is>
       </c>
-      <c r="D11" s="23" t="n"/>
-      <c r="E11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="25" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>Horas faturáveis no mês (todas as pessoas)</t>
         </is>
       </c>
-      <c r="B12" s="26">
-        <f>SUM(Pessoas!$F$5:$F$14)</f>
+      <c r="B12" s="27">
+        <f>IF(SUM(Pessoas!$K$5:$K$14)&gt;0,"cadastro incompleto",SUM(Pessoas!$F$5:$F$14))</f>
         <v>280</v>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>Aba Pessoas</t>
         </is>
       </c>
-      <c r="D12" s="23" t="n"/>
-      <c r="E12" s="24" t="n"/>
+      <c r="D12" s="24" t="n"/>
+      <c r="E12" s="25" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>Custo-hora do escritório</t>
         </is>
       </c>
-      <c r="B13" s="25">
-        <f>IF(B12=0,"",B11/B12)</f>
+      <c r="B13" s="26">
+        <f>IF(SUM(Pessoas!$K$5:$K$14)&gt;0,"cadastro incompleto",IF(B12=0,"",B11/B12))</f>
         <v>66.0714285714286</v>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>Custo total ÷ horas faturáveis</t>
         </is>
       </c>
-      <c r="D13" s="23" t="n"/>
-      <c r="E13" s="24" t="n"/>
+      <c r="D13" s="24" t="n"/>
+      <c r="E13" s="25" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>Margem desejada sobre o preço</t>
         </is>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="28">
         <f>Config!$B$7</f>
         <v>0.3</v>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="D14" s="23" t="n"/>
-      <c r="E14" s="24" t="n"/>
+      <c r="D14" s="24" t="n"/>
+      <c r="E14" s="25" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>Impostos e taxas sobre o que entra</t>
         </is>
       </c>
-      <c r="B15" s="27">
+      <c r="B15" s="28">
         <f>Config!$B$8</f>
         <v>0.08</v>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="D15" s="23" t="n"/>
-      <c r="E15" s="24" t="n"/>
+      <c r="D15" s="24" t="n"/>
+      <c r="E15" s="25" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>Hora mínima a cobrar (exata)</t>
         </is>
       </c>
-      <c r="B16" s="21">
-        <f>IF(B13="","",IFERROR(B13/(1-Config!$B$7-Config!$B$8),""))</f>
+      <c r="B16" s="22">
+        <f>IF(B13="","",IF(NOT(ISNUMBER(B13)),B13,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",B13/(1-Config!$B$7-Config!$B$8))))</f>
         <v>106.566820276498</v>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>Custo-hora ÷ (1 − margem − impostos)</t>
         </is>
       </c>
-      <c r="D16" s="23" t="n"/>
-      <c r="E16" s="24" t="n"/>
+      <c r="D16" s="24" t="n"/>
+      <c r="E16" s="25" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>Hora mínima a cobrar (arredondada)</t>
         </is>
       </c>
-      <c r="B17" s="25">
-        <f>IF(B16="","",CEILING(B16,Config!$B$9))</f>
+      <c r="B17" s="26">
+        <f>IF(B16="","",IF(NOT(ISNUMBER(B16)),B16,CEILING(B16,Config!$B$9)))</f>
         <v>110</v>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>Arredondada para cima, no múltiplo de Config</t>
         </is>
       </c>
-      <c r="D17" s="23" t="n"/>
-      <c r="E17" s="24" t="n"/>
+      <c r="D17" s="24" t="n"/>
+      <c r="E17" s="25" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>Custos indiretos (custos fixos menos pessoas já contadas neles)</t>
         </is>
       </c>
-      <c r="B18" s="21">
-        <f>B9-SUMIFS(Pessoas!$C$5:$C$14,Pessoas!$D$5:$D$14,"Sim")</f>
+      <c r="B18" s="22">
+        <f>IF(SUM(Pessoas!$K$5:$K$14)&gt;0,"cadastro incompleto",B9-SUMIFS(Pessoas!$C$5:$C$14,Pessoas!$D$5:$D$14,"Sim"))</f>
         <v>5100</v>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>Para ratear entre as pessoas</t>
         </is>
       </c>
-      <c r="D18" s="23" t="n"/>
-      <c r="E18" s="24" t="n"/>
+      <c r="D18" s="24" t="n"/>
+      <c r="E18" s="25" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>Custo indireto por hora faturável</t>
         </is>
       </c>
-      <c r="B19" s="21">
-        <f>IF(B12=0,0,B18/B12)</f>
+      <c r="B19" s="22">
+        <f>IF(SUM(Pessoas!$K$5:$K$14)&gt;0,"cadastro incompleto",IF(B12=0,0,B18/B12))</f>
         <v>18.2142857142857</v>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>Custos indiretos ÷ horas faturáveis</t>
         </is>
       </c>
-      <c r="D19" s="23" t="n"/>
-      <c r="E19" s="24" t="n"/>
+      <c r="D19" s="24" t="n"/>
+      <c r="E19" s="25" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>Horas de trabalho no mês (todas as pessoas)</t>
         </is>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="27">
         <f>SUM(Pessoas!$E$5:$E$14)</f>
         <v>440</v>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>Aba Pessoas</t>
         </is>
       </c>
-      <c r="D20" s="23" t="n"/>
-      <c r="E20" s="24" t="n"/>
+      <c r="D20" s="24" t="n"/>
+      <c r="E20" s="25" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>Tempo faturável planejado (horas faturáveis ÷ horas de trabalho)</t>
         </is>
       </c>
-      <c r="B21" s="27">
-        <f>IF(B20=0,"",B12/B20)</f>
+      <c r="B21" s="28">
+        <f>IF(OR(B20=0,NOT(ISNUMBER(B12))),"",B12/B20)</f>
         <v>0.636363636363636</v>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>Quanto do tempo pago vira hora cobrável (a planilha 16 mede o realizado contra a meta)</t>
         </is>
       </c>
-      <c r="D21" s="23" t="n"/>
-      <c r="E21" s="24" t="n"/>
+      <c r="D21" s="24" t="n"/>
+      <c r="E21" s="25" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>Por pessoa</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>Pessoa</t>
         </is>
       </c>
-      <c r="B25" s="19" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>Papel</t>
         </is>
       </c>
-      <c r="C25" s="19" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>Horas faturáveis</t>
         </is>
       </c>
-      <c r="D25" s="19" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>Ocupação</t>
         </is>
       </c>
-      <c r="E25" s="19" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>Custo direto por hora</t>
         </is>
       </c>
-      <c r="F25" s="19" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>Custo-hora completo</t>
         </is>
       </c>
-      <c r="G25" s="19" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>Hora mínima a cobrar</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="str">
+      <c r="A26" s="21" t="str">
         <f>IF(Pessoas!$A$5="","",Pessoas!$A$5)</f>
         <v>Marina Ferraz</v>
       </c>
-      <c r="B26" s="20" t="str">
+      <c r="B26" s="21" t="str">
         <f>IF(Pessoas!$A$5="","",Pessoas!$B$5)</f>
         <v>Sócia · cível e empresarial</v>
       </c>
-      <c r="C26" s="26">
+      <c r="C26" s="27">
         <f>IF(Pessoas!$A$5="","",Pessoas!$F$5)</f>
         <v>110</v>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="28">
         <f>IF(Pessoas!$A$5="","",Pessoas!$G$5)</f>
         <v>0.6875</v>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="22">
         <f>IF(Pessoas!$A$5="","",Pessoas!$H$5)</f>
         <v>54.5454545454546</v>
       </c>
-      <c r="F26" s="21">
+      <c r="F26" s="22">
         <f>IF(Pessoas!$A$5="","",Pessoas!$I$5)</f>
         <v>72.7597402597403</v>
       </c>
-      <c r="G26" s="21">
+      <c r="G26" s="22">
         <f>IF(Pessoas!$A$5="","",Pessoas!$J$5)</f>
         <v>117.354419773775</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="str">
+      <c r="A27" s="21" t="str">
         <f>IF(Pessoas!$A$6="","",Pessoas!$A$6)</f>
         <v>Rafael Lima</v>
       </c>
-      <c r="B27" s="20" t="str">
+      <c r="B27" s="21" t="str">
         <f>IF(Pessoas!$A$6="","",Pessoas!$B$6)</f>
         <v>Sócio · trabalhista e previdenciário</v>
       </c>
-      <c r="C27" s="26">
+      <c r="C27" s="27">
         <f>IF(Pessoas!$A$6="","",Pessoas!$F$6)</f>
         <v>110</v>
       </c>
-      <c r="D27" s="27">
+      <c r="D27" s="28">
         <f>IF(Pessoas!$A$6="","",Pessoas!$G$6)</f>
         <v>0.6875</v>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="22">
         <f>IF(Pessoas!$A$6="","",Pessoas!$H$6)</f>
         <v>54.5454545454546</v>
       </c>
-      <c r="F27" s="21">
+      <c r="F27" s="22">
         <f>IF(Pessoas!$A$6="","",Pessoas!$I$6)</f>
         <v>72.7597402597403</v>
       </c>
-      <c r="G27" s="21">
+      <c r="G27" s="22">
         <f>IF(Pessoas!$A$6="","",Pessoas!$J$6)</f>
         <v>117.354419773775</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="str">
+      <c r="A28" s="21" t="str">
         <f>IF(Pessoas!$A$7="","",Pessoas!$A$7)</f>
         <v>Júlia Prado</v>
       </c>
-      <c r="B28" s="20" t="str">
+      <c r="B28" s="21" t="str">
         <f>IF(Pessoas!$A$7="","",Pessoas!$B$7)</f>
         <v>Estagiária</v>
       </c>
-      <c r="C28" s="26">
+      <c r="C28" s="27">
         <f>IF(Pessoas!$A$7="","",Pessoas!$F$7)</f>
         <v>60</v>
       </c>
-      <c r="D28" s="27">
+      <c r="D28" s="28">
         <f>IF(Pessoas!$A$7="","",Pessoas!$G$7)</f>
         <v>0.5</v>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="22">
         <f>IF(Pessoas!$A$7="","",Pessoas!$H$7)</f>
         <v>23.3333333333333</v>
       </c>
-      <c r="F28" s="21">
+      <c r="F28" s="22">
         <f>IF(Pessoas!$A$7="","",Pessoas!$I$7)</f>
         <v>41.5476190476191</v>
       </c>
-      <c r="G28" s="21">
+      <c r="G28" s="22">
         <f>IF(Pessoas!$A$7="","",Pessoas!$J$7)</f>
         <v>67.0122887864823</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="20">
+      <c r="A29" s="21">
         <f>IF(Pessoas!$A$8="","",Pessoas!$A$8)</f>
         <v/>
       </c>
-      <c r="B29" s="20">
+      <c r="B29" s="21">
         <f>IF(Pessoas!$A$8="","",Pessoas!$B$8)</f>
         <v/>
       </c>
-      <c r="C29" s="26">
+      <c r="C29" s="27">
         <f>IF(Pessoas!$A$8="","",Pessoas!$F$8)</f>
         <v/>
       </c>
-      <c r="D29" s="27">
+      <c r="D29" s="28">
         <f>IF(Pessoas!$A$8="","",Pessoas!$G$8)</f>
         <v/>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="22">
         <f>IF(Pessoas!$A$8="","",Pessoas!$H$8)</f>
         <v/>
       </c>
-      <c r="F29" s="21">
+      <c r="F29" s="22">
         <f>IF(Pessoas!$A$8="","",Pessoas!$I$8)</f>
         <v/>
       </c>
-      <c r="G29" s="21">
+      <c r="G29" s="22">
         <f>IF(Pessoas!$A$8="","",Pessoas!$J$8)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="20">
+      <c r="A30" s="21">
         <f>IF(Pessoas!$A$9="","",Pessoas!$A$9)</f>
         <v/>
       </c>
-      <c r="B30" s="20">
+      <c r="B30" s="21">
         <f>IF(Pessoas!$A$9="","",Pessoas!$B$9)</f>
         <v/>
       </c>
-      <c r="C30" s="26">
+      <c r="C30" s="27">
         <f>IF(Pessoas!$A$9="","",Pessoas!$F$9)</f>
         <v/>
       </c>
-      <c r="D30" s="27">
+      <c r="D30" s="28">
         <f>IF(Pessoas!$A$9="","",Pessoas!$G$9)</f>
         <v/>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="22">
         <f>IF(Pessoas!$A$9="","",Pessoas!$H$9)</f>
         <v/>
       </c>
-      <c r="F30" s="21">
+      <c r="F30" s="22">
         <f>IF(Pessoas!$A$9="","",Pessoas!$I$9)</f>
         <v/>
       </c>
-      <c r="G30" s="21">
+      <c r="G30" s="22">
         <f>IF(Pessoas!$A$9="","",Pessoas!$J$9)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="20">
+      <c r="A31" s="21">
         <f>IF(Pessoas!$A$10="","",Pessoas!$A$10)</f>
         <v/>
       </c>
-      <c r="B31" s="20">
+      <c r="B31" s="21">
         <f>IF(Pessoas!$A$10="","",Pessoas!$B$10)</f>
         <v/>
       </c>
-      <c r="C31" s="26">
+      <c r="C31" s="27">
         <f>IF(Pessoas!$A$10="","",Pessoas!$F$10)</f>
         <v/>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="28">
         <f>IF(Pessoas!$A$10="","",Pessoas!$G$10)</f>
         <v/>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="22">
         <f>IF(Pessoas!$A$10="","",Pessoas!$H$10)</f>
         <v/>
       </c>
-      <c r="F31" s="21">
+      <c r="F31" s="22">
         <f>IF(Pessoas!$A$10="","",Pessoas!$I$10)</f>
         <v/>
       </c>
-      <c r="G31" s="21">
+      <c r="G31" s="22">
         <f>IF(Pessoas!$A$10="","",Pessoas!$J$10)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="20">
+      <c r="A32" s="21">
         <f>IF(Pessoas!$A$11="","",Pessoas!$A$11)</f>
         <v/>
       </c>
-      <c r="B32" s="20">
+      <c r="B32" s="21">
         <f>IF(Pessoas!$A$11="","",Pessoas!$B$11)</f>
         <v/>
       </c>
-      <c r="C32" s="26">
+      <c r="C32" s="27">
         <f>IF(Pessoas!$A$11="","",Pessoas!$F$11)</f>
         <v/>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="28">
         <f>IF(Pessoas!$A$11="","",Pessoas!$G$11)</f>
         <v/>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="22">
         <f>IF(Pessoas!$A$11="","",Pessoas!$H$11)</f>
         <v/>
       </c>
-      <c r="F32" s="21">
+      <c r="F32" s="22">
         <f>IF(Pessoas!$A$11="","",Pessoas!$I$11)</f>
         <v/>
       </c>
-      <c r="G32" s="21">
+      <c r="G32" s="22">
         <f>IF(Pessoas!$A$11="","",Pessoas!$J$11)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="20">
+      <c r="A33" s="21">
         <f>IF(Pessoas!$A$12="","",Pessoas!$A$12)</f>
         <v/>
       </c>
-      <c r="B33" s="20">
+      <c r="B33" s="21">
         <f>IF(Pessoas!$A$12="","",Pessoas!$B$12)</f>
         <v/>
       </c>
-      <c r="C33" s="26">
+      <c r="C33" s="27">
         <f>IF(Pessoas!$A$12="","",Pessoas!$F$12)</f>
         <v/>
       </c>
-      <c r="D33" s="27">
+      <c r="D33" s="28">
         <f>IF(Pessoas!$A$12="","",Pessoas!$G$12)</f>
         <v/>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="22">
         <f>IF(Pessoas!$A$12="","",Pessoas!$H$12)</f>
         <v/>
       </c>
-      <c r="F33" s="21">
+      <c r="F33" s="22">
         <f>IF(Pessoas!$A$12="","",Pessoas!$I$12)</f>
         <v/>
       </c>
-      <c r="G33" s="21">
+      <c r="G33" s="22">
         <f>IF(Pessoas!$A$12="","",Pessoas!$J$12)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="20">
+      <c r="A34" s="21">
         <f>IF(Pessoas!$A$13="","",Pessoas!$A$13)</f>
         <v/>
       </c>
-      <c r="B34" s="20">
+      <c r="B34" s="21">
         <f>IF(Pessoas!$A$13="","",Pessoas!$B$13)</f>
         <v/>
       </c>
-      <c r="C34" s="26">
+      <c r="C34" s="27">
         <f>IF(Pessoas!$A$13="","",Pessoas!$F$13)</f>
         <v/>
       </c>
-      <c r="D34" s="27">
+      <c r="D34" s="28">
         <f>IF(Pessoas!$A$13="","",Pessoas!$G$13)</f>
         <v/>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="22">
         <f>IF(Pessoas!$A$13="","",Pessoas!$H$13)</f>
         <v/>
       </c>
-      <c r="F34" s="21">
+      <c r="F34" s="22">
         <f>IF(Pessoas!$A$13="","",Pessoas!$I$13)</f>
         <v/>
       </c>
-      <c r="G34" s="21">
+      <c r="G34" s="22">
         <f>IF(Pessoas!$A$13="","",Pessoas!$J$13)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="20">
+      <c r="A35" s="21">
         <f>IF(Pessoas!$A$14="","",Pessoas!$A$14)</f>
         <v/>
       </c>
-      <c r="B35" s="20">
+      <c r="B35" s="21">
         <f>IF(Pessoas!$A$14="","",Pessoas!$B$14)</f>
         <v/>
       </c>
-      <c r="C35" s="26">
+      <c r="C35" s="27">
         <f>IF(Pessoas!$A$14="","",Pessoas!$F$14)</f>
         <v/>
       </c>
-      <c r="D35" s="27">
+      <c r="D35" s="28">
         <f>IF(Pessoas!$A$14="","",Pessoas!$G$14)</f>
         <v/>
       </c>
-      <c r="E35" s="21">
+      <c r="E35" s="22">
         <f>IF(Pessoas!$A$14="","",Pessoas!$H$14)</f>
         <v/>
       </c>
-      <c r="F35" s="21">
+      <c r="F35" s="22">
         <f>IF(Pessoas!$A$14="","",Pessoas!$I$14)</f>
         <v/>
       </c>
-      <c r="G35" s="21">
+      <c r="G35" s="22">
         <f>IF(Pessoas!$A$14="","",Pessoas!$J$14)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="28" t="inlineStr">
+      <c r="A36" s="29" t="inlineStr">
         <is>
           <t>Ocupação abaixo de 50% fica destacada: ou há horas trabalhadas que não estão sendo cobradas, ou falta caso para a pessoa.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>Sensibilidade: e se as horas faturáveis caírem?</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="28" t="inlineStr">
+      <c r="A39" s="29" t="inlineStr">
         <is>
           <t>Mês fraco, férias, um sócio doente: o custo fixo continua e cada hora fica mais cara. Os percentuais em amarelo podem ser trocados.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="19" t="inlineStr">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>Cenário</t>
         </is>
       </c>
-      <c r="B40" s="19" t="inlineStr">
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t>Queda nas horas</t>
         </is>
       </c>
-      <c r="C40" s="19" t="inlineStr">
+      <c r="C40" s="20" t="inlineStr">
         <is>
           <t>Horas faturáveis</t>
         </is>
       </c>
-      <c r="D40" s="19" t="inlineStr">
+      <c r="D40" s="20" t="inlineStr">
         <is>
           <t>Custo-hora</t>
         </is>
       </c>
-      <c r="E40" s="19" t="inlineStr">
+      <c r="E40" s="20" t="inlineStr">
         <is>
           <t>Hora mínima a cobrar</t>
         </is>
       </c>
-      <c r="F40" s="19" t="inlineStr">
+      <c r="F40" s="20" t="inlineStr">
         <is>
           <t>Diferença por hora</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="20" t="inlineStr">
+      <c r="A41" s="21" t="inlineStr">
         <is>
           <t>Hoje</t>
         </is>
       </c>
-      <c r="B41" s="27" t="n">
+      <c r="B41" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="C41" s="26">
-        <f>$B$12*(1-B41)</f>
+      <c r="C41" s="27">
+        <f>IF(ISNUMBER($B$12),$B$12*(1-B41),"")</f>
         <v>280</v>
       </c>
-      <c r="D41" s="21">
-        <f>IF(C41=0,"",$B$11/C41)</f>
+      <c r="D41" s="22">
+        <f>IF(OR(C41="",C41=0,NOT(ISNUMBER($B$11))),"",$B$11/C41)</f>
         <v>66.0714285714286</v>
       </c>
-      <c r="E41" s="21">
-        <f>IF(D41="","",IFERROR(D41/(1-Config!$B$7-Config!$B$8),""))</f>
+      <c r="E41" s="22">
+        <f>IF(D41="","",IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",D41/(1-Config!$B$7-Config!$B$8)))</f>
         <v>106.566820276498</v>
       </c>
-      <c r="F41" s="21">
+      <c r="F41" s="22">
         <f>IF(D41="","",D41-$D$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="20" t="str">
+      <c r="A42" s="21" t="str">
         <f>"Queda de "&amp;ROUND(B42*100,0)&amp;"%"</f>
         <v>Queda de 10%</v>
       </c>
-      <c r="B42" s="29" t="n">
+      <c r="B42" s="30" t="n">
         <v>0.1</v>
       </c>
-      <c r="C42" s="26">
-        <f>$B$12*(1-B42)</f>
+      <c r="C42" s="27">
+        <f>IF(ISNUMBER($B$12),$B$12*(1-B42),"")</f>
         <v>252</v>
       </c>
-      <c r="D42" s="21">
-        <f>IF(C42=0,"",$B$11/C42)</f>
+      <c r="D42" s="22">
+        <f>IF(OR(C42="",C42=0,NOT(ISNUMBER($B$11))),"",$B$11/C42)</f>
         <v>73.4126984126984</v>
       </c>
-      <c r="E42" s="21">
-        <f>IF(D42="","",IFERROR(D42/(1-Config!$B$7-Config!$B$8),""))</f>
+      <c r="E42" s="22">
+        <f>IF(D42="","",IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",D42/(1-Config!$B$7-Config!$B$8)))</f>
         <v>118.407578084997</v>
       </c>
-      <c r="F42" s="21">
+      <c r="F42" s="22">
         <f>IF(D42="","",D42-$D$41)</f>
         <v>7.34126984126985</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="20" t="str">
+      <c r="A43" s="21" t="str">
         <f>"Queda de "&amp;ROUND(B43*100,0)&amp;"%"</f>
         <v>Queda de 20%</v>
       </c>
-      <c r="B43" s="29" t="n">
+      <c r="B43" s="30" t="n">
         <v>0.2</v>
       </c>
-      <c r="C43" s="26">
-        <f>$B$12*(1-B43)</f>
+      <c r="C43" s="27">
+        <f>IF(ISNUMBER($B$12),$B$12*(1-B43),"")</f>
         <v>224</v>
       </c>
-      <c r="D43" s="21">
-        <f>IF(C43=0,"",$B$11/C43)</f>
+      <c r="D43" s="22">
+        <f>IF(OR(C43="",C43=0,NOT(ISNUMBER($B$11))),"",$B$11/C43)</f>
         <v>82.5892857142857</v>
       </c>
-      <c r="E43" s="21">
-        <f>IF(D43="","",IFERROR(D43/(1-Config!$B$7-Config!$B$8),""))</f>
+      <c r="E43" s="22">
+        <f>IF(D43="","",IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",D43/(1-Config!$B$7-Config!$B$8)))</f>
         <v>133.208525345622</v>
       </c>
-      <c r="F43" s="21">
+      <c r="F43" s="22">
         <f>IF(D43="","",D43-$D$41)</f>
         <v>16.5178571428571</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="20" t="str">
+      <c r="A44" s="21" t="str">
         <f>"Queda de "&amp;ROUND(B44*100,0)&amp;"%"</f>
         <v>Queda de 30%</v>
       </c>
-      <c r="B44" s="29" t="n">
+      <c r="B44" s="30" t="n">
         <v>0.3</v>
       </c>
-      <c r="C44" s="26">
-        <f>$B$12*(1-B44)</f>
+      <c r="C44" s="27">
+        <f>IF(ISNUMBER($B$12),$B$12*(1-B44),"")</f>
         <v>196</v>
       </c>
-      <c r="D44" s="21">
-        <f>IF(C44=0,"",$B$11/C44)</f>
+      <c r="D44" s="22">
+        <f>IF(OR(C44="",C44=0,NOT(ISNUMBER($B$11))),"",$B$11/C44)</f>
         <v>94.3877551020408</v>
       </c>
-      <c r="E44" s="21">
-        <f>IF(D44="","",IFERROR(D44/(1-Config!$B$7-Config!$B$8),""))</f>
+      <c r="E44" s="22">
+        <f>IF(D44="","",IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",D44/(1-Config!$B$7-Config!$B$8)))</f>
         <v>152.238314680711</v>
       </c>
-      <c r="F44" s="21">
+      <c r="F44" s="22">
         <f>IF(D44="","",D44-$D$41)</f>
         <v>28.3163265306122</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="25">
+  <mergeCells count="26">
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="C9:E9"/>
@@ -1848,6 +1869,7 @@
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="C13:E13"/>
+    <mergeCell ref="A6:J6"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="G5:H5"/>
@@ -1901,93 +1923,93 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>Nome do escritório</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>Ferraz &amp; Lima Advocacia (exemplo fictício)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>Mês de referência</t>
         </is>
       </c>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>Setembro de 2026</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>Data de referência</t>
         </is>
       </c>
-      <c r="B6" s="32" t="n">
+      <c r="B6" s="33" t="n">
         <v>46279</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>Margem desejada sobre o preço (%)</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="30" t="n">
         <v>0.3</v>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Quanto do preço deve sobrar depois de pagar o custo do escritório. 30% é um ponto de partida; ajuste ao seu mercado.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>Impostos e taxas sobre o que entra (%)</t>
         </is>
       </c>
-      <c r="B8" s="29" t="n">
+      <c r="B8" s="30" t="n">
         <v>0.08</v>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Percentual que sai de cada real recebido (imposto do escritório e taxa de recebimento). Exemplo; confira com o seu contador.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Arredondar a hora mínima para múltiplos de (R$)</t>
         </is>
       </c>
-      <c r="B9" s="33" t="n">
+      <c r="B9" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Só para o número ficar redondo na proposta.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>A hora mínima a cobrar é: custo-hora ÷ (1 − margem − impostos). Assim a margem é calculada sobre o preço, e não sobre o custo.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>Esta é a hora mínima do kit (no exemplo: R$ 106,57, arredondada para R$ 110). A planilha 06 usa a mesma conta; a planilha 08 acrescenta uma folga de 20 % para horas não previstas e por isso mostra um valor maior ("hora mínima com folga").</t>
         </is>
@@ -1999,6 +2021,14 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Margem entre 0 % e 99 %, e margem + impostos abaixo de 100 %: senão nenhum preço cobre o custo." type="custom">
+      <formula1>=AND(ISNUMBER(B7),B7&gt;=0,B7&lt;1,B7+N(B8)&lt;1)</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Impostos entre 0 % e 99 %, e margem + impostos abaixo de 100 %: senão nenhum preço cobre o custo." type="custom">
+      <formula1>=AND(ISNUMBER(B8),B8&gt;=0,B8&lt;1,B8+N(B7)&lt;1)</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2032,237 +2062,237 @@
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>Custo fixo</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>Valor mensal (R$)</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>Observação</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>Aluguel e condomínio</t>
         </is>
       </c>
-      <c r="B5" s="34" t="n">
+      <c r="B5" s="35" t="n">
         <v>2800</v>
       </c>
-      <c r="C5" s="31" t="n"/>
+      <c r="C5" s="32" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="A6" s="32" t="inlineStr">
         <is>
           <t>Contador</t>
         </is>
       </c>
-      <c r="B6" s="34" t="n">
+      <c r="B6" s="35" t="n">
         <v>600</v>
       </c>
-      <c r="C6" s="31" t="n"/>
+      <c r="C6" s="32" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>Sistemas e assinaturas</t>
         </is>
       </c>
-      <c r="B7" s="34" t="n">
+      <c r="B7" s="35" t="n">
         <v>450</v>
       </c>
-      <c r="C7" s="31" t="n"/>
+      <c r="C7" s="32" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>Telefone e internet</t>
         </is>
       </c>
-      <c r="B8" s="34" t="n">
+      <c r="B8" s="35" t="n">
         <v>220</v>
       </c>
-      <c r="C8" s="31" t="n"/>
+      <c r="C8" s="32" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Anuidades OAB e cursos</t>
         </is>
       </c>
-      <c r="B9" s="34" t="n">
+      <c r="B9" s="35" t="n">
         <v>250</v>
       </c>
-      <c r="C9" s="31" t="n"/>
+      <c r="C9" s="32" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>Marketing e site</t>
         </is>
       </c>
-      <c r="B10" s="34" t="n">
+      <c r="B10" s="35" t="n">
         <v>400</v>
       </c>
-      <c r="C10" s="31" t="n"/>
+      <c r="C10" s="32" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>Estagiária (bolsa)</t>
         </is>
       </c>
-      <c r="B11" s="34" t="n">
+      <c r="B11" s="35" t="n">
         <v>1400</v>
       </c>
-      <c r="C11" s="31" t="inlineStr">
+      <c r="C11" s="32" t="inlineStr">
         <is>
           <t>Mesma pessoa da aba Pessoas (marcada "Sim" lá)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>Material, correio e outros</t>
         </is>
       </c>
-      <c r="B12" s="34" t="n">
+      <c r="B12" s="35" t="n">
         <v>380</v>
       </c>
-      <c r="C12" s="31" t="n"/>
+      <c r="C12" s="32" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="n"/>
-      <c r="B13" s="34" t="n"/>
-      <c r="C13" s="31" t="n"/>
+      <c r="A13" s="32" t="n"/>
+      <c r="B13" s="35" t="n"/>
+      <c r="C13" s="32" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="n"/>
-      <c r="B14" s="34" t="n"/>
-      <c r="C14" s="31" t="n"/>
+      <c r="A14" s="32" t="n"/>
+      <c r="B14" s="35" t="n"/>
+      <c r="C14" s="32" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="31" t="n"/>
-      <c r="B15" s="34" t="n"/>
-      <c r="C15" s="31" t="n"/>
+      <c r="A15" s="32" t="n"/>
+      <c r="B15" s="35" t="n"/>
+      <c r="C15" s="32" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="31" t="n"/>
-      <c r="B16" s="34" t="n"/>
-      <c r="C16" s="31" t="n"/>
+      <c r="A16" s="32" t="n"/>
+      <c r="B16" s="35" t="n"/>
+      <c r="C16" s="32" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="31" t="n"/>
-      <c r="B17" s="34" t="n"/>
-      <c r="C17" s="31" t="n"/>
+      <c r="A17" s="32" t="n"/>
+      <c r="B17" s="35" t="n"/>
+      <c r="C17" s="32" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="31" t="n"/>
-      <c r="B18" s="34" t="n"/>
-      <c r="C18" s="31" t="n"/>
+      <c r="A18" s="32" t="n"/>
+      <c r="B18" s="35" t="n"/>
+      <c r="C18" s="32" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="31" t="n"/>
-      <c r="B19" s="34" t="n"/>
-      <c r="C19" s="31" t="n"/>
+      <c r="A19" s="32" t="n"/>
+      <c r="B19" s="35" t="n"/>
+      <c r="C19" s="32" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="31" t="n"/>
-      <c r="B20" s="34" t="n"/>
-      <c r="C20" s="31" t="n"/>
+      <c r="A20" s="32" t="n"/>
+      <c r="B20" s="35" t="n"/>
+      <c r="C20" s="32" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="31" t="n"/>
-      <c r="B21" s="34" t="n"/>
-      <c r="C21" s="31" t="n"/>
+      <c r="A21" s="32" t="n"/>
+      <c r="B21" s="35" t="n"/>
+      <c r="C21" s="32" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="31" t="n"/>
-      <c r="B22" s="34" t="n"/>
-      <c r="C22" s="31" t="n"/>
+      <c r="A22" s="32" t="n"/>
+      <c r="B22" s="35" t="n"/>
+      <c r="C22" s="32" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="31" t="n"/>
-      <c r="B23" s="34" t="n"/>
-      <c r="C23" s="31" t="n"/>
+      <c r="A23" s="32" t="n"/>
+      <c r="B23" s="35" t="n"/>
+      <c r="C23" s="32" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="31" t="n"/>
-      <c r="B24" s="34" t="n"/>
-      <c r="C24" s="31" t="n"/>
+      <c r="A24" s="32" t="n"/>
+      <c r="B24" s="35" t="n"/>
+      <c r="C24" s="32" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="31" t="n"/>
-      <c r="B25" s="34" t="n"/>
-      <c r="C25" s="31" t="n"/>
+      <c r="A25" s="32" t="n"/>
+      <c r="B25" s="35" t="n"/>
+      <c r="C25" s="32" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="31" t="n"/>
-      <c r="B26" s="34" t="n"/>
-      <c r="C26" s="31" t="n"/>
+      <c r="A26" s="32" t="n"/>
+      <c r="B26" s="35" t="n"/>
+      <c r="C26" s="32" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="31" t="n"/>
-      <c r="B27" s="34" t="n"/>
-      <c r="C27" s="31" t="n"/>
+      <c r="A27" s="32" t="n"/>
+      <c r="B27" s="35" t="n"/>
+      <c r="C27" s="32" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="31" t="n"/>
-      <c r="B28" s="34" t="n"/>
-      <c r="C28" s="31" t="n"/>
+      <c r="A28" s="32" t="n"/>
+      <c r="B28" s="35" t="n"/>
+      <c r="C28" s="32" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="31" t="n"/>
-      <c r="B29" s="34" t="n"/>
-      <c r="C29" s="31" t="n"/>
+      <c r="A29" s="32" t="n"/>
+      <c r="B29" s="35" t="n"/>
+      <c r="C29" s="32" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="31" t="n"/>
-      <c r="B30" s="34" t="n"/>
-      <c r="C30" s="31" t="n"/>
+      <c r="A30" s="32" t="n"/>
+      <c r="B30" s="35" t="n"/>
+      <c r="C30" s="32" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="31" t="n"/>
-      <c r="B31" s="34" t="n"/>
-      <c r="C31" s="31" t="n"/>
+      <c r="A31" s="32" t="n"/>
+      <c r="B31" s="35" t="n"/>
+      <c r="C31" s="32" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="31" t="n"/>
-      <c r="B32" s="34" t="n"/>
-      <c r="C32" s="31" t="n"/>
+      <c r="A32" s="32" t="n"/>
+      <c r="B32" s="35" t="n"/>
+      <c r="C32" s="32" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="31" t="n"/>
-      <c r="B33" s="34" t="n"/>
-      <c r="C33" s="31" t="n"/>
+      <c r="A33" s="32" t="n"/>
+      <c r="B33" s="35" t="n"/>
+      <c r="C33" s="32" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="31" t="n"/>
-      <c r="B34" s="34" t="n"/>
-      <c r="C34" s="31" t="n"/>
+      <c r="A34" s="32" t="n"/>
+      <c r="B34" s="35" t="n"/>
+      <c r="C34" s="32" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="35" t="inlineStr">
+      <c r="A36" s="36" t="inlineStr">
         <is>
           <t>Total de custos fixos</t>
         </is>
       </c>
-      <c r="B36" s="25">
+      <c r="B36" s="26">
         <f>SUM(B5:B34)</f>
         <v>6500</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="28" t="inlineStr">
+      <c r="A38" s="29" t="inlineStr">
         <is>
           <t>Pró-labore dos sócios vai na aba Pessoas. Se alguém da equipe já aparece aqui (bolsa de estágio, salário), marque "Sim" na aba Pessoas para não contar duas vezes.</t>
         </is>
@@ -2284,7 +2314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2297,6 +2327,7 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
+    <col hidden="1" width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2314,360 +2345,400 @@
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>Pessoa</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>Papel</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>Pró-labore ou salário (R$/mês)</t>
         </is>
       </c>
-      <c r="D4" s="19" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>Já está nos custos fixos?</t>
         </is>
       </c>
-      <c r="E4" s="19" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>Horas de trabalho no mês</t>
         </is>
       </c>
-      <c r="F4" s="19" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>Horas faturáveis no mês</t>
         </is>
       </c>
-      <c r="G4" s="19" t="inlineStr">
+      <c r="G4" s="20" t="inlineStr">
         <is>
           <t>Ocupação</t>
         </is>
       </c>
-      <c r="H4" s="19" t="inlineStr">
+      <c r="H4" s="20" t="inlineStr">
         <is>
           <t>Custo direto por hora</t>
         </is>
       </c>
-      <c r="I4" s="19" t="inlineStr">
+      <c r="I4" s="20" t="inlineStr">
         <is>
           <t>Custo-hora completo</t>
         </is>
       </c>
-      <c r="J4" s="19" t="inlineStr">
+      <c r="J4" s="20" t="inlineStr">
         <is>
           <t>Hora mínima a cobrar</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>Marina Ferraz</t>
         </is>
       </c>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>Sócia · cível e empresarial</t>
         </is>
       </c>
-      <c r="C5" s="34" t="n">
+      <c r="C5" s="35" t="n">
         <v>6000</v>
       </c>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="D5" s="37" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="E5" s="37" t="n">
+      <c r="E5" s="38" t="n">
         <v>160</v>
       </c>
-      <c r="F5" s="37" t="n">
+      <c r="F5" s="38" t="n">
         <v>110</v>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="28">
         <f>IF(OR(A5="",E5="",E5=0),"",F5/E5)</f>
         <v>0.6875</v>
       </c>
-      <c r="H5" s="21">
-        <f>IF(OR(A5="",F5="",F5=0),"",C5/F5)</f>
+      <c r="H5" s="22">
+        <f>IF(A5="","",IF(NOT(ISNUMBER(C5)),"falta o pró-labore",IF(OR(NOT(ISNUMBER(F5)),F5=0),"faltam as horas faturáveis",C5/F5)))</f>
         <v>54.5454545454546</v>
       </c>
-      <c r="I5" s="21">
-        <f>IF(H5="","",H5+Painel!$B$19)</f>
+      <c r="I5" s="22">
+        <f>IF(H5="","",IF(NOT(ISNUMBER(H5)),H5,IF(NOT(ISNUMBER(Painel!$B$19)),"cadastro incompleto",H5+Painel!$B$19)))</f>
         <v>72.7597402597403</v>
       </c>
-      <c r="J5" s="21">
-        <f>IF(I5="","",IFERROR(I5/(1-Config!$B$7-Config!$B$8),""))</f>
+      <c r="J5" s="22">
+        <f>IF(I5="","",IF(NOT(ISNUMBER(I5)),I5,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I5/(1-Config!$B$7-Config!$B$8))))</f>
         <v>117.354419773775</v>
       </c>
+      <c r="K5" s="39">
+        <f>IF(AND(A5&lt;&gt;"",OR(NOT(ISNUMBER(C5)),NOT(ISNUMBER(F5)))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="A6" s="32" t="inlineStr">
         <is>
           <t>Rafael Lima</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>Sócio · trabalhista e previdenciário</t>
         </is>
       </c>
-      <c r="C6" s="34" t="n">
+      <c r="C6" s="35" t="n">
         <v>6000</v>
       </c>
-      <c r="D6" s="36" t="inlineStr">
+      <c r="D6" s="37" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="E6" s="37" t="n">
+      <c r="E6" s="38" t="n">
         <v>160</v>
       </c>
-      <c r="F6" s="37" t="n">
+      <c r="F6" s="38" t="n">
         <v>110</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="28">
         <f>IF(OR(A6="",E6="",E6=0),"",F6/E6)</f>
         <v>0.6875</v>
       </c>
-      <c r="H6" s="21">
-        <f>IF(OR(A6="",F6="",F6=0),"",C6/F6)</f>
+      <c r="H6" s="22">
+        <f>IF(A6="","",IF(NOT(ISNUMBER(C6)),"falta o pró-labore",IF(OR(NOT(ISNUMBER(F6)),F6=0),"faltam as horas faturáveis",C6/F6)))</f>
         <v>54.5454545454546</v>
       </c>
-      <c r="I6" s="21">
-        <f>IF(H6="","",H6+Painel!$B$19)</f>
+      <c r="I6" s="22">
+        <f>IF(H6="","",IF(NOT(ISNUMBER(H6)),H6,IF(NOT(ISNUMBER(Painel!$B$19)),"cadastro incompleto",H6+Painel!$B$19)))</f>
         <v>72.7597402597403</v>
       </c>
-      <c r="J6" s="21">
-        <f>IF(I6="","",IFERROR(I6/(1-Config!$B$7-Config!$B$8),""))</f>
+      <c r="J6" s="22">
+        <f>IF(I6="","",IF(NOT(ISNUMBER(I6)),I6,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I6/(1-Config!$B$7-Config!$B$8))))</f>
         <v>117.354419773775</v>
       </c>
+      <c r="K6" s="39">
+        <f>IF(AND(A6&lt;&gt;"",OR(NOT(ISNUMBER(C6)),NOT(ISNUMBER(F6)))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>Júlia Prado</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Estagiária</t>
         </is>
       </c>
-      <c r="C7" s="34" t="n">
+      <c r="C7" s="35" t="n">
         <v>1400</v>
       </c>
-      <c r="D7" s="36" t="inlineStr">
+      <c r="D7" s="37" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E7" s="37" t="n">
+      <c r="E7" s="38" t="n">
         <v>120</v>
       </c>
-      <c r="F7" s="37" t="n">
+      <c r="F7" s="38" t="n">
         <v>60</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="28">
         <f>IF(OR(A7="",E7="",E7=0),"",F7/E7)</f>
         <v>0.5</v>
       </c>
-      <c r="H7" s="21">
-        <f>IF(OR(A7="",F7="",F7=0),"",C7/F7)</f>
+      <c r="H7" s="22">
+        <f>IF(A7="","",IF(NOT(ISNUMBER(C7)),"falta o pró-labore",IF(OR(NOT(ISNUMBER(F7)),F7=0),"faltam as horas faturáveis",C7/F7)))</f>
         <v>23.3333333333333</v>
       </c>
-      <c r="I7" s="21">
-        <f>IF(H7="","",H7+Painel!$B$19)</f>
+      <c r="I7" s="22">
+        <f>IF(H7="","",IF(NOT(ISNUMBER(H7)),H7,IF(NOT(ISNUMBER(Painel!$B$19)),"cadastro incompleto",H7+Painel!$B$19)))</f>
         <v>41.5476190476191</v>
       </c>
-      <c r="J7" s="21">
-        <f>IF(I7="","",IFERROR(I7/(1-Config!$B$7-Config!$B$8),""))</f>
+      <c r="J7" s="22">
+        <f>IF(I7="","",IF(NOT(ISNUMBER(I7)),I7,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I7/(1-Config!$B$7-Config!$B$8))))</f>
         <v>67.0122887864823</v>
       </c>
+      <c r="K7" s="39">
+        <f>IF(AND(A7&lt;&gt;"",OR(NOT(ISNUMBER(C7)),NOT(ISNUMBER(F7)))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="31" t="n"/>
-      <c r="B8" s="31" t="n"/>
-      <c r="C8" s="34" t="n"/>
-      <c r="D8" s="36" t="n"/>
-      <c r="E8" s="37" t="n"/>
-      <c r="F8" s="37" t="n"/>
-      <c r="G8" s="27">
+      <c r="A8" s="32" t="n"/>
+      <c r="B8" s="32" t="n"/>
+      <c r="C8" s="35" t="n"/>
+      <c r="D8" s="37" t="n"/>
+      <c r="E8" s="38" t="n"/>
+      <c r="F8" s="38" t="n"/>
+      <c r="G8" s="28">
         <f>IF(OR(A8="",E8="",E8=0),"",F8/E8)</f>
         <v/>
       </c>
-      <c r="H8" s="21">
-        <f>IF(OR(A8="",F8="",F8=0),"",C8/F8)</f>
-        <v/>
-      </c>
-      <c r="I8" s="21">
-        <f>IF(H8="","",H8+Painel!$B$19)</f>
-        <v/>
-      </c>
-      <c r="J8" s="21">
-        <f>IF(I8="","",IFERROR(I8/(1-Config!$B$7-Config!$B$8),""))</f>
-        <v/>
+      <c r="H8" s="22">
+        <f>IF(A8="","",IF(NOT(ISNUMBER(C8)),"falta o pró-labore",IF(OR(NOT(ISNUMBER(F8)),F8=0),"faltam as horas faturáveis",C8/F8)))</f>
+        <v/>
+      </c>
+      <c r="I8" s="22">
+        <f>IF(H8="","",IF(NOT(ISNUMBER(H8)),H8,IF(NOT(ISNUMBER(Painel!$B$19)),"cadastro incompleto",H8+Painel!$B$19)))</f>
+        <v/>
+      </c>
+      <c r="J8" s="22">
+        <f>IF(I8="","",IF(NOT(ISNUMBER(I8)),I8,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I8/(1-Config!$B$7-Config!$B$8))))</f>
+        <v/>
+      </c>
+      <c r="K8" s="39">
+        <f>IF(AND(A8&lt;&gt;"",OR(NOT(ISNUMBER(C8)),NOT(ISNUMBER(F8)))),1,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="n"/>
-      <c r="B9" s="31" t="n"/>
-      <c r="C9" s="34" t="n"/>
-      <c r="D9" s="36" t="n"/>
-      <c r="E9" s="37" t="n"/>
-      <c r="F9" s="37" t="n"/>
-      <c r="G9" s="27">
+      <c r="A9" s="32" t="n"/>
+      <c r="B9" s="32" t="n"/>
+      <c r="C9" s="35" t="n"/>
+      <c r="D9" s="37" t="n"/>
+      <c r="E9" s="38" t="n"/>
+      <c r="F9" s="38" t="n"/>
+      <c r="G9" s="28">
         <f>IF(OR(A9="",E9="",E9=0),"",F9/E9)</f>
         <v/>
       </c>
-      <c r="H9" s="21">
-        <f>IF(OR(A9="",F9="",F9=0),"",C9/F9)</f>
-        <v/>
-      </c>
-      <c r="I9" s="21">
-        <f>IF(H9="","",H9+Painel!$B$19)</f>
-        <v/>
-      </c>
-      <c r="J9" s="21">
-        <f>IF(I9="","",IFERROR(I9/(1-Config!$B$7-Config!$B$8),""))</f>
-        <v/>
+      <c r="H9" s="22">
+        <f>IF(A9="","",IF(NOT(ISNUMBER(C9)),"falta o pró-labore",IF(OR(NOT(ISNUMBER(F9)),F9=0),"faltam as horas faturáveis",C9/F9)))</f>
+        <v/>
+      </c>
+      <c r="I9" s="22">
+        <f>IF(H9="","",IF(NOT(ISNUMBER(H9)),H9,IF(NOT(ISNUMBER(Painel!$B$19)),"cadastro incompleto",H9+Painel!$B$19)))</f>
+        <v/>
+      </c>
+      <c r="J9" s="22">
+        <f>IF(I9="","",IF(NOT(ISNUMBER(I9)),I9,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I9/(1-Config!$B$7-Config!$B$8))))</f>
+        <v/>
+      </c>
+      <c r="K9" s="39">
+        <f>IF(AND(A9&lt;&gt;"",OR(NOT(ISNUMBER(C9)),NOT(ISNUMBER(F9)))),1,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="n"/>
-      <c r="B10" s="31" t="n"/>
-      <c r="C10" s="34" t="n"/>
-      <c r="D10" s="36" t="n"/>
-      <c r="E10" s="37" t="n"/>
-      <c r="F10" s="37" t="n"/>
-      <c r="G10" s="27">
+      <c r="A10" s="32" t="n"/>
+      <c r="B10" s="32" t="n"/>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="37" t="n"/>
+      <c r="E10" s="38" t="n"/>
+      <c r="F10" s="38" t="n"/>
+      <c r="G10" s="28">
         <f>IF(OR(A10="",E10="",E10=0),"",F10/E10)</f>
         <v/>
       </c>
-      <c r="H10" s="21">
-        <f>IF(OR(A10="",F10="",F10=0),"",C10/F10)</f>
-        <v/>
-      </c>
-      <c r="I10" s="21">
-        <f>IF(H10="","",H10+Painel!$B$19)</f>
-        <v/>
-      </c>
-      <c r="J10" s="21">
-        <f>IF(I10="","",IFERROR(I10/(1-Config!$B$7-Config!$B$8),""))</f>
-        <v/>
+      <c r="H10" s="22">
+        <f>IF(A10="","",IF(NOT(ISNUMBER(C10)),"falta o pró-labore",IF(OR(NOT(ISNUMBER(F10)),F10=0),"faltam as horas faturáveis",C10/F10)))</f>
+        <v/>
+      </c>
+      <c r="I10" s="22">
+        <f>IF(H10="","",IF(NOT(ISNUMBER(H10)),H10,IF(NOT(ISNUMBER(Painel!$B$19)),"cadastro incompleto",H10+Painel!$B$19)))</f>
+        <v/>
+      </c>
+      <c r="J10" s="22">
+        <f>IF(I10="","",IF(NOT(ISNUMBER(I10)),I10,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I10/(1-Config!$B$7-Config!$B$8))))</f>
+        <v/>
+      </c>
+      <c r="K10" s="39">
+        <f>IF(AND(A10&lt;&gt;"",OR(NOT(ISNUMBER(C10)),NOT(ISNUMBER(F10)))),1,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="n"/>
-      <c r="B11" s="31" t="n"/>
-      <c r="C11" s="34" t="n"/>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="37" t="n"/>
-      <c r="F11" s="37" t="n"/>
-      <c r="G11" s="27">
+      <c r="A11" s="32" t="n"/>
+      <c r="B11" s="32" t="n"/>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="37" t="n"/>
+      <c r="E11" s="38" t="n"/>
+      <c r="F11" s="38" t="n"/>
+      <c r="G11" s="28">
         <f>IF(OR(A11="",E11="",E11=0),"",F11/E11)</f>
         <v/>
       </c>
-      <c r="H11" s="21">
-        <f>IF(OR(A11="",F11="",F11=0),"",C11/F11)</f>
-        <v/>
-      </c>
-      <c r="I11" s="21">
-        <f>IF(H11="","",H11+Painel!$B$19)</f>
-        <v/>
-      </c>
-      <c r="J11" s="21">
-        <f>IF(I11="","",IFERROR(I11/(1-Config!$B$7-Config!$B$8),""))</f>
-        <v/>
+      <c r="H11" s="22">
+        <f>IF(A11="","",IF(NOT(ISNUMBER(C11)),"falta o pró-labore",IF(OR(NOT(ISNUMBER(F11)),F11=0),"faltam as horas faturáveis",C11/F11)))</f>
+        <v/>
+      </c>
+      <c r="I11" s="22">
+        <f>IF(H11="","",IF(NOT(ISNUMBER(H11)),H11,IF(NOT(ISNUMBER(Painel!$B$19)),"cadastro incompleto",H11+Painel!$B$19)))</f>
+        <v/>
+      </c>
+      <c r="J11" s="22">
+        <f>IF(I11="","",IF(NOT(ISNUMBER(I11)),I11,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I11/(1-Config!$B$7-Config!$B$8))))</f>
+        <v/>
+      </c>
+      <c r="K11" s="39">
+        <f>IF(AND(A11&lt;&gt;"",OR(NOT(ISNUMBER(C11)),NOT(ISNUMBER(F11)))),1,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="n"/>
-      <c r="B12" s="31" t="n"/>
-      <c r="C12" s="34" t="n"/>
-      <c r="D12" s="36" t="n"/>
-      <c r="E12" s="37" t="n"/>
-      <c r="F12" s="37" t="n"/>
-      <c r="G12" s="27">
+      <c r="A12" s="32" t="n"/>
+      <c r="B12" s="32" t="n"/>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="37" t="n"/>
+      <c r="E12" s="38" t="n"/>
+      <c r="F12" s="38" t="n"/>
+      <c r="G12" s="28">
         <f>IF(OR(A12="",E12="",E12=0),"",F12/E12)</f>
         <v/>
       </c>
-      <c r="H12" s="21">
-        <f>IF(OR(A12="",F12="",F12=0),"",C12/F12)</f>
-        <v/>
-      </c>
-      <c r="I12" s="21">
-        <f>IF(H12="","",H12+Painel!$B$19)</f>
-        <v/>
-      </c>
-      <c r="J12" s="21">
-        <f>IF(I12="","",IFERROR(I12/(1-Config!$B$7-Config!$B$8),""))</f>
-        <v/>
+      <c r="H12" s="22">
+        <f>IF(A12="","",IF(NOT(ISNUMBER(C12)),"falta o pró-labore",IF(OR(NOT(ISNUMBER(F12)),F12=0),"faltam as horas faturáveis",C12/F12)))</f>
+        <v/>
+      </c>
+      <c r="I12" s="22">
+        <f>IF(H12="","",IF(NOT(ISNUMBER(H12)),H12,IF(NOT(ISNUMBER(Painel!$B$19)),"cadastro incompleto",H12+Painel!$B$19)))</f>
+        <v/>
+      </c>
+      <c r="J12" s="22">
+        <f>IF(I12="","",IF(NOT(ISNUMBER(I12)),I12,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I12/(1-Config!$B$7-Config!$B$8))))</f>
+        <v/>
+      </c>
+      <c r="K12" s="39">
+        <f>IF(AND(A12&lt;&gt;"",OR(NOT(ISNUMBER(C12)),NOT(ISNUMBER(F12)))),1,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="n"/>
-      <c r="B13" s="31" t="n"/>
-      <c r="C13" s="34" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="37" t="n"/>
-      <c r="F13" s="37" t="n"/>
-      <c r="G13" s="27">
+      <c r="A13" s="32" t="n"/>
+      <c r="B13" s="32" t="n"/>
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="38" t="n"/>
+      <c r="F13" s="38" t="n"/>
+      <c r="G13" s="28">
         <f>IF(OR(A13="",E13="",E13=0),"",F13/E13)</f>
         <v/>
       </c>
-      <c r="H13" s="21">
-        <f>IF(OR(A13="",F13="",F13=0),"",C13/F13)</f>
-        <v/>
-      </c>
-      <c r="I13" s="21">
-        <f>IF(H13="","",H13+Painel!$B$19)</f>
-        <v/>
-      </c>
-      <c r="J13" s="21">
-        <f>IF(I13="","",IFERROR(I13/(1-Config!$B$7-Config!$B$8),""))</f>
-        <v/>
+      <c r="H13" s="22">
+        <f>IF(A13="","",IF(NOT(ISNUMBER(C13)),"falta o pró-labore",IF(OR(NOT(ISNUMBER(F13)),F13=0),"faltam as horas faturáveis",C13/F13)))</f>
+        <v/>
+      </c>
+      <c r="I13" s="22">
+        <f>IF(H13="","",IF(NOT(ISNUMBER(H13)),H13,IF(NOT(ISNUMBER(Painel!$B$19)),"cadastro incompleto",H13+Painel!$B$19)))</f>
+        <v/>
+      </c>
+      <c r="J13" s="22">
+        <f>IF(I13="","",IF(NOT(ISNUMBER(I13)),I13,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I13/(1-Config!$B$7-Config!$B$8))))</f>
+        <v/>
+      </c>
+      <c r="K13" s="39">
+        <f>IF(AND(A13&lt;&gt;"",OR(NOT(ISNUMBER(C13)),NOT(ISNUMBER(F13)))),1,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="n"/>
-      <c r="B14" s="31" t="n"/>
-      <c r="C14" s="34" t="n"/>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="37" t="n"/>
-      <c r="F14" s="37" t="n"/>
-      <c r="G14" s="27">
+      <c r="A14" s="32" t="n"/>
+      <c r="B14" s="32" t="n"/>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="37" t="n"/>
+      <c r="E14" s="38" t="n"/>
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="28">
         <f>IF(OR(A14="",E14="",E14=0),"",F14/E14)</f>
         <v/>
       </c>
-      <c r="H14" s="21">
-        <f>IF(OR(A14="",F14="",F14=0),"",C14/F14)</f>
-        <v/>
-      </c>
-      <c r="I14" s="21">
-        <f>IF(H14="","",H14+Painel!$B$19)</f>
-        <v/>
-      </c>
-      <c r="J14" s="21">
-        <f>IF(I14="","",IFERROR(I14/(1-Config!$B$7-Config!$B$8),""))</f>
-        <v/>
+      <c r="H14" s="22">
+        <f>IF(A14="","",IF(NOT(ISNUMBER(C14)),"falta o pró-labore",IF(OR(NOT(ISNUMBER(F14)),F14=0),"faltam as horas faturáveis",C14/F14)))</f>
+        <v/>
+      </c>
+      <c r="I14" s="22">
+        <f>IF(H14="","",IF(NOT(ISNUMBER(H14)),H14,IF(NOT(ISNUMBER(Painel!$B$19)),"cadastro incompleto",H14+Painel!$B$19)))</f>
+        <v/>
+      </c>
+      <c r="J14" s="22">
+        <f>IF(I14="","",IF(NOT(ISNUMBER(I14)),I14,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I14/(1-Config!$B$7-Config!$B$8))))</f>
+        <v/>
+      </c>
+      <c r="K14" s="39">
+        <f>IF(AND(A14&lt;&gt;"",OR(NOT(ISNUMBER(C14)),NOT(ISNUMBER(F14)))),1,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="inlineStr">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>Custo direto por hora = pró-labore ou salário ÷ horas faturáveis. Custo-hora completo = custo direto + rateio dos custos indiretos do escritório por hora faturável (o rateio é calculado no Painel). Hora mínima = custo-hora completo ÷ (1 − margem − impostos).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="28" t="inlineStr">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>Horas de trabalho no mês: 160 para tempo integral; 120 para meio período. Horas faturáveis: uma média realista; 60% a 70% das horas de trabalho já é bom para quem também administra o escritório.</t>
         </is>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/05-custo-hora.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/05-custo-hora.xlsx
@@ -227,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -306,6 +306,9 @@
     <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1255,7 +1258,7 @@
         </is>
       </c>
       <c r="B16" s="22">
-        <f>IF(B13="","",IF(NOT(ISNUMBER(B13)),B13,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",B13/(1-Config!$B$7-Config!$B$8))))</f>
+        <f>IF(B13="","",IF(NOT(ISNUMBER(B13)),B13,IF(Config!$B$10&lt;&gt;"Sim","margens inválidas (Config)",B13/(1-Config!$B$7-Config!$B$8))))</f>
         <v>106.566820276498</v>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -1771,7 +1774,7 @@
         <v>66.0714285714286</v>
       </c>
       <c r="E41" s="22">
-        <f>IF(D41="","",IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",D41/(1-Config!$B$7-Config!$B$8)))</f>
+        <f>IF(D41="","",IF(Config!$B$10&lt;&gt;"Sim","margens inválidas (Config)",D41/(1-Config!$B$7-Config!$B$8)))</f>
         <v>106.566820276498</v>
       </c>
       <c r="F41" s="22">
@@ -1796,7 +1799,7 @@
         <v>73.4126984126984</v>
       </c>
       <c r="E42" s="22">
-        <f>IF(D42="","",IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",D42/(1-Config!$B$7-Config!$B$8)))</f>
+        <f>IF(D42="","",IF(Config!$B$10&lt;&gt;"Sim","margens inválidas (Config)",D42/(1-Config!$B$7-Config!$B$8)))</f>
         <v>118.407578084997</v>
       </c>
       <c r="F42" s="22">
@@ -1821,7 +1824,7 @@
         <v>82.5892857142857</v>
       </c>
       <c r="E43" s="22">
-        <f>IF(D43="","",IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",D43/(1-Config!$B$7-Config!$B$8)))</f>
+        <f>IF(D43="","",IF(Config!$B$10&lt;&gt;"Sim","margens inválidas (Config)",D43/(1-Config!$B$7-Config!$B$8)))</f>
         <v>133.208525345622</v>
       </c>
       <c r="F43" s="22">
@@ -1846,7 +1849,7 @@
         <v>94.3877551020408</v>
       </c>
       <c r="E44" s="22">
-        <f>IF(D44="","",IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",D44/(1-Config!$B$7-Config!$B$8)))</f>
+        <f>IF(D44="","",IF(Config!$B$10&lt;&gt;"Sim","margens inválidas (Config)",D44/(1-Config!$B$7-Config!$B$8)))</f>
         <v>152.238314680711</v>
       </c>
       <c r="F44" s="22">
@@ -2001,6 +2004,22 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>Margem e impostos conferem? (calculado)</t>
+        </is>
+      </c>
+      <c r="B10" s="35" t="str">
+        <f>IF(AND(ISNUMBER(B7),ISNUMBER(B8)),IF(AND(B7&gt;=0,B7&lt;1,B8&gt;=0,B8&lt;1,B7+B8&lt;1),"Sim","Não"),"Não")</f>
+        <v>Sim</v>
+      </c>
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>"Não" suspende a hora mínima em todas as abas: cada percentual precisa ficar entre 0 % e 99 %, e margem + impostos abaixo de 100 %.</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" s="29" t="inlineStr">
         <is>
@@ -2084,7 +2103,7 @@
           <t>Aluguel e condomínio</t>
         </is>
       </c>
-      <c r="B5" s="35" t="n">
+      <c r="B5" s="36" t="n">
         <v>2800</v>
       </c>
       <c r="C5" s="32" t="n"/>
@@ -2095,7 +2114,7 @@
           <t>Contador</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n">
+      <c r="B6" s="36" t="n">
         <v>600</v>
       </c>
       <c r="C6" s="32" t="n"/>
@@ -2106,7 +2125,7 @@
           <t>Sistemas e assinaturas</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n">
+      <c r="B7" s="36" t="n">
         <v>450</v>
       </c>
       <c r="C7" s="32" t="n"/>
@@ -2117,7 +2136,7 @@
           <t>Telefone e internet</t>
         </is>
       </c>
-      <c r="B8" s="35" t="n">
+      <c r="B8" s="36" t="n">
         <v>220</v>
       </c>
       <c r="C8" s="32" t="n"/>
@@ -2128,7 +2147,7 @@
           <t>Anuidades OAB e cursos</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n">
+      <c r="B9" s="36" t="n">
         <v>250</v>
       </c>
       <c r="C9" s="32" t="n"/>
@@ -2139,7 +2158,7 @@
           <t>Marketing e site</t>
         </is>
       </c>
-      <c r="B10" s="35" t="n">
+      <c r="B10" s="36" t="n">
         <v>400</v>
       </c>
       <c r="C10" s="32" t="n"/>
@@ -2150,7 +2169,7 @@
           <t>Estagiária (bolsa)</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n">
+      <c r="B11" s="36" t="n">
         <v>1400</v>
       </c>
       <c r="C11" s="32" t="inlineStr">
@@ -2165,123 +2184,123 @@
           <t>Material, correio e outros</t>
         </is>
       </c>
-      <c r="B12" s="35" t="n">
+      <c r="B12" s="36" t="n">
         <v>380</v>
       </c>
       <c r="C12" s="32" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="32" t="n"/>
-      <c r="B13" s="35" t="n"/>
+      <c r="B13" s="36" t="n"/>
       <c r="C13" s="32" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="32" t="n"/>
-      <c r="B14" s="35" t="n"/>
+      <c r="B14" s="36" t="n"/>
       <c r="C14" s="32" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="32" t="n"/>
-      <c r="B15" s="35" t="n"/>
+      <c r="B15" s="36" t="n"/>
       <c r="C15" s="32" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="32" t="n"/>
-      <c r="B16" s="35" t="n"/>
+      <c r="B16" s="36" t="n"/>
       <c r="C16" s="32" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="32" t="n"/>
-      <c r="B17" s="35" t="n"/>
+      <c r="B17" s="36" t="n"/>
       <c r="C17" s="32" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="32" t="n"/>
-      <c r="B18" s="35" t="n"/>
+      <c r="B18" s="36" t="n"/>
       <c r="C18" s="32" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="32" t="n"/>
-      <c r="B19" s="35" t="n"/>
+      <c r="B19" s="36" t="n"/>
       <c r="C19" s="32" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="32" t="n"/>
-      <c r="B20" s="35" t="n"/>
+      <c r="B20" s="36" t="n"/>
       <c r="C20" s="32" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="32" t="n"/>
-      <c r="B21" s="35" t="n"/>
+      <c r="B21" s="36" t="n"/>
       <c r="C21" s="32" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="32" t="n"/>
-      <c r="B22" s="35" t="n"/>
+      <c r="B22" s="36" t="n"/>
       <c r="C22" s="32" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="32" t="n"/>
-      <c r="B23" s="35" t="n"/>
+      <c r="B23" s="36" t="n"/>
       <c r="C23" s="32" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="32" t="n"/>
-      <c r="B24" s="35" t="n"/>
+      <c r="B24" s="36" t="n"/>
       <c r="C24" s="32" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="32" t="n"/>
-      <c r="B25" s="35" t="n"/>
+      <c r="B25" s="36" t="n"/>
       <c r="C25" s="32" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="32" t="n"/>
-      <c r="B26" s="35" t="n"/>
+      <c r="B26" s="36" t="n"/>
       <c r="C26" s="32" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="32" t="n"/>
-      <c r="B27" s="35" t="n"/>
+      <c r="B27" s="36" t="n"/>
       <c r="C27" s="32" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="32" t="n"/>
-      <c r="B28" s="35" t="n"/>
+      <c r="B28" s="36" t="n"/>
       <c r="C28" s="32" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="32" t="n"/>
-      <c r="B29" s="35" t="n"/>
+      <c r="B29" s="36" t="n"/>
       <c r="C29" s="32" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="32" t="n"/>
-      <c r="B30" s="35" t="n"/>
+      <c r="B30" s="36" t="n"/>
       <c r="C30" s="32" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="32" t="n"/>
-      <c r="B31" s="35" t="n"/>
+      <c r="B31" s="36" t="n"/>
       <c r="C31" s="32" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="32" t="n"/>
-      <c r="B32" s="35" t="n"/>
+      <c r="B32" s="36" t="n"/>
       <c r="C32" s="32" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="32" t="n"/>
-      <c r="B33" s="35" t="n"/>
+      <c r="B33" s="36" t="n"/>
       <c r="C33" s="32" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="32" t="n"/>
-      <c r="B34" s="35" t="n"/>
+      <c r="B34" s="36" t="n"/>
       <c r="C34" s="32" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="36" t="inlineStr">
+      <c r="A36" s="37" t="inlineStr">
         <is>
           <t>Total de custos fixos</t>
         </is>
@@ -2407,18 +2426,18 @@
           <t>Sócia · cível e empresarial</t>
         </is>
       </c>
-      <c r="C5" s="35" t="n">
+      <c r="C5" s="36" t="n">
         <v>6000</v>
       </c>
-      <c r="D5" s="37" t="inlineStr">
+      <c r="D5" s="38" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="E5" s="38" t="n">
+      <c r="E5" s="39" t="n">
         <v>160</v>
       </c>
-      <c r="F5" s="38" t="n">
+      <c r="F5" s="39" t="n">
         <v>110</v>
       </c>
       <c r="G5" s="28">
@@ -2434,10 +2453,10 @@
         <v>72.7597402597403</v>
       </c>
       <c r="J5" s="22">
-        <f>IF(I5="","",IF(NOT(ISNUMBER(I5)),I5,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I5/(1-Config!$B$7-Config!$B$8))))</f>
+        <f>IF(I5="","",IF(NOT(ISNUMBER(I5)),I5,IF(Config!$B$10&lt;&gt;"Sim","margens inválidas (Config)",I5/(1-Config!$B$7-Config!$B$8))))</f>
         <v>117.354419773775</v>
       </c>
-      <c r="K5" s="39">
+      <c r="K5" s="40">
         <f>IF(AND(A5&lt;&gt;"",OR(NOT(ISNUMBER(C5)),NOT(ISNUMBER(F5)))),1,0)</f>
         <v>0</v>
       </c>
@@ -2453,18 +2472,18 @@
           <t>Sócio · trabalhista e previdenciário</t>
         </is>
       </c>
-      <c r="C6" s="35" t="n">
+      <c r="C6" s="36" t="n">
         <v>6000</v>
       </c>
-      <c r="D6" s="37" t="inlineStr">
+      <c r="D6" s="38" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="E6" s="38" t="n">
+      <c r="E6" s="39" t="n">
         <v>160</v>
       </c>
-      <c r="F6" s="38" t="n">
+      <c r="F6" s="39" t="n">
         <v>110</v>
       </c>
       <c r="G6" s="28">
@@ -2480,10 +2499,10 @@
         <v>72.7597402597403</v>
       </c>
       <c r="J6" s="22">
-        <f>IF(I6="","",IF(NOT(ISNUMBER(I6)),I6,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I6/(1-Config!$B$7-Config!$B$8))))</f>
+        <f>IF(I6="","",IF(NOT(ISNUMBER(I6)),I6,IF(Config!$B$10&lt;&gt;"Sim","margens inválidas (Config)",I6/(1-Config!$B$7-Config!$B$8))))</f>
         <v>117.354419773775</v>
       </c>
-      <c r="K6" s="39">
+      <c r="K6" s="40">
         <f>IF(AND(A6&lt;&gt;"",OR(NOT(ISNUMBER(C6)),NOT(ISNUMBER(F6)))),1,0)</f>
         <v>0</v>
       </c>
@@ -2499,18 +2518,18 @@
           <t>Estagiária</t>
         </is>
       </c>
-      <c r="C7" s="35" t="n">
+      <c r="C7" s="36" t="n">
         <v>1400</v>
       </c>
-      <c r="D7" s="37" t="inlineStr">
+      <c r="D7" s="38" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="E7" s="38" t="n">
+      <c r="E7" s="39" t="n">
         <v>120</v>
       </c>
-      <c r="F7" s="38" t="n">
+      <c r="F7" s="39" t="n">
         <v>60</v>
       </c>
       <c r="G7" s="28">
@@ -2526,10 +2545,10 @@
         <v>41.5476190476191</v>
       </c>
       <c r="J7" s="22">
-        <f>IF(I7="","",IF(NOT(ISNUMBER(I7)),I7,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I7/(1-Config!$B$7-Config!$B$8))))</f>
+        <f>IF(I7="","",IF(NOT(ISNUMBER(I7)),I7,IF(Config!$B$10&lt;&gt;"Sim","margens inválidas (Config)",I7/(1-Config!$B$7-Config!$B$8))))</f>
         <v>67.0122887864823</v>
       </c>
-      <c r="K7" s="39">
+      <c r="K7" s="40">
         <f>IF(AND(A7&lt;&gt;"",OR(NOT(ISNUMBER(C7)),NOT(ISNUMBER(F7)))),1,0)</f>
         <v>0</v>
       </c>
@@ -2537,10 +2556,10 @@
     <row r="8">
       <c r="A8" s="32" t="n"/>
       <c r="B8" s="32" t="n"/>
-      <c r="C8" s="35" t="n"/>
-      <c r="D8" s="37" t="n"/>
-      <c r="E8" s="38" t="n"/>
-      <c r="F8" s="38" t="n"/>
+      <c r="C8" s="36" t="n"/>
+      <c r="D8" s="38" t="n"/>
+      <c r="E8" s="39" t="n"/>
+      <c r="F8" s="39" t="n"/>
       <c r="G8" s="28">
         <f>IF(OR(A8="",E8="",E8=0),"",F8/E8)</f>
         <v/>
@@ -2554,10 +2573,10 @@
         <v/>
       </c>
       <c r="J8" s="22">
-        <f>IF(I8="","",IF(NOT(ISNUMBER(I8)),I8,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I8/(1-Config!$B$7-Config!$B$8))))</f>
-        <v/>
-      </c>
-      <c r="K8" s="39">
+        <f>IF(I8="","",IF(NOT(ISNUMBER(I8)),I8,IF(Config!$B$10&lt;&gt;"Sim","margens inválidas (Config)",I8/(1-Config!$B$7-Config!$B$8))))</f>
+        <v/>
+      </c>
+      <c r="K8" s="40">
         <f>IF(AND(A8&lt;&gt;"",OR(NOT(ISNUMBER(C8)),NOT(ISNUMBER(F8)))),1,0)</f>
         <v>0</v>
       </c>
@@ -2565,10 +2584,10 @@
     <row r="9">
       <c r="A9" s="32" t="n"/>
       <c r="B9" s="32" t="n"/>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="37" t="n"/>
-      <c r="E9" s="38" t="n"/>
-      <c r="F9" s="38" t="n"/>
+      <c r="C9" s="36" t="n"/>
+      <c r="D9" s="38" t="n"/>
+      <c r="E9" s="39" t="n"/>
+      <c r="F9" s="39" t="n"/>
       <c r="G9" s="28">
         <f>IF(OR(A9="",E9="",E9=0),"",F9/E9)</f>
         <v/>
@@ -2582,10 +2601,10 @@
         <v/>
       </c>
       <c r="J9" s="22">
-        <f>IF(I9="","",IF(NOT(ISNUMBER(I9)),I9,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I9/(1-Config!$B$7-Config!$B$8))))</f>
-        <v/>
-      </c>
-      <c r="K9" s="39">
+        <f>IF(I9="","",IF(NOT(ISNUMBER(I9)),I9,IF(Config!$B$10&lt;&gt;"Sim","margens inválidas (Config)",I9/(1-Config!$B$7-Config!$B$8))))</f>
+        <v/>
+      </c>
+      <c r="K9" s="40">
         <f>IF(AND(A9&lt;&gt;"",OR(NOT(ISNUMBER(C9)),NOT(ISNUMBER(F9)))),1,0)</f>
         <v>0</v>
       </c>
@@ -2593,10 +2612,10 @@
     <row r="10">
       <c r="A10" s="32" t="n"/>
       <c r="B10" s="32" t="n"/>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="37" t="n"/>
-      <c r="E10" s="38" t="n"/>
-      <c r="F10" s="38" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="38" t="n"/>
+      <c r="E10" s="39" t="n"/>
+      <c r="F10" s="39" t="n"/>
       <c r="G10" s="28">
         <f>IF(OR(A10="",E10="",E10=0),"",F10/E10)</f>
         <v/>
@@ -2610,10 +2629,10 @@
         <v/>
       </c>
       <c r="J10" s="22">
-        <f>IF(I10="","",IF(NOT(ISNUMBER(I10)),I10,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I10/(1-Config!$B$7-Config!$B$8))))</f>
-        <v/>
-      </c>
-      <c r="K10" s="39">
+        <f>IF(I10="","",IF(NOT(ISNUMBER(I10)),I10,IF(Config!$B$10&lt;&gt;"Sim","margens inválidas (Config)",I10/(1-Config!$B$7-Config!$B$8))))</f>
+        <v/>
+      </c>
+      <c r="K10" s="40">
         <f>IF(AND(A10&lt;&gt;"",OR(NOT(ISNUMBER(C10)),NOT(ISNUMBER(F10)))),1,0)</f>
         <v>0</v>
       </c>
@@ -2621,10 +2640,10 @@
     <row r="11">
       <c r="A11" s="32" t="n"/>
       <c r="B11" s="32" t="n"/>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="37" t="n"/>
-      <c r="E11" s="38" t="n"/>
-      <c r="F11" s="38" t="n"/>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="38" t="n"/>
+      <c r="E11" s="39" t="n"/>
+      <c r="F11" s="39" t="n"/>
       <c r="G11" s="28">
         <f>IF(OR(A11="",E11="",E11=0),"",F11/E11)</f>
         <v/>
@@ -2638,10 +2657,10 @@
         <v/>
       </c>
       <c r="J11" s="22">
-        <f>IF(I11="","",IF(NOT(ISNUMBER(I11)),I11,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I11/(1-Config!$B$7-Config!$B$8))))</f>
-        <v/>
-      </c>
-      <c r="K11" s="39">
+        <f>IF(I11="","",IF(NOT(ISNUMBER(I11)),I11,IF(Config!$B$10&lt;&gt;"Sim","margens inválidas (Config)",I11/(1-Config!$B$7-Config!$B$8))))</f>
+        <v/>
+      </c>
+      <c r="K11" s="40">
         <f>IF(AND(A11&lt;&gt;"",OR(NOT(ISNUMBER(C11)),NOT(ISNUMBER(F11)))),1,0)</f>
         <v>0</v>
       </c>
@@ -2649,10 +2668,10 @@
     <row r="12">
       <c r="A12" s="32" t="n"/>
       <c r="B12" s="32" t="n"/>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="37" t="n"/>
-      <c r="E12" s="38" t="n"/>
-      <c r="F12" s="38" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="38" t="n"/>
+      <c r="E12" s="39" t="n"/>
+      <c r="F12" s="39" t="n"/>
       <c r="G12" s="28">
         <f>IF(OR(A12="",E12="",E12=0),"",F12/E12)</f>
         <v/>
@@ -2666,10 +2685,10 @@
         <v/>
       </c>
       <c r="J12" s="22">
-        <f>IF(I12="","",IF(NOT(ISNUMBER(I12)),I12,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I12/(1-Config!$B$7-Config!$B$8))))</f>
-        <v/>
-      </c>
-      <c r="K12" s="39">
+        <f>IF(I12="","",IF(NOT(ISNUMBER(I12)),I12,IF(Config!$B$10&lt;&gt;"Sim","margens inválidas (Config)",I12/(1-Config!$B$7-Config!$B$8))))</f>
+        <v/>
+      </c>
+      <c r="K12" s="40">
         <f>IF(AND(A12&lt;&gt;"",OR(NOT(ISNUMBER(C12)),NOT(ISNUMBER(F12)))),1,0)</f>
         <v>0</v>
       </c>
@@ -2677,10 +2696,10 @@
     <row r="13">
       <c r="A13" s="32" t="n"/>
       <c r="B13" s="32" t="n"/>
-      <c r="C13" s="35" t="n"/>
-      <c r="D13" s="37" t="n"/>
-      <c r="E13" s="38" t="n"/>
-      <c r="F13" s="38" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="38" t="n"/>
+      <c r="E13" s="39" t="n"/>
+      <c r="F13" s="39" t="n"/>
       <c r="G13" s="28">
         <f>IF(OR(A13="",E13="",E13=0),"",F13/E13)</f>
         <v/>
@@ -2694,10 +2713,10 @@
         <v/>
       </c>
       <c r="J13" s="22">
-        <f>IF(I13="","",IF(NOT(ISNUMBER(I13)),I13,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I13/(1-Config!$B$7-Config!$B$8))))</f>
-        <v/>
-      </c>
-      <c r="K13" s="39">
+        <f>IF(I13="","",IF(NOT(ISNUMBER(I13)),I13,IF(Config!$B$10&lt;&gt;"Sim","margens inválidas (Config)",I13/(1-Config!$B$7-Config!$B$8))))</f>
+        <v/>
+      </c>
+      <c r="K13" s="40">
         <f>IF(AND(A13&lt;&gt;"",OR(NOT(ISNUMBER(C13)),NOT(ISNUMBER(F13)))),1,0)</f>
         <v>0</v>
       </c>
@@ -2705,10 +2724,10 @@
     <row r="14">
       <c r="A14" s="32" t="n"/>
       <c r="B14" s="32" t="n"/>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="37" t="n"/>
-      <c r="E14" s="38" t="n"/>
-      <c r="F14" s="38" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="38" t="n"/>
+      <c r="E14" s="39" t="n"/>
+      <c r="F14" s="39" t="n"/>
       <c r="G14" s="28">
         <f>IF(OR(A14="",E14="",E14=0),"",F14/E14)</f>
         <v/>
@@ -2722,10 +2741,10 @@
         <v/>
       </c>
       <c r="J14" s="22">
-        <f>IF(I14="","",IF(NOT(ISNUMBER(I14)),I14,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I14/(1-Config!$B$7-Config!$B$8))))</f>
-        <v/>
-      </c>
-      <c r="K14" s="39">
+        <f>IF(I14="","",IF(NOT(ISNUMBER(I14)),I14,IF(Config!$B$10&lt;&gt;"Sim","margens inválidas (Config)",I14/(1-Config!$B$7-Config!$B$8))))</f>
+        <v/>
+      </c>
+      <c r="K14" s="40">
         <f>IF(AND(A14&lt;&gt;"",OR(NOT(ISNUMBER(C14)),NOT(ISNUMBER(F14)))),1,0)</f>
         <v>0</v>
       </c>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/05-custo-hora.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/05-custo-hora.xlsx
@@ -2042,10 +2042,10 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Margem entre 0 % e 99 %, e margem + impostos abaixo de 100 %: senão nenhum preço cobre o custo." type="custom">
-      <formula1>=AND(ISNUMBER(B7),B7&gt;=0,B7&lt;1,B7+N(B8)&lt;1)</formula1>
+      <formula1>=IF(ISNUMBER(B7),AND(B7&gt;=0,B7&lt;1,B7+N(B8)&lt;1),FALSE)</formula1>
     </dataValidation>
     <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Impostos entre 0 % e 99 %, e margem + impostos abaixo de 100 %: senão nenhum preço cobre o custo." type="custom">
-      <formula1>=AND(ISNUMBER(B8),B8&gt;=0,B8&lt;1,B8+N(B7)&lt;1)</formula1>
+      <formula1>=IF(ISNUMBER(B8),AND(B8&gt;=0,B8&lt;1,B8+N(B7)&lt;1),FALSE)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/05-custo-hora.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/05-custo-hora.xlsx
@@ -1097,7 +1097,7 @@
     </row>
     <row r="6">
       <c r="A6" s="18">
-        <f>IF(SUM(Pessoas!$K$5:$K$14)=0,"","Atenção: "&amp;SUM(Pessoas!$K$5:$K$14)&amp;" pessoa(s) na aba Pessoas sem pró-labore ou sem horas faturáveis. O custo do mês, o custo-hora e a hora mínima ficam como 'cadastro incompleto' até você completar: uma soma parcial daria um custo-hora MENOR do que o real.")</f>
+        <f>IF((SUM(Pessoas!$K$5:$K$14)+IF(ISNUMBER('Custos fixos'!$B$36),0,1))=0,"",IF(IF(ISNUMBER('Custos fixos'!$B$36),0,1)&gt;0,"Atenção: há custo fixo sem valor numérico na aba Custos fixos. ","")&amp;IF(SUM(Pessoas!$K$5:$K$14)&gt;0,"Atenção: "&amp;SUM(Pessoas!$K$5:$K$14)&amp;" pessoa(s) na aba Pessoas com pró-labore, horas faturáveis ou 'já está nos custos fixos?' em branco. ","")&amp;"Custo do mês, custo-hora e hora mínima ficam como 'cadastro incompleto' até você completar: uma soma parcial daria um custo-hora MENOR do que o real.")</f>
         <v/>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="B10" s="22">
-        <f>IF(SUM(Pessoas!$K$5:$K$14)&gt;0,"cadastro incompleto",SUMIFS(Pessoas!$C$5:$C$14,Pessoas!$D$5:$D$14,"Não"))</f>
+        <f>IF((SUM(Pessoas!$K$5:$K$14)+IF(ISNUMBER('Custos fixos'!$B$36),0,1))&gt;0,"cadastro incompleto",SUMIFS(Pessoas!$C$5:$C$14,Pessoas!$D$5:$D$14,"Não"))</f>
         <v>12000</v>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="B11" s="26">
-        <f>IF(SUM(Pessoas!$K$5:$K$14)&gt;0,"cadastro incompleto",B9+B10)</f>
+        <f>IF((SUM(Pessoas!$K$5:$K$14)+IF(ISNUMBER('Custos fixos'!$B$36),0,1))&gt;0,"cadastro incompleto",B9+B10)</f>
         <v>18500</v>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="B12" s="27">
-        <f>IF(SUM(Pessoas!$K$5:$K$14)&gt;0,"cadastro incompleto",SUM(Pessoas!$F$5:$F$14))</f>
+        <f>IF((SUM(Pessoas!$K$5:$K$14)+IF(ISNUMBER('Custos fixos'!$B$36),0,1))&gt;0,"cadastro incompleto",SUM(Pessoas!$F$5:$F$14))</f>
         <v>280</v>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="B13" s="26">
-        <f>IF(SUM(Pessoas!$K$5:$K$14)&gt;0,"cadastro incompleto",IF(B12=0,"",B11/B12))</f>
+        <f>IF((SUM(Pessoas!$K$5:$K$14)+IF(ISNUMBER('Custos fixos'!$B$36),0,1))&gt;0,"cadastro incompleto",IF(B12=0,"",B11/B12))</f>
         <v>66.0714285714286</v>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="B18" s="22">
-        <f>IF(SUM(Pessoas!$K$5:$K$14)&gt;0,"cadastro incompleto",B9-SUMIFS(Pessoas!$C$5:$C$14,Pessoas!$D$5:$D$14,"Sim"))</f>
+        <f>IF((SUM(Pessoas!$K$5:$K$14)+IF(ISNUMBER('Custos fixos'!$B$36),0,1))&gt;0,"cadastro incompleto",B9-SUMIFS(Pessoas!$C$5:$C$14,Pessoas!$D$5:$D$14,"Sim"))</f>
         <v>5100</v>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="B19" s="22">
-        <f>IF(SUM(Pessoas!$K$5:$K$14)&gt;0,"cadastro incompleto",IF(B12=0,0,B18/B12))</f>
+        <f>IF((SUM(Pessoas!$K$5:$K$14)+IF(ISNUMBER('Custos fixos'!$B$36),0,1))&gt;0,"cadastro incompleto",IF(B12=0,0,B18/B12))</f>
         <v>18.2142857142857</v>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="B20" s="27">
-        <f>SUM(Pessoas!$E$5:$E$14)</f>
+        <f>IF(SUMPRODUCT((Pessoas!$A$5:$A$14&lt;&gt;"")*(ISNUMBER(Pessoas!$E$5:$E$14)=FALSE))&gt;0,"faltam horas de trabalho",SUM(Pessoas!$E$5:$E$14))</f>
         <v>440</v>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="B21" s="28">
-        <f>IF(OR(B20=0,NOT(ISNUMBER(B12))),"",B12/B20)</f>
+        <f>IF(OR(NOT(ISNUMBER(B20)),N(B20)=0,NOT(ISNUMBER(B12))),"",B12/B20)</f>
         <v>0.636363636363636</v>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="B36" s="26">
-        <f>SUM(B5:B34)</f>
+        <f>IF(SUMPRODUCT(((A5:A34&lt;&gt;"")+(B5:B34&lt;&gt;"")&gt;0)*(ISNUMBER(B5:B34)=FALSE))&gt;0,"custo fixo sem valor numérico",SUM(B5:B34))</f>
         <v>6500</v>
       </c>
     </row>
@@ -2441,11 +2441,11 @@
         <v>110</v>
       </c>
       <c r="G5" s="28">
-        <f>IF(OR(A5="",E5="",E5=0),"",F5/E5)</f>
+        <f>IF(OR(A5="",NOT(ISNUMBER(E5)),N(E5)=0,NOT(ISNUMBER(F5))),"",F5/E5)</f>
         <v>0.6875</v>
       </c>
       <c r="H5" s="22">
-        <f>IF(A5="","",IF(NOT(ISNUMBER(C5)),"falta o pró-labore",IF(OR(NOT(ISNUMBER(F5)),F5=0),"faltam as horas faturáveis",C5/F5)))</f>
+        <f>IF(A5="","",IF(NOT(ISNUMBER(C5)),"falta o pró-labore",IF(AND(D5&lt;&gt;"Sim",D5&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F5)),F5=0),"faltam as horas faturáveis",C5/F5))))</f>
         <v>54.5454545454546</v>
       </c>
       <c r="I5" s="22">
@@ -2457,7 +2457,7 @@
         <v>117.354419773775</v>
       </c>
       <c r="K5" s="40">
-        <f>IF(AND(A5&lt;&gt;"",OR(NOT(ISNUMBER(C5)),NOT(ISNUMBER(F5)))),1,0)</f>
+        <f>IF(AND(A5&lt;&gt;"",OR(NOT(ISNUMBER(C5)),NOT(ISNUMBER(F5)),AND(D5&lt;&gt;"Sim",D5&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2487,11 +2487,11 @@
         <v>110</v>
       </c>
       <c r="G6" s="28">
-        <f>IF(OR(A6="",E6="",E6=0),"",F6/E6)</f>
+        <f>IF(OR(A6="",NOT(ISNUMBER(E6)),N(E6)=0,NOT(ISNUMBER(F6))),"",F6/E6)</f>
         <v>0.6875</v>
       </c>
       <c r="H6" s="22">
-        <f>IF(A6="","",IF(NOT(ISNUMBER(C6)),"falta o pró-labore",IF(OR(NOT(ISNUMBER(F6)),F6=0),"faltam as horas faturáveis",C6/F6)))</f>
+        <f>IF(A6="","",IF(NOT(ISNUMBER(C6)),"falta o pró-labore",IF(AND(D6&lt;&gt;"Sim",D6&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F6)),F6=0),"faltam as horas faturáveis",C6/F6))))</f>
         <v>54.5454545454546</v>
       </c>
       <c r="I6" s="22">
@@ -2503,7 +2503,7 @@
         <v>117.354419773775</v>
       </c>
       <c r="K6" s="40">
-        <f>IF(AND(A6&lt;&gt;"",OR(NOT(ISNUMBER(C6)),NOT(ISNUMBER(F6)))),1,0)</f>
+        <f>IF(AND(A6&lt;&gt;"",OR(NOT(ISNUMBER(C6)),NOT(ISNUMBER(F6)),AND(D6&lt;&gt;"Sim",D6&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2533,11 +2533,11 @@
         <v>60</v>
       </c>
       <c r="G7" s="28">
-        <f>IF(OR(A7="",E7="",E7=0),"",F7/E7)</f>
+        <f>IF(OR(A7="",NOT(ISNUMBER(E7)),N(E7)=0,NOT(ISNUMBER(F7))),"",F7/E7)</f>
         <v>0.5</v>
       </c>
       <c r="H7" s="22">
-        <f>IF(A7="","",IF(NOT(ISNUMBER(C7)),"falta o pró-labore",IF(OR(NOT(ISNUMBER(F7)),F7=0),"faltam as horas faturáveis",C7/F7)))</f>
+        <f>IF(A7="","",IF(NOT(ISNUMBER(C7)),"falta o pró-labore",IF(AND(D7&lt;&gt;"Sim",D7&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F7)),F7=0),"faltam as horas faturáveis",C7/F7))))</f>
         <v>23.3333333333333</v>
       </c>
       <c r="I7" s="22">
@@ -2549,7 +2549,7 @@
         <v>67.0122887864823</v>
       </c>
       <c r="K7" s="40">
-        <f>IF(AND(A7&lt;&gt;"",OR(NOT(ISNUMBER(C7)),NOT(ISNUMBER(F7)))),1,0)</f>
+        <f>IF(AND(A7&lt;&gt;"",OR(NOT(ISNUMBER(C7)),NOT(ISNUMBER(F7)),AND(D7&lt;&gt;"Sim",D7&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2561,11 +2561,11 @@
       <c r="E8" s="39" t="n"/>
       <c r="F8" s="39" t="n"/>
       <c r="G8" s="28">
-        <f>IF(OR(A8="",E8="",E8=0),"",F8/E8)</f>
+        <f>IF(OR(A8="",NOT(ISNUMBER(E8)),N(E8)=0,NOT(ISNUMBER(F8))),"",F8/E8)</f>
         <v/>
       </c>
       <c r="H8" s="22">
-        <f>IF(A8="","",IF(NOT(ISNUMBER(C8)),"falta o pró-labore",IF(OR(NOT(ISNUMBER(F8)),F8=0),"faltam as horas faturáveis",C8/F8)))</f>
+        <f>IF(A8="","",IF(NOT(ISNUMBER(C8)),"falta o pró-labore",IF(AND(D8&lt;&gt;"Sim",D8&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F8)),F8=0),"faltam as horas faturáveis",C8/F8))))</f>
         <v/>
       </c>
       <c r="I8" s="22">
@@ -2577,7 +2577,7 @@
         <v/>
       </c>
       <c r="K8" s="40">
-        <f>IF(AND(A8&lt;&gt;"",OR(NOT(ISNUMBER(C8)),NOT(ISNUMBER(F8)))),1,0)</f>
+        <f>IF(AND(A8&lt;&gt;"",OR(NOT(ISNUMBER(C8)),NOT(ISNUMBER(F8)),AND(D8&lt;&gt;"Sim",D8&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2589,11 +2589,11 @@
       <c r="E9" s="39" t="n"/>
       <c r="F9" s="39" t="n"/>
       <c r="G9" s="28">
-        <f>IF(OR(A9="",E9="",E9=0),"",F9/E9)</f>
+        <f>IF(OR(A9="",NOT(ISNUMBER(E9)),N(E9)=0,NOT(ISNUMBER(F9))),"",F9/E9)</f>
         <v/>
       </c>
       <c r="H9" s="22">
-        <f>IF(A9="","",IF(NOT(ISNUMBER(C9)),"falta o pró-labore",IF(OR(NOT(ISNUMBER(F9)),F9=0),"faltam as horas faturáveis",C9/F9)))</f>
+        <f>IF(A9="","",IF(NOT(ISNUMBER(C9)),"falta o pró-labore",IF(AND(D9&lt;&gt;"Sim",D9&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F9)),F9=0),"faltam as horas faturáveis",C9/F9))))</f>
         <v/>
       </c>
       <c r="I9" s="22">
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="K9" s="40">
-        <f>IF(AND(A9&lt;&gt;"",OR(NOT(ISNUMBER(C9)),NOT(ISNUMBER(F9)))),1,0)</f>
+        <f>IF(AND(A9&lt;&gt;"",OR(NOT(ISNUMBER(C9)),NOT(ISNUMBER(F9)),AND(D9&lt;&gt;"Sim",D9&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2617,11 +2617,11 @@
       <c r="E10" s="39" t="n"/>
       <c r="F10" s="39" t="n"/>
       <c r="G10" s="28">
-        <f>IF(OR(A10="",E10="",E10=0),"",F10/E10)</f>
+        <f>IF(OR(A10="",NOT(ISNUMBER(E10)),N(E10)=0,NOT(ISNUMBER(F10))),"",F10/E10)</f>
         <v/>
       </c>
       <c r="H10" s="22">
-        <f>IF(A10="","",IF(NOT(ISNUMBER(C10)),"falta o pró-labore",IF(OR(NOT(ISNUMBER(F10)),F10=0),"faltam as horas faturáveis",C10/F10)))</f>
+        <f>IF(A10="","",IF(NOT(ISNUMBER(C10)),"falta o pró-labore",IF(AND(D10&lt;&gt;"Sim",D10&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F10)),F10=0),"faltam as horas faturáveis",C10/F10))))</f>
         <v/>
       </c>
       <c r="I10" s="22">
@@ -2633,7 +2633,7 @@
         <v/>
       </c>
       <c r="K10" s="40">
-        <f>IF(AND(A10&lt;&gt;"",OR(NOT(ISNUMBER(C10)),NOT(ISNUMBER(F10)))),1,0)</f>
+        <f>IF(AND(A10&lt;&gt;"",OR(NOT(ISNUMBER(C10)),NOT(ISNUMBER(F10)),AND(D10&lt;&gt;"Sim",D10&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2645,11 +2645,11 @@
       <c r="E11" s="39" t="n"/>
       <c r="F11" s="39" t="n"/>
       <c r="G11" s="28">
-        <f>IF(OR(A11="",E11="",E11=0),"",F11/E11)</f>
+        <f>IF(OR(A11="",NOT(ISNUMBER(E11)),N(E11)=0,NOT(ISNUMBER(F11))),"",F11/E11)</f>
         <v/>
       </c>
       <c r="H11" s="22">
-        <f>IF(A11="","",IF(NOT(ISNUMBER(C11)),"falta o pró-labore",IF(OR(NOT(ISNUMBER(F11)),F11=0),"faltam as horas faturáveis",C11/F11)))</f>
+        <f>IF(A11="","",IF(NOT(ISNUMBER(C11)),"falta o pró-labore",IF(AND(D11&lt;&gt;"Sim",D11&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F11)),F11=0),"faltam as horas faturáveis",C11/F11))))</f>
         <v/>
       </c>
       <c r="I11" s="22">
@@ -2661,7 +2661,7 @@
         <v/>
       </c>
       <c r="K11" s="40">
-        <f>IF(AND(A11&lt;&gt;"",OR(NOT(ISNUMBER(C11)),NOT(ISNUMBER(F11)))),1,0)</f>
+        <f>IF(AND(A11&lt;&gt;"",OR(NOT(ISNUMBER(C11)),NOT(ISNUMBER(F11)),AND(D11&lt;&gt;"Sim",D11&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2673,11 +2673,11 @@
       <c r="E12" s="39" t="n"/>
       <c r="F12" s="39" t="n"/>
       <c r="G12" s="28">
-        <f>IF(OR(A12="",E12="",E12=0),"",F12/E12)</f>
+        <f>IF(OR(A12="",NOT(ISNUMBER(E12)),N(E12)=0,NOT(ISNUMBER(F12))),"",F12/E12)</f>
         <v/>
       </c>
       <c r="H12" s="22">
-        <f>IF(A12="","",IF(NOT(ISNUMBER(C12)),"falta o pró-labore",IF(OR(NOT(ISNUMBER(F12)),F12=0),"faltam as horas faturáveis",C12/F12)))</f>
+        <f>IF(A12="","",IF(NOT(ISNUMBER(C12)),"falta o pró-labore",IF(AND(D12&lt;&gt;"Sim",D12&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F12)),F12=0),"faltam as horas faturáveis",C12/F12))))</f>
         <v/>
       </c>
       <c r="I12" s="22">
@@ -2689,7 +2689,7 @@
         <v/>
       </c>
       <c r="K12" s="40">
-        <f>IF(AND(A12&lt;&gt;"",OR(NOT(ISNUMBER(C12)),NOT(ISNUMBER(F12)))),1,0)</f>
+        <f>IF(AND(A12&lt;&gt;"",OR(NOT(ISNUMBER(C12)),NOT(ISNUMBER(F12)),AND(D12&lt;&gt;"Sim",D12&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2701,11 +2701,11 @@
       <c r="E13" s="39" t="n"/>
       <c r="F13" s="39" t="n"/>
       <c r="G13" s="28">
-        <f>IF(OR(A13="",E13="",E13=0),"",F13/E13)</f>
+        <f>IF(OR(A13="",NOT(ISNUMBER(E13)),N(E13)=0,NOT(ISNUMBER(F13))),"",F13/E13)</f>
         <v/>
       </c>
       <c r="H13" s="22">
-        <f>IF(A13="","",IF(NOT(ISNUMBER(C13)),"falta o pró-labore",IF(OR(NOT(ISNUMBER(F13)),F13=0),"faltam as horas faturáveis",C13/F13)))</f>
+        <f>IF(A13="","",IF(NOT(ISNUMBER(C13)),"falta o pró-labore",IF(AND(D13&lt;&gt;"Sim",D13&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F13)),F13=0),"faltam as horas faturáveis",C13/F13))))</f>
         <v/>
       </c>
       <c r="I13" s="22">
@@ -2717,7 +2717,7 @@
         <v/>
       </c>
       <c r="K13" s="40">
-        <f>IF(AND(A13&lt;&gt;"",OR(NOT(ISNUMBER(C13)),NOT(ISNUMBER(F13)))),1,0)</f>
+        <f>IF(AND(A13&lt;&gt;"",OR(NOT(ISNUMBER(C13)),NOT(ISNUMBER(F13)),AND(D13&lt;&gt;"Sim",D13&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2729,11 +2729,11 @@
       <c r="E14" s="39" t="n"/>
       <c r="F14" s="39" t="n"/>
       <c r="G14" s="28">
-        <f>IF(OR(A14="",E14="",E14=0),"",F14/E14)</f>
+        <f>IF(OR(A14="",NOT(ISNUMBER(E14)),N(E14)=0,NOT(ISNUMBER(F14))),"",F14/E14)</f>
         <v/>
       </c>
       <c r="H14" s="22">
-        <f>IF(A14="","",IF(NOT(ISNUMBER(C14)),"falta o pró-labore",IF(OR(NOT(ISNUMBER(F14)),F14=0),"faltam as horas faturáveis",C14/F14)))</f>
+        <f>IF(A14="","",IF(NOT(ISNUMBER(C14)),"falta o pró-labore",IF(AND(D14&lt;&gt;"Sim",D14&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F14)),F14=0),"faltam as horas faturáveis",C14/F14))))</f>
         <v/>
       </c>
       <c r="I14" s="22">
@@ -2745,7 +2745,7 @@
         <v/>
       </c>
       <c r="K14" s="40">
-        <f>IF(AND(A14&lt;&gt;"",OR(NOT(ISNUMBER(C14)),NOT(ISNUMBER(F14)))),1,0)</f>
+        <f>IF(AND(A14&lt;&gt;"",OR(NOT(ISNUMBER(C14)),NOT(ISNUMBER(F14)),AND(D14&lt;&gt;"Sim",D14&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/05-custo-hora.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/05-custo-hora.xlsx
@@ -1097,7 +1097,7 @@
     </row>
     <row r="6">
       <c r="A6" s="18">
-        <f>IF((SUM(Pessoas!$K$5:$K$14)+IF(ISNUMBER('Custos fixos'!$B$36),0,1))=0,"",IF(IF(ISNUMBER('Custos fixos'!$B$36),0,1)&gt;0,"Atenção: há custo fixo sem valor numérico na aba Custos fixos. ","")&amp;IF(SUM(Pessoas!$K$5:$K$14)&gt;0,"Atenção: "&amp;SUM(Pessoas!$K$5:$K$14)&amp;" pessoa(s) na aba Pessoas com pró-labore, horas faturáveis ou 'já está nos custos fixos?' em branco. ","")&amp;"Custo do mês, custo-hora e hora mínima ficam como 'cadastro incompleto' até você completar: uma soma parcial daria um custo-hora MENOR do que o real.")</f>
+        <f>IF((SUM(Pessoas!$K$5:$K$14)+IF(ISNUMBER('Custos fixos'!$B$36),0,1))=0,"",IF(IF(ISNUMBER('Custos fixos'!$B$36),0,1)&gt;0,"Atenção: há custo fixo sem valor, com texto ou negativo na aba Custos fixos. ","")&amp;IF(SUM(Pessoas!$K$5:$K$14)&gt;0,"Atenção: "&amp;SUM(Pessoas!$K$5:$K$14)&amp;" pessoa(s) na aba Pessoas com pró-labore, horas faturáveis ou 'já está nos custos fixos?' em branco. ","")&amp;"Custo do mês, custo-hora e hora mínima ficam como 'cadastro incompleto' até você completar: uma soma parcial daria um custo-hora MENOR do que o real.")</f>
         <v/>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="B14" s="28">
-        <f>Config!$B$7</f>
+        <f>IF(ISNUMBER(Config!$B$7),Config!$B$7,"falta em Config")</f>
         <v>0.3</v>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="B15" s="28">
-        <f>Config!$B$8</f>
+        <f>IF(ISNUMBER(Config!$B$8),Config!$B$8,"falta em Config")</f>
         <v>0.08</v>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="B17" s="26">
-        <f>IF(B16="","",IF(NOT(ISNUMBER(B16)),B16,CEILING(B16,Config!$B$9)))</f>
+        <f>IF(B16="","",IF(NOT(ISNUMBER(B16)),B16,IF(NOT(IF(ISNUMBER(Config!$B$9),Config!$B$9&gt;0,FALSE)),"falta o múltiplo de arredondamento em Config",CEILING(B16,Config!$B$9))))</f>
         <v>110</v>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="B20" s="27">
-        <f>IF(SUMPRODUCT((Pessoas!$A$5:$A$14&lt;&gt;"")*(ISNUMBER(Pessoas!$E$5:$E$14)=FALSE))&gt;0,"faltam horas de trabalho",SUM(Pessoas!$E$5:$E$14))</f>
+        <f>IF(SUMPRODUCT((Pessoas!$A$5:$A$14&lt;&gt;"")*((ISNUMBER(Pessoas!$E$5:$E$14)=FALSE)+ISNUMBER(Pessoas!$E$5:$E$14)*(Pessoas!$E$5:$E$14&lt;0)&gt;0))&gt;0,"faltam horas de trabalho",SUM(Pessoas!$E$5:$E$14))</f>
         <v>440</v>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -1413,7 +1413,7 @@
         <v>Sócia · cível e empresarial</v>
       </c>
       <c r="C26" s="27">
-        <f>IF(Pessoas!$A$5="","",Pessoas!$F$5)</f>
+        <f>IF(OR(Pessoas!$A$5="",Pessoas!$F$5=""),"",Pessoas!$F$5)</f>
         <v>110</v>
       </c>
       <c r="D26" s="28">
@@ -1443,7 +1443,7 @@
         <v>Sócio · trabalhista e previdenciário</v>
       </c>
       <c r="C27" s="27">
-        <f>IF(Pessoas!$A$6="","",Pessoas!$F$6)</f>
+        <f>IF(OR(Pessoas!$A$6="",Pessoas!$F$6=""),"",Pessoas!$F$6)</f>
         <v>110</v>
       </c>
       <c r="D27" s="28">
@@ -1473,7 +1473,7 @@
         <v>Estagiária</v>
       </c>
       <c r="C28" s="27">
-        <f>IF(Pessoas!$A$7="","",Pessoas!$F$7)</f>
+        <f>IF(OR(Pessoas!$A$7="",Pessoas!$F$7=""),"",Pessoas!$F$7)</f>
         <v>60</v>
       </c>
       <c r="D28" s="28">
@@ -1503,7 +1503,7 @@
         <v/>
       </c>
       <c r="C29" s="27">
-        <f>IF(Pessoas!$A$8="","",Pessoas!$F$8)</f>
+        <f>IF(OR(Pessoas!$A$8="",Pessoas!$F$8=""),"",Pessoas!$F$8)</f>
         <v/>
       </c>
       <c r="D29" s="28">
@@ -1533,7 +1533,7 @@
         <v/>
       </c>
       <c r="C30" s="27">
-        <f>IF(Pessoas!$A$9="","",Pessoas!$F$9)</f>
+        <f>IF(OR(Pessoas!$A$9="",Pessoas!$F$9=""),"",Pessoas!$F$9)</f>
         <v/>
       </c>
       <c r="D30" s="28">
@@ -1563,7 +1563,7 @@
         <v/>
       </c>
       <c r="C31" s="27">
-        <f>IF(Pessoas!$A$10="","",Pessoas!$F$10)</f>
+        <f>IF(OR(Pessoas!$A$10="",Pessoas!$F$10=""),"",Pessoas!$F$10)</f>
         <v/>
       </c>
       <c r="D31" s="28">
@@ -1593,7 +1593,7 @@
         <v/>
       </c>
       <c r="C32" s="27">
-        <f>IF(Pessoas!$A$11="","",Pessoas!$F$11)</f>
+        <f>IF(OR(Pessoas!$A$11="",Pessoas!$F$11=""),"",Pessoas!$F$11)</f>
         <v/>
       </c>
       <c r="D32" s="28">
@@ -1623,7 +1623,7 @@
         <v/>
       </c>
       <c r="C33" s="27">
-        <f>IF(Pessoas!$A$12="","",Pessoas!$F$12)</f>
+        <f>IF(OR(Pessoas!$A$12="",Pessoas!$F$12=""),"",Pessoas!$F$12)</f>
         <v/>
       </c>
       <c r="D33" s="28">
@@ -1653,7 +1653,7 @@
         <v/>
       </c>
       <c r="C34" s="27">
-        <f>IF(Pessoas!$A$13="","",Pessoas!$F$13)</f>
+        <f>IF(OR(Pessoas!$A$13="",Pessoas!$F$13=""),"",Pessoas!$F$13)</f>
         <v/>
       </c>
       <c r="D34" s="28">
@@ -1683,7 +1683,7 @@
         <v/>
       </c>
       <c r="C35" s="27">
-        <f>IF(Pessoas!$A$14="","",Pessoas!$F$14)</f>
+        <f>IF(OR(Pessoas!$A$14="",Pessoas!$F$14=""),"",Pessoas!$F$14)</f>
         <v/>
       </c>
       <c r="D35" s="28">
@@ -1766,11 +1766,11 @@
         <v>0</v>
       </c>
       <c r="C41" s="27">
-        <f>IF(ISNUMBER($B$12),$B$12*(1-B41),"")</f>
+        <f>IF(AND(ISNUMBER($B$12),IF(ISNUMBER(B41),AND(B41&gt;=0,B41&lt;1),FALSE)),$B$12*(1-B41),"")</f>
         <v>280</v>
       </c>
       <c r="D41" s="22">
-        <f>IF(OR(C41="",C41=0,NOT(ISNUMBER($B$11))),"",$B$11/C41)</f>
+        <f>IF(OR(NOT(IF(ISNUMBER(C41),C41&gt;0,FALSE)),NOT(ISNUMBER($B$11))),"",$B$11/C41)</f>
         <v>66.0714285714286</v>
       </c>
       <c r="E41" s="22">
@@ -1784,18 +1784,18 @@
     </row>
     <row r="42">
       <c r="A42" s="21" t="str">
-        <f>"Queda de "&amp;ROUND(B42*100,0)&amp;"%"</f>
+        <f>IF(IF(ISNUMBER(B42),AND(B42&gt;=0,B42&lt;1),FALSE),"Queda de "&amp;ROUND(B42*100,0)&amp;"%","Percentual inválido (0 a 99 %)")</f>
         <v>Queda de 10%</v>
       </c>
       <c r="B42" s="30" t="n">
         <v>0.1</v>
       </c>
       <c r="C42" s="27">
-        <f>IF(ISNUMBER($B$12),$B$12*(1-B42),"")</f>
+        <f>IF(AND(ISNUMBER($B$12),IF(ISNUMBER(B42),AND(B42&gt;=0,B42&lt;1),FALSE)),$B$12*(1-B42),"")</f>
         <v>252</v>
       </c>
       <c r="D42" s="22">
-        <f>IF(OR(C42="",C42=0,NOT(ISNUMBER($B$11))),"",$B$11/C42)</f>
+        <f>IF(OR(NOT(IF(ISNUMBER(C42),C42&gt;0,FALSE)),NOT(ISNUMBER($B$11))),"",$B$11/C42)</f>
         <v>73.4126984126984</v>
       </c>
       <c r="E42" s="22">
@@ -1809,18 +1809,18 @@
     </row>
     <row r="43">
       <c r="A43" s="21" t="str">
-        <f>"Queda de "&amp;ROUND(B43*100,0)&amp;"%"</f>
+        <f>IF(IF(ISNUMBER(B43),AND(B43&gt;=0,B43&lt;1),FALSE),"Queda de "&amp;ROUND(B43*100,0)&amp;"%","Percentual inválido (0 a 99 %)")</f>
         <v>Queda de 20%</v>
       </c>
       <c r="B43" s="30" t="n">
         <v>0.2</v>
       </c>
       <c r="C43" s="27">
-        <f>IF(ISNUMBER($B$12),$B$12*(1-B43),"")</f>
+        <f>IF(AND(ISNUMBER($B$12),IF(ISNUMBER(B43),AND(B43&gt;=0,B43&lt;1),FALSE)),$B$12*(1-B43),"")</f>
         <v>224</v>
       </c>
       <c r="D43" s="22">
-        <f>IF(OR(C43="",C43=0,NOT(ISNUMBER($B$11))),"",$B$11/C43)</f>
+        <f>IF(OR(NOT(IF(ISNUMBER(C43),C43&gt;0,FALSE)),NOT(ISNUMBER($B$11))),"",$B$11/C43)</f>
         <v>82.5892857142857</v>
       </c>
       <c r="E43" s="22">
@@ -1834,18 +1834,18 @@
     </row>
     <row r="44">
       <c r="A44" s="21" t="str">
-        <f>"Queda de "&amp;ROUND(B44*100,0)&amp;"%"</f>
+        <f>IF(IF(ISNUMBER(B44),AND(B44&gt;=0,B44&lt;1),FALSE),"Queda de "&amp;ROUND(B44*100,0)&amp;"%","Percentual inválido (0 a 99 %)")</f>
         <v>Queda de 30%</v>
       </c>
       <c r="B44" s="30" t="n">
         <v>0.3</v>
       </c>
       <c r="C44" s="27">
-        <f>IF(ISNUMBER($B$12),$B$12*(1-B44),"")</f>
+        <f>IF(AND(ISNUMBER($B$12),IF(ISNUMBER(B44),AND(B44&gt;=0,B44&lt;1),FALSE)),$B$12*(1-B44),"")</f>
         <v>196</v>
       </c>
       <c r="D44" s="22">
-        <f>IF(OR(C44="",C44=0,NOT(ISNUMBER($B$11))),"",$B$11/C44)</f>
+        <f>IF(OR(NOT(IF(ISNUMBER(C44),C44&gt;0,FALSE)),NOT(ISNUMBER($B$11))),"",$B$11/C44)</f>
         <v>94.3877551020408</v>
       </c>
       <c r="E44" s="22">
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="B36" s="26">
-        <f>IF(SUMPRODUCT(((A5:A34&lt;&gt;"")+(B5:B34&lt;&gt;"")&gt;0)*(ISNUMBER(B5:B34)=FALSE))&gt;0,"custo fixo sem valor numérico",SUM(B5:B34))</f>
+        <f>IF(SUMPRODUCT(((A5:A34&lt;&gt;"")+(B5:B34&lt;&gt;"")&gt;0)*((ISNUMBER(B5:B34)=FALSE)+ISNUMBER(B5:B34)*(B5:B34&lt;0)&gt;0))&gt;0,"custo fixo sem valor numérico ou negativo",SUM(B5:B34))</f>
         <v>6500</v>
       </c>
     </row>
@@ -2441,11 +2441,11 @@
         <v>110</v>
       </c>
       <c r="G5" s="28">
-        <f>IF(OR(A5="",NOT(ISNUMBER(E5)),N(E5)=0,NOT(ISNUMBER(F5))),"",F5/E5)</f>
+        <f>IF(OR(A5="",NOT(IF(ISNUMBER(E5),E5&gt;0,FALSE)),NOT(IF(ISNUMBER(F5),F5&gt;=0,FALSE))),"",F5/E5)</f>
         <v>0.6875</v>
       </c>
       <c r="H5" s="22">
-        <f>IF(A5="","",IF(NOT(ISNUMBER(C5)),"falta o pró-labore",IF(AND(D5&lt;&gt;"Sim",D5&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F5)),F5=0),"faltam as horas faturáveis",C5/F5))))</f>
+        <f>IF(A5="","",IF(NOT(IF(ISNUMBER(C5),C5&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D5&lt;&gt;"Sim",D5&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F5),F5&gt;0,FALSE)),"faltam as horas faturáveis",C5/F5))))</f>
         <v>54.5454545454546</v>
       </c>
       <c r="I5" s="22">
@@ -2457,7 +2457,7 @@
         <v>117.354419773775</v>
       </c>
       <c r="K5" s="40">
-        <f>IF(AND(A5&lt;&gt;"",OR(NOT(ISNUMBER(C5)),NOT(ISNUMBER(F5)),AND(D5&lt;&gt;"Sim",D5&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(A5&lt;&gt;"",OR(NOT(IF(ISNUMBER(C5),C5&gt;=0,FALSE)),NOT(IF(ISNUMBER(F5),F5&gt;0,FALSE)),AND(D5&lt;&gt;"Sim",D5&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2487,11 +2487,11 @@
         <v>110</v>
       </c>
       <c r="G6" s="28">
-        <f>IF(OR(A6="",NOT(ISNUMBER(E6)),N(E6)=0,NOT(ISNUMBER(F6))),"",F6/E6)</f>
+        <f>IF(OR(A6="",NOT(IF(ISNUMBER(E6),E6&gt;0,FALSE)),NOT(IF(ISNUMBER(F6),F6&gt;=0,FALSE))),"",F6/E6)</f>
         <v>0.6875</v>
       </c>
       <c r="H6" s="22">
-        <f>IF(A6="","",IF(NOT(ISNUMBER(C6)),"falta o pró-labore",IF(AND(D6&lt;&gt;"Sim",D6&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F6)),F6=0),"faltam as horas faturáveis",C6/F6))))</f>
+        <f>IF(A6="","",IF(NOT(IF(ISNUMBER(C6),C6&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D6&lt;&gt;"Sim",D6&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F6),F6&gt;0,FALSE)),"faltam as horas faturáveis",C6/F6))))</f>
         <v>54.5454545454546</v>
       </c>
       <c r="I6" s="22">
@@ -2503,7 +2503,7 @@
         <v>117.354419773775</v>
       </c>
       <c r="K6" s="40">
-        <f>IF(AND(A6&lt;&gt;"",OR(NOT(ISNUMBER(C6)),NOT(ISNUMBER(F6)),AND(D6&lt;&gt;"Sim",D6&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(A6&lt;&gt;"",OR(NOT(IF(ISNUMBER(C6),C6&gt;=0,FALSE)),NOT(IF(ISNUMBER(F6),F6&gt;0,FALSE)),AND(D6&lt;&gt;"Sim",D6&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2533,11 +2533,11 @@
         <v>60</v>
       </c>
       <c r="G7" s="28">
-        <f>IF(OR(A7="",NOT(ISNUMBER(E7)),N(E7)=0,NOT(ISNUMBER(F7))),"",F7/E7)</f>
+        <f>IF(OR(A7="",NOT(IF(ISNUMBER(E7),E7&gt;0,FALSE)),NOT(IF(ISNUMBER(F7),F7&gt;=0,FALSE))),"",F7/E7)</f>
         <v>0.5</v>
       </c>
       <c r="H7" s="22">
-        <f>IF(A7="","",IF(NOT(ISNUMBER(C7)),"falta o pró-labore",IF(AND(D7&lt;&gt;"Sim",D7&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F7)),F7=0),"faltam as horas faturáveis",C7/F7))))</f>
+        <f>IF(A7="","",IF(NOT(IF(ISNUMBER(C7),C7&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D7&lt;&gt;"Sim",D7&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F7),F7&gt;0,FALSE)),"faltam as horas faturáveis",C7/F7))))</f>
         <v>23.3333333333333</v>
       </c>
       <c r="I7" s="22">
@@ -2549,7 +2549,7 @@
         <v>67.0122887864823</v>
       </c>
       <c r="K7" s="40">
-        <f>IF(AND(A7&lt;&gt;"",OR(NOT(ISNUMBER(C7)),NOT(ISNUMBER(F7)),AND(D7&lt;&gt;"Sim",D7&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(A7&lt;&gt;"",OR(NOT(IF(ISNUMBER(C7),C7&gt;=0,FALSE)),NOT(IF(ISNUMBER(F7),F7&gt;0,FALSE)),AND(D7&lt;&gt;"Sim",D7&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2561,11 +2561,11 @@
       <c r="E8" s="39" t="n"/>
       <c r="F8" s="39" t="n"/>
       <c r="G8" s="28">
-        <f>IF(OR(A8="",NOT(ISNUMBER(E8)),N(E8)=0,NOT(ISNUMBER(F8))),"",F8/E8)</f>
+        <f>IF(OR(A8="",NOT(IF(ISNUMBER(E8),E8&gt;0,FALSE)),NOT(IF(ISNUMBER(F8),F8&gt;=0,FALSE))),"",F8/E8)</f>
         <v/>
       </c>
       <c r="H8" s="22">
-        <f>IF(A8="","",IF(NOT(ISNUMBER(C8)),"falta o pró-labore",IF(AND(D8&lt;&gt;"Sim",D8&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F8)),F8=0),"faltam as horas faturáveis",C8/F8))))</f>
+        <f>IF(A8="","",IF(NOT(IF(ISNUMBER(C8),C8&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D8&lt;&gt;"Sim",D8&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F8),F8&gt;0,FALSE)),"faltam as horas faturáveis",C8/F8))))</f>
         <v/>
       </c>
       <c r="I8" s="22">
@@ -2577,7 +2577,7 @@
         <v/>
       </c>
       <c r="K8" s="40">
-        <f>IF(AND(A8&lt;&gt;"",OR(NOT(ISNUMBER(C8)),NOT(ISNUMBER(F8)),AND(D8&lt;&gt;"Sim",D8&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(A8&lt;&gt;"",OR(NOT(IF(ISNUMBER(C8),C8&gt;=0,FALSE)),NOT(IF(ISNUMBER(F8),F8&gt;0,FALSE)),AND(D8&lt;&gt;"Sim",D8&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2589,11 +2589,11 @@
       <c r="E9" s="39" t="n"/>
       <c r="F9" s="39" t="n"/>
       <c r="G9" s="28">
-        <f>IF(OR(A9="",NOT(ISNUMBER(E9)),N(E9)=0,NOT(ISNUMBER(F9))),"",F9/E9)</f>
+        <f>IF(OR(A9="",NOT(IF(ISNUMBER(E9),E9&gt;0,FALSE)),NOT(IF(ISNUMBER(F9),F9&gt;=0,FALSE))),"",F9/E9)</f>
         <v/>
       </c>
       <c r="H9" s="22">
-        <f>IF(A9="","",IF(NOT(ISNUMBER(C9)),"falta o pró-labore",IF(AND(D9&lt;&gt;"Sim",D9&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F9)),F9=0),"faltam as horas faturáveis",C9/F9))))</f>
+        <f>IF(A9="","",IF(NOT(IF(ISNUMBER(C9),C9&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D9&lt;&gt;"Sim",D9&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F9),F9&gt;0,FALSE)),"faltam as horas faturáveis",C9/F9))))</f>
         <v/>
       </c>
       <c r="I9" s="22">
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="K9" s="40">
-        <f>IF(AND(A9&lt;&gt;"",OR(NOT(ISNUMBER(C9)),NOT(ISNUMBER(F9)),AND(D9&lt;&gt;"Sim",D9&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(A9&lt;&gt;"",OR(NOT(IF(ISNUMBER(C9),C9&gt;=0,FALSE)),NOT(IF(ISNUMBER(F9),F9&gt;0,FALSE)),AND(D9&lt;&gt;"Sim",D9&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2617,11 +2617,11 @@
       <c r="E10" s="39" t="n"/>
       <c r="F10" s="39" t="n"/>
       <c r="G10" s="28">
-        <f>IF(OR(A10="",NOT(ISNUMBER(E10)),N(E10)=0,NOT(ISNUMBER(F10))),"",F10/E10)</f>
+        <f>IF(OR(A10="",NOT(IF(ISNUMBER(E10),E10&gt;0,FALSE)),NOT(IF(ISNUMBER(F10),F10&gt;=0,FALSE))),"",F10/E10)</f>
         <v/>
       </c>
       <c r="H10" s="22">
-        <f>IF(A10="","",IF(NOT(ISNUMBER(C10)),"falta o pró-labore",IF(AND(D10&lt;&gt;"Sim",D10&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F10)),F10=0),"faltam as horas faturáveis",C10/F10))))</f>
+        <f>IF(A10="","",IF(NOT(IF(ISNUMBER(C10),C10&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D10&lt;&gt;"Sim",D10&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F10),F10&gt;0,FALSE)),"faltam as horas faturáveis",C10/F10))))</f>
         <v/>
       </c>
       <c r="I10" s="22">
@@ -2633,7 +2633,7 @@
         <v/>
       </c>
       <c r="K10" s="40">
-        <f>IF(AND(A10&lt;&gt;"",OR(NOT(ISNUMBER(C10)),NOT(ISNUMBER(F10)),AND(D10&lt;&gt;"Sim",D10&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(A10&lt;&gt;"",OR(NOT(IF(ISNUMBER(C10),C10&gt;=0,FALSE)),NOT(IF(ISNUMBER(F10),F10&gt;0,FALSE)),AND(D10&lt;&gt;"Sim",D10&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2645,11 +2645,11 @@
       <c r="E11" s="39" t="n"/>
       <c r="F11" s="39" t="n"/>
       <c r="G11" s="28">
-        <f>IF(OR(A11="",NOT(ISNUMBER(E11)),N(E11)=0,NOT(ISNUMBER(F11))),"",F11/E11)</f>
+        <f>IF(OR(A11="",NOT(IF(ISNUMBER(E11),E11&gt;0,FALSE)),NOT(IF(ISNUMBER(F11),F11&gt;=0,FALSE))),"",F11/E11)</f>
         <v/>
       </c>
       <c r="H11" s="22">
-        <f>IF(A11="","",IF(NOT(ISNUMBER(C11)),"falta o pró-labore",IF(AND(D11&lt;&gt;"Sim",D11&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F11)),F11=0),"faltam as horas faturáveis",C11/F11))))</f>
+        <f>IF(A11="","",IF(NOT(IF(ISNUMBER(C11),C11&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D11&lt;&gt;"Sim",D11&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F11),F11&gt;0,FALSE)),"faltam as horas faturáveis",C11/F11))))</f>
         <v/>
       </c>
       <c r="I11" s="22">
@@ -2661,7 +2661,7 @@
         <v/>
       </c>
       <c r="K11" s="40">
-        <f>IF(AND(A11&lt;&gt;"",OR(NOT(ISNUMBER(C11)),NOT(ISNUMBER(F11)),AND(D11&lt;&gt;"Sim",D11&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(A11&lt;&gt;"",OR(NOT(IF(ISNUMBER(C11),C11&gt;=0,FALSE)),NOT(IF(ISNUMBER(F11),F11&gt;0,FALSE)),AND(D11&lt;&gt;"Sim",D11&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2673,11 +2673,11 @@
       <c r="E12" s="39" t="n"/>
       <c r="F12" s="39" t="n"/>
       <c r="G12" s="28">
-        <f>IF(OR(A12="",NOT(ISNUMBER(E12)),N(E12)=0,NOT(ISNUMBER(F12))),"",F12/E12)</f>
+        <f>IF(OR(A12="",NOT(IF(ISNUMBER(E12),E12&gt;0,FALSE)),NOT(IF(ISNUMBER(F12),F12&gt;=0,FALSE))),"",F12/E12)</f>
         <v/>
       </c>
       <c r="H12" s="22">
-        <f>IF(A12="","",IF(NOT(ISNUMBER(C12)),"falta o pró-labore",IF(AND(D12&lt;&gt;"Sim",D12&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F12)),F12=0),"faltam as horas faturáveis",C12/F12))))</f>
+        <f>IF(A12="","",IF(NOT(IF(ISNUMBER(C12),C12&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D12&lt;&gt;"Sim",D12&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F12),F12&gt;0,FALSE)),"faltam as horas faturáveis",C12/F12))))</f>
         <v/>
       </c>
       <c r="I12" s="22">
@@ -2689,7 +2689,7 @@
         <v/>
       </c>
       <c r="K12" s="40">
-        <f>IF(AND(A12&lt;&gt;"",OR(NOT(ISNUMBER(C12)),NOT(ISNUMBER(F12)),AND(D12&lt;&gt;"Sim",D12&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(A12&lt;&gt;"",OR(NOT(IF(ISNUMBER(C12),C12&gt;=0,FALSE)),NOT(IF(ISNUMBER(F12),F12&gt;0,FALSE)),AND(D12&lt;&gt;"Sim",D12&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2701,11 +2701,11 @@
       <c r="E13" s="39" t="n"/>
       <c r="F13" s="39" t="n"/>
       <c r="G13" s="28">
-        <f>IF(OR(A13="",NOT(ISNUMBER(E13)),N(E13)=0,NOT(ISNUMBER(F13))),"",F13/E13)</f>
+        <f>IF(OR(A13="",NOT(IF(ISNUMBER(E13),E13&gt;0,FALSE)),NOT(IF(ISNUMBER(F13),F13&gt;=0,FALSE))),"",F13/E13)</f>
         <v/>
       </c>
       <c r="H13" s="22">
-        <f>IF(A13="","",IF(NOT(ISNUMBER(C13)),"falta o pró-labore",IF(AND(D13&lt;&gt;"Sim",D13&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F13)),F13=0),"faltam as horas faturáveis",C13/F13))))</f>
+        <f>IF(A13="","",IF(NOT(IF(ISNUMBER(C13),C13&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D13&lt;&gt;"Sim",D13&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F13),F13&gt;0,FALSE)),"faltam as horas faturáveis",C13/F13))))</f>
         <v/>
       </c>
       <c r="I13" s="22">
@@ -2717,7 +2717,7 @@
         <v/>
       </c>
       <c r="K13" s="40">
-        <f>IF(AND(A13&lt;&gt;"",OR(NOT(ISNUMBER(C13)),NOT(ISNUMBER(F13)),AND(D13&lt;&gt;"Sim",D13&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(A13&lt;&gt;"",OR(NOT(IF(ISNUMBER(C13),C13&gt;=0,FALSE)),NOT(IF(ISNUMBER(F13),F13&gt;0,FALSE)),AND(D13&lt;&gt;"Sim",D13&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2729,11 +2729,11 @@
       <c r="E14" s="39" t="n"/>
       <c r="F14" s="39" t="n"/>
       <c r="G14" s="28">
-        <f>IF(OR(A14="",NOT(ISNUMBER(E14)),N(E14)=0,NOT(ISNUMBER(F14))),"",F14/E14)</f>
+        <f>IF(OR(A14="",NOT(IF(ISNUMBER(E14),E14&gt;0,FALSE)),NOT(IF(ISNUMBER(F14),F14&gt;=0,FALSE))),"",F14/E14)</f>
         <v/>
       </c>
       <c r="H14" s="22">
-        <f>IF(A14="","",IF(NOT(ISNUMBER(C14)),"falta o pró-labore",IF(AND(D14&lt;&gt;"Sim",D14&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F14)),F14=0),"faltam as horas faturáveis",C14/F14))))</f>
+        <f>IF(A14="","",IF(NOT(IF(ISNUMBER(C14),C14&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D14&lt;&gt;"Sim",D14&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F14),F14&gt;0,FALSE)),"faltam as horas faturáveis",C14/F14))))</f>
         <v/>
       </c>
       <c r="I14" s="22">
@@ -2745,7 +2745,7 @@
         <v/>
       </c>
       <c r="K14" s="40">
-        <f>IF(AND(A14&lt;&gt;"",OR(NOT(ISNUMBER(C14)),NOT(ISNUMBER(F14)),AND(D14&lt;&gt;"Sim",D14&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(A14&lt;&gt;"",OR(NOT(IF(ISNUMBER(C14),C14&gt;=0,FALSE)),NOT(IF(ISNUMBER(F14),F14&gt;0,FALSE)),AND(D14&lt;&gt;"Sim",D14&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/05-custo-hora.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/05-custo-hora.xlsx
@@ -2445,7 +2445,7 @@
         <v>0.6875</v>
       </c>
       <c r="H5" s="22">
-        <f>IF(A5="","",IF(NOT(IF(ISNUMBER(C5),C5&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D5&lt;&gt;"Sim",D5&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F5),F5&gt;0,FALSE)),"faltam as horas faturáveis",C5/F5))))</f>
+        <f>IF(NOT(OR(A5&lt;&gt;"",B5&lt;&gt;"",C5&lt;&gt;"",D5&lt;&gt;"",E5&lt;&gt;"",F5&lt;&gt;"")),"",IF(A5="","falta o nome",IF(NOT(IF(ISNUMBER(C5),C5&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D5&lt;&gt;"Sim",D5&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F5),F5&gt;0,FALSE)),"faltam as horas faturáveis",C5/F5)))))</f>
         <v>54.5454545454546</v>
       </c>
       <c r="I5" s="22">
@@ -2457,7 +2457,7 @@
         <v>117.354419773775</v>
       </c>
       <c r="K5" s="40">
-        <f>IF(AND(A5&lt;&gt;"",OR(NOT(IF(ISNUMBER(C5),C5&gt;=0,FALSE)),NOT(IF(ISNUMBER(F5),F5&gt;0,FALSE)),AND(D5&lt;&gt;"Sim",D5&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(OR(A5&lt;&gt;"",B5&lt;&gt;"",C5&lt;&gt;"",D5&lt;&gt;"",E5&lt;&gt;"",F5&lt;&gt;""),OR(A5="",NOT(IF(ISNUMBER(C5),C5&gt;=0,FALSE)),NOT(IF(ISNUMBER(F5),F5&gt;0,FALSE)),AND(D5&lt;&gt;"Sim",D5&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
         <v>0.6875</v>
       </c>
       <c r="H6" s="22">
-        <f>IF(A6="","",IF(NOT(IF(ISNUMBER(C6),C6&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D6&lt;&gt;"Sim",D6&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F6),F6&gt;0,FALSE)),"faltam as horas faturáveis",C6/F6))))</f>
+        <f>IF(NOT(OR(A6&lt;&gt;"",B6&lt;&gt;"",C6&lt;&gt;"",D6&lt;&gt;"",E6&lt;&gt;"",F6&lt;&gt;"")),"",IF(A6="","falta o nome",IF(NOT(IF(ISNUMBER(C6),C6&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D6&lt;&gt;"Sim",D6&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F6),F6&gt;0,FALSE)),"faltam as horas faturáveis",C6/F6)))))</f>
         <v>54.5454545454546</v>
       </c>
       <c r="I6" s="22">
@@ -2503,7 +2503,7 @@
         <v>117.354419773775</v>
       </c>
       <c r="K6" s="40">
-        <f>IF(AND(A6&lt;&gt;"",OR(NOT(IF(ISNUMBER(C6),C6&gt;=0,FALSE)),NOT(IF(ISNUMBER(F6),F6&gt;0,FALSE)),AND(D6&lt;&gt;"Sim",D6&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(OR(A6&lt;&gt;"",B6&lt;&gt;"",C6&lt;&gt;"",D6&lt;&gt;"",E6&lt;&gt;"",F6&lt;&gt;""),OR(A6="",NOT(IF(ISNUMBER(C6),C6&gt;=0,FALSE)),NOT(IF(ISNUMBER(F6),F6&gt;0,FALSE)),AND(D6&lt;&gt;"Sim",D6&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
         <v>0.5</v>
       </c>
       <c r="H7" s="22">
-        <f>IF(A7="","",IF(NOT(IF(ISNUMBER(C7),C7&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D7&lt;&gt;"Sim",D7&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F7),F7&gt;0,FALSE)),"faltam as horas faturáveis",C7/F7))))</f>
+        <f>IF(NOT(OR(A7&lt;&gt;"",B7&lt;&gt;"",C7&lt;&gt;"",D7&lt;&gt;"",E7&lt;&gt;"",F7&lt;&gt;"")),"",IF(A7="","falta o nome",IF(NOT(IF(ISNUMBER(C7),C7&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D7&lt;&gt;"Sim",D7&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F7),F7&gt;0,FALSE)),"faltam as horas faturáveis",C7/F7)))))</f>
         <v>23.3333333333333</v>
       </c>
       <c r="I7" s="22">
@@ -2549,7 +2549,7 @@
         <v>67.0122887864823</v>
       </c>
       <c r="K7" s="40">
-        <f>IF(AND(A7&lt;&gt;"",OR(NOT(IF(ISNUMBER(C7),C7&gt;=0,FALSE)),NOT(IF(ISNUMBER(F7),F7&gt;0,FALSE)),AND(D7&lt;&gt;"Sim",D7&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(OR(A7&lt;&gt;"",B7&lt;&gt;"",C7&lt;&gt;"",D7&lt;&gt;"",E7&lt;&gt;"",F7&lt;&gt;""),OR(A7="",NOT(IF(ISNUMBER(C7),C7&gt;=0,FALSE)),NOT(IF(ISNUMBER(F7),F7&gt;0,FALSE)),AND(D7&lt;&gt;"Sim",D7&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
         <v/>
       </c>
       <c r="H8" s="22">
-        <f>IF(A8="","",IF(NOT(IF(ISNUMBER(C8),C8&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D8&lt;&gt;"Sim",D8&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F8),F8&gt;0,FALSE)),"faltam as horas faturáveis",C8/F8))))</f>
+        <f>IF(NOT(OR(A8&lt;&gt;"",B8&lt;&gt;"",C8&lt;&gt;"",D8&lt;&gt;"",E8&lt;&gt;"",F8&lt;&gt;"")),"",IF(A8="","falta o nome",IF(NOT(IF(ISNUMBER(C8),C8&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D8&lt;&gt;"Sim",D8&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F8),F8&gt;0,FALSE)),"faltam as horas faturáveis",C8/F8)))))</f>
         <v/>
       </c>
       <c r="I8" s="22">
@@ -2577,7 +2577,7 @@
         <v/>
       </c>
       <c r="K8" s="40">
-        <f>IF(AND(A8&lt;&gt;"",OR(NOT(IF(ISNUMBER(C8),C8&gt;=0,FALSE)),NOT(IF(ISNUMBER(F8),F8&gt;0,FALSE)),AND(D8&lt;&gt;"Sim",D8&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(OR(A8&lt;&gt;"",B8&lt;&gt;"",C8&lt;&gt;"",D8&lt;&gt;"",E8&lt;&gt;"",F8&lt;&gt;""),OR(A8="",NOT(IF(ISNUMBER(C8),C8&gt;=0,FALSE)),NOT(IF(ISNUMBER(F8),F8&gt;0,FALSE)),AND(D8&lt;&gt;"Sim",D8&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
         <v/>
       </c>
       <c r="H9" s="22">
-        <f>IF(A9="","",IF(NOT(IF(ISNUMBER(C9),C9&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D9&lt;&gt;"Sim",D9&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F9),F9&gt;0,FALSE)),"faltam as horas faturáveis",C9/F9))))</f>
+        <f>IF(NOT(OR(A9&lt;&gt;"",B9&lt;&gt;"",C9&lt;&gt;"",D9&lt;&gt;"",E9&lt;&gt;"",F9&lt;&gt;"")),"",IF(A9="","falta o nome",IF(NOT(IF(ISNUMBER(C9),C9&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D9&lt;&gt;"Sim",D9&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F9),F9&gt;0,FALSE)),"faltam as horas faturáveis",C9/F9)))))</f>
         <v/>
       </c>
       <c r="I9" s="22">
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="K9" s="40">
-        <f>IF(AND(A9&lt;&gt;"",OR(NOT(IF(ISNUMBER(C9),C9&gt;=0,FALSE)),NOT(IF(ISNUMBER(F9),F9&gt;0,FALSE)),AND(D9&lt;&gt;"Sim",D9&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(OR(A9&lt;&gt;"",B9&lt;&gt;"",C9&lt;&gt;"",D9&lt;&gt;"",E9&lt;&gt;"",F9&lt;&gt;""),OR(A9="",NOT(IF(ISNUMBER(C9),C9&gt;=0,FALSE)),NOT(IF(ISNUMBER(F9),F9&gt;0,FALSE)),AND(D9&lt;&gt;"Sim",D9&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
         <v/>
       </c>
       <c r="H10" s="22">
-        <f>IF(A10="","",IF(NOT(IF(ISNUMBER(C10),C10&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D10&lt;&gt;"Sim",D10&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F10),F10&gt;0,FALSE)),"faltam as horas faturáveis",C10/F10))))</f>
+        <f>IF(NOT(OR(A10&lt;&gt;"",B10&lt;&gt;"",C10&lt;&gt;"",D10&lt;&gt;"",E10&lt;&gt;"",F10&lt;&gt;"")),"",IF(A10="","falta o nome",IF(NOT(IF(ISNUMBER(C10),C10&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D10&lt;&gt;"Sim",D10&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F10),F10&gt;0,FALSE)),"faltam as horas faturáveis",C10/F10)))))</f>
         <v/>
       </c>
       <c r="I10" s="22">
@@ -2633,7 +2633,7 @@
         <v/>
       </c>
       <c r="K10" s="40">
-        <f>IF(AND(A10&lt;&gt;"",OR(NOT(IF(ISNUMBER(C10),C10&gt;=0,FALSE)),NOT(IF(ISNUMBER(F10),F10&gt;0,FALSE)),AND(D10&lt;&gt;"Sim",D10&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(OR(A10&lt;&gt;"",B10&lt;&gt;"",C10&lt;&gt;"",D10&lt;&gt;"",E10&lt;&gt;"",F10&lt;&gt;""),OR(A10="",NOT(IF(ISNUMBER(C10),C10&gt;=0,FALSE)),NOT(IF(ISNUMBER(F10),F10&gt;0,FALSE)),AND(D10&lt;&gt;"Sim",D10&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
         <v/>
       </c>
       <c r="H11" s="22">
-        <f>IF(A11="","",IF(NOT(IF(ISNUMBER(C11),C11&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D11&lt;&gt;"Sim",D11&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F11),F11&gt;0,FALSE)),"faltam as horas faturáveis",C11/F11))))</f>
+        <f>IF(NOT(OR(A11&lt;&gt;"",B11&lt;&gt;"",C11&lt;&gt;"",D11&lt;&gt;"",E11&lt;&gt;"",F11&lt;&gt;"")),"",IF(A11="","falta o nome",IF(NOT(IF(ISNUMBER(C11),C11&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D11&lt;&gt;"Sim",D11&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F11),F11&gt;0,FALSE)),"faltam as horas faturáveis",C11/F11)))))</f>
         <v/>
       </c>
       <c r="I11" s="22">
@@ -2661,7 +2661,7 @@
         <v/>
       </c>
       <c r="K11" s="40">
-        <f>IF(AND(A11&lt;&gt;"",OR(NOT(IF(ISNUMBER(C11),C11&gt;=0,FALSE)),NOT(IF(ISNUMBER(F11),F11&gt;0,FALSE)),AND(D11&lt;&gt;"Sim",D11&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(OR(A11&lt;&gt;"",B11&lt;&gt;"",C11&lt;&gt;"",D11&lt;&gt;"",E11&lt;&gt;"",F11&lt;&gt;""),OR(A11="",NOT(IF(ISNUMBER(C11),C11&gt;=0,FALSE)),NOT(IF(ISNUMBER(F11),F11&gt;0,FALSE)),AND(D11&lt;&gt;"Sim",D11&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2677,7 +2677,7 @@
         <v/>
       </c>
       <c r="H12" s="22">
-        <f>IF(A12="","",IF(NOT(IF(ISNUMBER(C12),C12&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D12&lt;&gt;"Sim",D12&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F12),F12&gt;0,FALSE)),"faltam as horas faturáveis",C12/F12))))</f>
+        <f>IF(NOT(OR(A12&lt;&gt;"",B12&lt;&gt;"",C12&lt;&gt;"",D12&lt;&gt;"",E12&lt;&gt;"",F12&lt;&gt;"")),"",IF(A12="","falta o nome",IF(NOT(IF(ISNUMBER(C12),C12&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D12&lt;&gt;"Sim",D12&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F12),F12&gt;0,FALSE)),"faltam as horas faturáveis",C12/F12)))))</f>
         <v/>
       </c>
       <c r="I12" s="22">
@@ -2689,7 +2689,7 @@
         <v/>
       </c>
       <c r="K12" s="40">
-        <f>IF(AND(A12&lt;&gt;"",OR(NOT(IF(ISNUMBER(C12),C12&gt;=0,FALSE)),NOT(IF(ISNUMBER(F12),F12&gt;0,FALSE)),AND(D12&lt;&gt;"Sim",D12&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(OR(A12&lt;&gt;"",B12&lt;&gt;"",C12&lt;&gt;"",D12&lt;&gt;"",E12&lt;&gt;"",F12&lt;&gt;""),OR(A12="",NOT(IF(ISNUMBER(C12),C12&gt;=0,FALSE)),NOT(IF(ISNUMBER(F12),F12&gt;0,FALSE)),AND(D12&lt;&gt;"Sim",D12&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2705,7 +2705,7 @@
         <v/>
       </c>
       <c r="H13" s="22">
-        <f>IF(A13="","",IF(NOT(IF(ISNUMBER(C13),C13&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D13&lt;&gt;"Sim",D13&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F13),F13&gt;0,FALSE)),"faltam as horas faturáveis",C13/F13))))</f>
+        <f>IF(NOT(OR(A13&lt;&gt;"",B13&lt;&gt;"",C13&lt;&gt;"",D13&lt;&gt;"",E13&lt;&gt;"",F13&lt;&gt;"")),"",IF(A13="","falta o nome",IF(NOT(IF(ISNUMBER(C13),C13&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D13&lt;&gt;"Sim",D13&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F13),F13&gt;0,FALSE)),"faltam as horas faturáveis",C13/F13)))))</f>
         <v/>
       </c>
       <c r="I13" s="22">
@@ -2717,7 +2717,7 @@
         <v/>
       </c>
       <c r="K13" s="40">
-        <f>IF(AND(A13&lt;&gt;"",OR(NOT(IF(ISNUMBER(C13),C13&gt;=0,FALSE)),NOT(IF(ISNUMBER(F13),F13&gt;0,FALSE)),AND(D13&lt;&gt;"Sim",D13&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(OR(A13&lt;&gt;"",B13&lt;&gt;"",C13&lt;&gt;"",D13&lt;&gt;"",E13&lt;&gt;"",F13&lt;&gt;""),OR(A13="",NOT(IF(ISNUMBER(C13),C13&gt;=0,FALSE)),NOT(IF(ISNUMBER(F13),F13&gt;0,FALSE)),AND(D13&lt;&gt;"Sim",D13&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2733,7 +2733,7 @@
         <v/>
       </c>
       <c r="H14" s="22">
-        <f>IF(A14="","",IF(NOT(IF(ISNUMBER(C14),C14&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D14&lt;&gt;"Sim",D14&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F14),F14&gt;0,FALSE)),"faltam as horas faturáveis",C14/F14))))</f>
+        <f>IF(NOT(OR(A14&lt;&gt;"",B14&lt;&gt;"",C14&lt;&gt;"",D14&lt;&gt;"",E14&lt;&gt;"",F14&lt;&gt;"")),"",IF(A14="","falta o nome",IF(NOT(IF(ISNUMBER(C14),C14&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D14&lt;&gt;"Sim",D14&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F14),F14&gt;0,FALSE)),"faltam as horas faturáveis",C14/F14)))))</f>
         <v/>
       </c>
       <c r="I14" s="22">
@@ -2745,7 +2745,7 @@
         <v/>
       </c>
       <c r="K14" s="40">
-        <f>IF(AND(A14&lt;&gt;"",OR(NOT(IF(ISNUMBER(C14),C14&gt;=0,FALSE)),NOT(IF(ISNUMBER(F14),F14&gt;0,FALSE)),AND(D14&lt;&gt;"Sim",D14&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(OR(A14&lt;&gt;"",B14&lt;&gt;"",C14&lt;&gt;"",D14&lt;&gt;"",E14&lt;&gt;"",F14&lt;&gt;""),OR(A14="",NOT(IF(ISNUMBER(C14),C14&gt;=0,FALSE)),NOT(IF(ISNUMBER(F14),F14&gt;0,FALSE)),AND(D14&lt;&gt;"Sim",D14&lt;&gt;"Não"))),1,0)</f>
         <v>0</v>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/05-custo-hora.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/05-custo-hora.xlsx
@@ -1097,7 +1097,7 @@
     </row>
     <row r="6">
       <c r="A6" s="18">
-        <f>IF((SUM(Pessoas!$K$5:$K$14)+IF(ISNUMBER('Custos fixos'!$B$36),0,1))=0,"",IF(IF(ISNUMBER('Custos fixos'!$B$36),0,1)&gt;0,"Atenção: há custo fixo sem valor, com texto ou negativo na aba Custos fixos. ","")&amp;IF(SUM(Pessoas!$K$5:$K$14)&gt;0,"Atenção: "&amp;SUM(Pessoas!$K$5:$K$14)&amp;" pessoa(s) na aba Pessoas com pró-labore, horas faturáveis ou 'já está nos custos fixos?' em branco. ","")&amp;"Custo do mês, custo-hora e hora mínima ficam como 'cadastro incompleto' até você completar: uma soma parcial daria um custo-hora MENOR do que o real.")</f>
+        <f>IF((SUM(Pessoas!$K$5:$K$14)+IF(ISNUMBER('Custos fixos'!$B$36),0,1))=0,"",IF(IF(ISNUMBER('Custos fixos'!$B$36),0,1)&gt;0,"Atenção: há custo fixo sem descrição, sem valor, com texto ou negativo na aba Custos fixos. ","")&amp;IF(SUM(Pessoas!$K$5:$K$14)&gt;0,"Atenção: "&amp;SUM(Pessoas!$K$5:$K$14)&amp;" pessoa(s) na aba Pessoas com pró-labore, horas faturáveis ou 'já está nos custos fixos?' em branco. ","")&amp;"Custo do mês, custo-hora e hora mínima ficam como 'cadastro incompleto' até você completar: uma soma parcial daria um custo-hora MENOR do que o real.")</f>
         <v/>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="B20" s="27">
-        <f>IF(SUMPRODUCT((Pessoas!$A$5:$A$14&lt;&gt;"")*((ISNUMBER(Pessoas!$E$5:$E$14)=FALSE)+ISNUMBER(Pessoas!$E$5:$E$14)*(Pessoas!$E$5:$E$14&lt;0)&gt;0))&gt;0,"faltam horas de trabalho",SUM(Pessoas!$E$5:$E$14))</f>
+        <f>IF((SUM(Pessoas!$K$5:$K$14)+IF(ISNUMBER('Custos fixos'!$B$36),0,1))&gt;0,"cadastro incompleto",IF(SUMPRODUCT((Pessoas!$A$5:$A$14&lt;&gt;"")*((ISNUMBER(Pessoas!$E$5:$E$14)=FALSE)+ISNUMBER(Pessoas!$E$5:$E$14)*(Pessoas!$E$5:$E$14&lt;0)&gt;0))&gt;0,"faltam horas de trabalho",SUM(Pessoas!$E$5:$E$14)))</f>
         <v>440</v>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -1409,7 +1409,7 @@
         <v>Marina Ferraz</v>
       </c>
       <c r="B26" s="21" t="str">
-        <f>IF(Pessoas!$A$5="","",Pessoas!$B$5)</f>
+        <f>IF(OR(Pessoas!$A$5="",Pessoas!$B$5=""),"",Pessoas!$B$5)</f>
         <v>Sócia · cível e empresarial</v>
       </c>
       <c r="C26" s="27">
@@ -1439,7 +1439,7 @@
         <v>Rafael Lima</v>
       </c>
       <c r="B27" s="21" t="str">
-        <f>IF(Pessoas!$A$6="","",Pessoas!$B$6)</f>
+        <f>IF(OR(Pessoas!$A$6="",Pessoas!$B$6=""),"",Pessoas!$B$6)</f>
         <v>Sócio · trabalhista e previdenciário</v>
       </c>
       <c r="C27" s="27">
@@ -1469,7 +1469,7 @@
         <v>Júlia Prado</v>
       </c>
       <c r="B28" s="21" t="str">
-        <f>IF(Pessoas!$A$7="","",Pessoas!$B$7)</f>
+        <f>IF(OR(Pessoas!$A$7="",Pessoas!$B$7=""),"",Pessoas!$B$7)</f>
         <v>Estagiária</v>
       </c>
       <c r="C28" s="27">
@@ -1499,7 +1499,7 @@
         <v/>
       </c>
       <c r="B29" s="21">
-        <f>IF(Pessoas!$A$8="","",Pessoas!$B$8)</f>
+        <f>IF(OR(Pessoas!$A$8="",Pessoas!$B$8=""),"",Pessoas!$B$8)</f>
         <v/>
       </c>
       <c r="C29" s="27">
@@ -1529,7 +1529,7 @@
         <v/>
       </c>
       <c r="B30" s="21">
-        <f>IF(Pessoas!$A$9="","",Pessoas!$B$9)</f>
+        <f>IF(OR(Pessoas!$A$9="",Pessoas!$B$9=""),"",Pessoas!$B$9)</f>
         <v/>
       </c>
       <c r="C30" s="27">
@@ -1559,7 +1559,7 @@
         <v/>
       </c>
       <c r="B31" s="21">
-        <f>IF(Pessoas!$A$10="","",Pessoas!$B$10)</f>
+        <f>IF(OR(Pessoas!$A$10="",Pessoas!$B$10=""),"",Pessoas!$B$10)</f>
         <v/>
       </c>
       <c r="C31" s="27">
@@ -1589,7 +1589,7 @@
         <v/>
       </c>
       <c r="B32" s="21">
-        <f>IF(Pessoas!$A$11="","",Pessoas!$B$11)</f>
+        <f>IF(OR(Pessoas!$A$11="",Pessoas!$B$11=""),"",Pessoas!$B$11)</f>
         <v/>
       </c>
       <c r="C32" s="27">
@@ -1619,7 +1619,7 @@
         <v/>
       </c>
       <c r="B33" s="21">
-        <f>IF(Pessoas!$A$12="","",Pessoas!$B$12)</f>
+        <f>IF(OR(Pessoas!$A$12="",Pessoas!$B$12=""),"",Pessoas!$B$12)</f>
         <v/>
       </c>
       <c r="C33" s="27">
@@ -1649,7 +1649,7 @@
         <v/>
       </c>
       <c r="B34" s="21">
-        <f>IF(Pessoas!$A$13="","",Pessoas!$B$13)</f>
+        <f>IF(OR(Pessoas!$A$13="",Pessoas!$B$13=""),"",Pessoas!$B$13)</f>
         <v/>
       </c>
       <c r="C34" s="27">
@@ -1679,7 +1679,7 @@
         <v/>
       </c>
       <c r="B35" s="21">
-        <f>IF(Pessoas!$A$14="","",Pessoas!$B$14)</f>
+        <f>IF(OR(Pessoas!$A$14="",Pessoas!$B$14=""),"",Pessoas!$B$14)</f>
         <v/>
       </c>
       <c r="C35" s="27">
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="B36" s="26">
-        <f>IF(SUMPRODUCT(((A5:A34&lt;&gt;"")+(B5:B34&lt;&gt;"")&gt;0)*((ISNUMBER(B5:B34)=FALSE)+ISNUMBER(B5:B34)*(B5:B34&lt;0)&gt;0))&gt;0,"custo fixo sem valor numérico ou negativo",SUM(B5:B34))</f>
+        <f>IF(SUMPRODUCT(((A5:A34&lt;&gt;"")+(B5:B34&lt;&gt;"")&gt;0)*((A5:A34="")+(ISNUMBER(B5:B34)=FALSE)+ISNUMBER(B5:B34)*(B5:B34&lt;0)&gt;0))&gt;0,"custo fixo sem descrição, sem valor numérico ou negativo",SUM(B5:B34))</f>
         <v>6500</v>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/05-custo-hora.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/05-custo-hora.xlsx
@@ -1097,7 +1097,7 @@
     </row>
     <row r="6">
       <c r="A6" s="18">
-        <f>IF((SUM(Pessoas!$K$5:$K$14)+IF(ISNUMBER('Custos fixos'!$B$36),0,1))=0,"",IF(IF(ISNUMBER('Custos fixos'!$B$36),0,1)&gt;0,"Atenção: há custo fixo sem descrição, sem valor, com texto ou negativo na aba Custos fixos. ","")&amp;IF(SUM(Pessoas!$K$5:$K$14)&gt;0,"Atenção: "&amp;SUM(Pessoas!$K$5:$K$14)&amp;" pessoa(s) na aba Pessoas com pró-labore, horas faturáveis ou 'já está nos custos fixos?' em branco. ","")&amp;"Custo do mês, custo-hora e hora mínima ficam como 'cadastro incompleto' até você completar: uma soma parcial daria um custo-hora MENOR do que o real.")</f>
+        <f>IF((SUM(Pessoas!$K$5:$K$14)+IF(ISNUMBER('Custos fixos'!$B$36),0,1))=0,"",IF(IF(ISNUMBER('Custos fixos'!$B$36),0,1)&gt;0,"Atenção: há custo fixo sem descrição, sem valor, com texto ou negativo na aba Custos fixos. ","")&amp;IF(SUM(Pessoas!$K$5:$K$14)&gt;0,"Atenção: "&amp;SUM(Pessoas!$K$5:$K$14)&amp;" pessoa(s) na aba Pessoas com pró-labore, horas faturáveis ou 'já está nos custos fixos?' em branco, ou com horas faturáveis acima das horas de trabalho. ","")&amp;"Custo do mês, custo-hora e hora mínima ficam como 'cadastro incompleto' até você completar: uma soma parcial daria um custo-hora MENOR do que o real.")</f>
         <v/>
       </c>
     </row>
@@ -2441,11 +2441,11 @@
         <v>110</v>
       </c>
       <c r="G5" s="28">
-        <f>IF(OR(A5="",NOT(IF(ISNUMBER(E5),E5&gt;0,FALSE)),NOT(IF(ISNUMBER(F5),F5&gt;=0,FALSE))),"",F5/E5)</f>
+        <f>IF(OR(A5="",NOT(IF(ISNUMBER(E5),E5&gt;0,FALSE)),NOT(IF(ISNUMBER(F5),F5&gt;=0,FALSE))),"",IF(F5&gt;E5,"faturáveis &gt; trabalho",F5/E5))</f>
         <v>0.6875</v>
       </c>
       <c r="H5" s="22">
-        <f>IF(NOT(OR(A5&lt;&gt;"",B5&lt;&gt;"",C5&lt;&gt;"",D5&lt;&gt;"",E5&lt;&gt;"",F5&lt;&gt;"")),"",IF(A5="","falta o nome",IF(NOT(IF(ISNUMBER(C5),C5&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D5&lt;&gt;"Sim",D5&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F5),F5&gt;0,FALSE)),"faltam as horas faturáveis",C5/F5)))))</f>
+        <f>IF(NOT(OR(A5&lt;&gt;"",B5&lt;&gt;"",C5&lt;&gt;"",D5&lt;&gt;"",E5&lt;&gt;"",F5&lt;&gt;"")),"",IF(A5="","falta o nome",IF(NOT(IF(ISNUMBER(C5),C5&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D5&lt;&gt;"Sim",D5&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F5),F5&gt;0,FALSE)),"faltam as horas faturáveis",IF(AND(ISNUMBER(E5),F5&gt;E5),"faturáveis acima das horas de trabalho",C5/F5))))))</f>
         <v>54.5454545454546</v>
       </c>
       <c r="I5" s="22">
@@ -2457,7 +2457,7 @@
         <v>117.354419773775</v>
       </c>
       <c r="K5" s="40">
-        <f>IF(AND(OR(A5&lt;&gt;"",B5&lt;&gt;"",C5&lt;&gt;"",D5&lt;&gt;"",E5&lt;&gt;"",F5&lt;&gt;""),OR(A5="",NOT(IF(ISNUMBER(C5),C5&gt;=0,FALSE)),NOT(IF(ISNUMBER(F5),F5&gt;0,FALSE)),AND(D5&lt;&gt;"Sim",D5&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(OR(A5&lt;&gt;"",B5&lt;&gt;"",C5&lt;&gt;"",D5&lt;&gt;"",E5&lt;&gt;"",F5&lt;&gt;""),OR(A5="",NOT(IF(ISNUMBER(C5),C5&gt;=0,FALSE)),NOT(IF(ISNUMBER(F5),F5&gt;0,FALSE)),AND(D5&lt;&gt;"Sim",D5&lt;&gt;"Não"),AND(ISNUMBER(E5),ISNUMBER(F5),N(F5)&gt;N(E5)))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2487,11 +2487,11 @@
         <v>110</v>
       </c>
       <c r="G6" s="28">
-        <f>IF(OR(A6="",NOT(IF(ISNUMBER(E6),E6&gt;0,FALSE)),NOT(IF(ISNUMBER(F6),F6&gt;=0,FALSE))),"",F6/E6)</f>
+        <f>IF(OR(A6="",NOT(IF(ISNUMBER(E6),E6&gt;0,FALSE)),NOT(IF(ISNUMBER(F6),F6&gt;=0,FALSE))),"",IF(F6&gt;E6,"faturáveis &gt; trabalho",F6/E6))</f>
         <v>0.6875</v>
       </c>
       <c r="H6" s="22">
-        <f>IF(NOT(OR(A6&lt;&gt;"",B6&lt;&gt;"",C6&lt;&gt;"",D6&lt;&gt;"",E6&lt;&gt;"",F6&lt;&gt;"")),"",IF(A6="","falta o nome",IF(NOT(IF(ISNUMBER(C6),C6&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D6&lt;&gt;"Sim",D6&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F6),F6&gt;0,FALSE)),"faltam as horas faturáveis",C6/F6)))))</f>
+        <f>IF(NOT(OR(A6&lt;&gt;"",B6&lt;&gt;"",C6&lt;&gt;"",D6&lt;&gt;"",E6&lt;&gt;"",F6&lt;&gt;"")),"",IF(A6="","falta o nome",IF(NOT(IF(ISNUMBER(C6),C6&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D6&lt;&gt;"Sim",D6&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F6),F6&gt;0,FALSE)),"faltam as horas faturáveis",IF(AND(ISNUMBER(E6),F6&gt;E6),"faturáveis acima das horas de trabalho",C6/F6))))))</f>
         <v>54.5454545454546</v>
       </c>
       <c r="I6" s="22">
@@ -2503,7 +2503,7 @@
         <v>117.354419773775</v>
       </c>
       <c r="K6" s="40">
-        <f>IF(AND(OR(A6&lt;&gt;"",B6&lt;&gt;"",C6&lt;&gt;"",D6&lt;&gt;"",E6&lt;&gt;"",F6&lt;&gt;""),OR(A6="",NOT(IF(ISNUMBER(C6),C6&gt;=0,FALSE)),NOT(IF(ISNUMBER(F6),F6&gt;0,FALSE)),AND(D6&lt;&gt;"Sim",D6&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(OR(A6&lt;&gt;"",B6&lt;&gt;"",C6&lt;&gt;"",D6&lt;&gt;"",E6&lt;&gt;"",F6&lt;&gt;""),OR(A6="",NOT(IF(ISNUMBER(C6),C6&gt;=0,FALSE)),NOT(IF(ISNUMBER(F6),F6&gt;0,FALSE)),AND(D6&lt;&gt;"Sim",D6&lt;&gt;"Não"),AND(ISNUMBER(E6),ISNUMBER(F6),N(F6)&gt;N(E6)))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2533,11 +2533,11 @@
         <v>60</v>
       </c>
       <c r="G7" s="28">
-        <f>IF(OR(A7="",NOT(IF(ISNUMBER(E7),E7&gt;0,FALSE)),NOT(IF(ISNUMBER(F7),F7&gt;=0,FALSE))),"",F7/E7)</f>
+        <f>IF(OR(A7="",NOT(IF(ISNUMBER(E7),E7&gt;0,FALSE)),NOT(IF(ISNUMBER(F7),F7&gt;=0,FALSE))),"",IF(F7&gt;E7,"faturáveis &gt; trabalho",F7/E7))</f>
         <v>0.5</v>
       </c>
       <c r="H7" s="22">
-        <f>IF(NOT(OR(A7&lt;&gt;"",B7&lt;&gt;"",C7&lt;&gt;"",D7&lt;&gt;"",E7&lt;&gt;"",F7&lt;&gt;"")),"",IF(A7="","falta o nome",IF(NOT(IF(ISNUMBER(C7),C7&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D7&lt;&gt;"Sim",D7&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F7),F7&gt;0,FALSE)),"faltam as horas faturáveis",C7/F7)))))</f>
+        <f>IF(NOT(OR(A7&lt;&gt;"",B7&lt;&gt;"",C7&lt;&gt;"",D7&lt;&gt;"",E7&lt;&gt;"",F7&lt;&gt;"")),"",IF(A7="","falta o nome",IF(NOT(IF(ISNUMBER(C7),C7&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D7&lt;&gt;"Sim",D7&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F7),F7&gt;0,FALSE)),"faltam as horas faturáveis",IF(AND(ISNUMBER(E7),F7&gt;E7),"faturáveis acima das horas de trabalho",C7/F7))))))</f>
         <v>23.3333333333333</v>
       </c>
       <c r="I7" s="22">
@@ -2549,7 +2549,7 @@
         <v>67.0122887864823</v>
       </c>
       <c r="K7" s="40">
-        <f>IF(AND(OR(A7&lt;&gt;"",B7&lt;&gt;"",C7&lt;&gt;"",D7&lt;&gt;"",E7&lt;&gt;"",F7&lt;&gt;""),OR(A7="",NOT(IF(ISNUMBER(C7),C7&gt;=0,FALSE)),NOT(IF(ISNUMBER(F7),F7&gt;0,FALSE)),AND(D7&lt;&gt;"Sim",D7&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(OR(A7&lt;&gt;"",B7&lt;&gt;"",C7&lt;&gt;"",D7&lt;&gt;"",E7&lt;&gt;"",F7&lt;&gt;""),OR(A7="",NOT(IF(ISNUMBER(C7),C7&gt;=0,FALSE)),NOT(IF(ISNUMBER(F7),F7&gt;0,FALSE)),AND(D7&lt;&gt;"Sim",D7&lt;&gt;"Não"),AND(ISNUMBER(E7),ISNUMBER(F7),N(F7)&gt;N(E7)))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2561,11 +2561,11 @@
       <c r="E8" s="39" t="n"/>
       <c r="F8" s="39" t="n"/>
       <c r="G8" s="28">
-        <f>IF(OR(A8="",NOT(IF(ISNUMBER(E8),E8&gt;0,FALSE)),NOT(IF(ISNUMBER(F8),F8&gt;=0,FALSE))),"",F8/E8)</f>
+        <f>IF(OR(A8="",NOT(IF(ISNUMBER(E8),E8&gt;0,FALSE)),NOT(IF(ISNUMBER(F8),F8&gt;=0,FALSE))),"",IF(F8&gt;E8,"faturáveis &gt; trabalho",F8/E8))</f>
         <v/>
       </c>
       <c r="H8" s="22">
-        <f>IF(NOT(OR(A8&lt;&gt;"",B8&lt;&gt;"",C8&lt;&gt;"",D8&lt;&gt;"",E8&lt;&gt;"",F8&lt;&gt;"")),"",IF(A8="","falta o nome",IF(NOT(IF(ISNUMBER(C8),C8&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D8&lt;&gt;"Sim",D8&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F8),F8&gt;0,FALSE)),"faltam as horas faturáveis",C8/F8)))))</f>
+        <f>IF(NOT(OR(A8&lt;&gt;"",B8&lt;&gt;"",C8&lt;&gt;"",D8&lt;&gt;"",E8&lt;&gt;"",F8&lt;&gt;"")),"",IF(A8="","falta o nome",IF(NOT(IF(ISNUMBER(C8),C8&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D8&lt;&gt;"Sim",D8&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F8),F8&gt;0,FALSE)),"faltam as horas faturáveis",IF(AND(ISNUMBER(E8),F8&gt;E8),"faturáveis acima das horas de trabalho",C8/F8))))))</f>
         <v/>
       </c>
       <c r="I8" s="22">
@@ -2577,7 +2577,7 @@
         <v/>
       </c>
       <c r="K8" s="40">
-        <f>IF(AND(OR(A8&lt;&gt;"",B8&lt;&gt;"",C8&lt;&gt;"",D8&lt;&gt;"",E8&lt;&gt;"",F8&lt;&gt;""),OR(A8="",NOT(IF(ISNUMBER(C8),C8&gt;=0,FALSE)),NOT(IF(ISNUMBER(F8),F8&gt;0,FALSE)),AND(D8&lt;&gt;"Sim",D8&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(OR(A8&lt;&gt;"",B8&lt;&gt;"",C8&lt;&gt;"",D8&lt;&gt;"",E8&lt;&gt;"",F8&lt;&gt;""),OR(A8="",NOT(IF(ISNUMBER(C8),C8&gt;=0,FALSE)),NOT(IF(ISNUMBER(F8),F8&gt;0,FALSE)),AND(D8&lt;&gt;"Sim",D8&lt;&gt;"Não"),AND(ISNUMBER(E8),ISNUMBER(F8),N(F8)&gt;N(E8)))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2589,11 +2589,11 @@
       <c r="E9" s="39" t="n"/>
       <c r="F9" s="39" t="n"/>
       <c r="G9" s="28">
-        <f>IF(OR(A9="",NOT(IF(ISNUMBER(E9),E9&gt;0,FALSE)),NOT(IF(ISNUMBER(F9),F9&gt;=0,FALSE))),"",F9/E9)</f>
+        <f>IF(OR(A9="",NOT(IF(ISNUMBER(E9),E9&gt;0,FALSE)),NOT(IF(ISNUMBER(F9),F9&gt;=0,FALSE))),"",IF(F9&gt;E9,"faturáveis &gt; trabalho",F9/E9))</f>
         <v/>
       </c>
       <c r="H9" s="22">
-        <f>IF(NOT(OR(A9&lt;&gt;"",B9&lt;&gt;"",C9&lt;&gt;"",D9&lt;&gt;"",E9&lt;&gt;"",F9&lt;&gt;"")),"",IF(A9="","falta o nome",IF(NOT(IF(ISNUMBER(C9),C9&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D9&lt;&gt;"Sim",D9&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F9),F9&gt;0,FALSE)),"faltam as horas faturáveis",C9/F9)))))</f>
+        <f>IF(NOT(OR(A9&lt;&gt;"",B9&lt;&gt;"",C9&lt;&gt;"",D9&lt;&gt;"",E9&lt;&gt;"",F9&lt;&gt;"")),"",IF(A9="","falta o nome",IF(NOT(IF(ISNUMBER(C9),C9&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D9&lt;&gt;"Sim",D9&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F9),F9&gt;0,FALSE)),"faltam as horas faturáveis",IF(AND(ISNUMBER(E9),F9&gt;E9),"faturáveis acima das horas de trabalho",C9/F9))))))</f>
         <v/>
       </c>
       <c r="I9" s="22">
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="K9" s="40">
-        <f>IF(AND(OR(A9&lt;&gt;"",B9&lt;&gt;"",C9&lt;&gt;"",D9&lt;&gt;"",E9&lt;&gt;"",F9&lt;&gt;""),OR(A9="",NOT(IF(ISNUMBER(C9),C9&gt;=0,FALSE)),NOT(IF(ISNUMBER(F9),F9&gt;0,FALSE)),AND(D9&lt;&gt;"Sim",D9&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(OR(A9&lt;&gt;"",B9&lt;&gt;"",C9&lt;&gt;"",D9&lt;&gt;"",E9&lt;&gt;"",F9&lt;&gt;""),OR(A9="",NOT(IF(ISNUMBER(C9),C9&gt;=0,FALSE)),NOT(IF(ISNUMBER(F9),F9&gt;0,FALSE)),AND(D9&lt;&gt;"Sim",D9&lt;&gt;"Não"),AND(ISNUMBER(E9),ISNUMBER(F9),N(F9)&gt;N(E9)))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2617,11 +2617,11 @@
       <c r="E10" s="39" t="n"/>
       <c r="F10" s="39" t="n"/>
       <c r="G10" s="28">
-        <f>IF(OR(A10="",NOT(IF(ISNUMBER(E10),E10&gt;0,FALSE)),NOT(IF(ISNUMBER(F10),F10&gt;=0,FALSE))),"",F10/E10)</f>
+        <f>IF(OR(A10="",NOT(IF(ISNUMBER(E10),E10&gt;0,FALSE)),NOT(IF(ISNUMBER(F10),F10&gt;=0,FALSE))),"",IF(F10&gt;E10,"faturáveis &gt; trabalho",F10/E10))</f>
         <v/>
       </c>
       <c r="H10" s="22">
-        <f>IF(NOT(OR(A10&lt;&gt;"",B10&lt;&gt;"",C10&lt;&gt;"",D10&lt;&gt;"",E10&lt;&gt;"",F10&lt;&gt;"")),"",IF(A10="","falta o nome",IF(NOT(IF(ISNUMBER(C10),C10&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D10&lt;&gt;"Sim",D10&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F10),F10&gt;0,FALSE)),"faltam as horas faturáveis",C10/F10)))))</f>
+        <f>IF(NOT(OR(A10&lt;&gt;"",B10&lt;&gt;"",C10&lt;&gt;"",D10&lt;&gt;"",E10&lt;&gt;"",F10&lt;&gt;"")),"",IF(A10="","falta o nome",IF(NOT(IF(ISNUMBER(C10),C10&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D10&lt;&gt;"Sim",D10&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F10),F10&gt;0,FALSE)),"faltam as horas faturáveis",IF(AND(ISNUMBER(E10),F10&gt;E10),"faturáveis acima das horas de trabalho",C10/F10))))))</f>
         <v/>
       </c>
       <c r="I10" s="22">
@@ -2633,7 +2633,7 @@
         <v/>
       </c>
       <c r="K10" s="40">
-        <f>IF(AND(OR(A10&lt;&gt;"",B10&lt;&gt;"",C10&lt;&gt;"",D10&lt;&gt;"",E10&lt;&gt;"",F10&lt;&gt;""),OR(A10="",NOT(IF(ISNUMBER(C10),C10&gt;=0,FALSE)),NOT(IF(ISNUMBER(F10),F10&gt;0,FALSE)),AND(D10&lt;&gt;"Sim",D10&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(OR(A10&lt;&gt;"",B10&lt;&gt;"",C10&lt;&gt;"",D10&lt;&gt;"",E10&lt;&gt;"",F10&lt;&gt;""),OR(A10="",NOT(IF(ISNUMBER(C10),C10&gt;=0,FALSE)),NOT(IF(ISNUMBER(F10),F10&gt;0,FALSE)),AND(D10&lt;&gt;"Sim",D10&lt;&gt;"Não"),AND(ISNUMBER(E10),ISNUMBER(F10),N(F10)&gt;N(E10)))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2645,11 +2645,11 @@
       <c r="E11" s="39" t="n"/>
       <c r="F11" s="39" t="n"/>
       <c r="G11" s="28">
-        <f>IF(OR(A11="",NOT(IF(ISNUMBER(E11),E11&gt;0,FALSE)),NOT(IF(ISNUMBER(F11),F11&gt;=0,FALSE))),"",F11/E11)</f>
+        <f>IF(OR(A11="",NOT(IF(ISNUMBER(E11),E11&gt;0,FALSE)),NOT(IF(ISNUMBER(F11),F11&gt;=0,FALSE))),"",IF(F11&gt;E11,"faturáveis &gt; trabalho",F11/E11))</f>
         <v/>
       </c>
       <c r="H11" s="22">
-        <f>IF(NOT(OR(A11&lt;&gt;"",B11&lt;&gt;"",C11&lt;&gt;"",D11&lt;&gt;"",E11&lt;&gt;"",F11&lt;&gt;"")),"",IF(A11="","falta o nome",IF(NOT(IF(ISNUMBER(C11),C11&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D11&lt;&gt;"Sim",D11&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F11),F11&gt;0,FALSE)),"faltam as horas faturáveis",C11/F11)))))</f>
+        <f>IF(NOT(OR(A11&lt;&gt;"",B11&lt;&gt;"",C11&lt;&gt;"",D11&lt;&gt;"",E11&lt;&gt;"",F11&lt;&gt;"")),"",IF(A11="","falta o nome",IF(NOT(IF(ISNUMBER(C11),C11&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D11&lt;&gt;"Sim",D11&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F11),F11&gt;0,FALSE)),"faltam as horas faturáveis",IF(AND(ISNUMBER(E11),F11&gt;E11),"faturáveis acima das horas de trabalho",C11/F11))))))</f>
         <v/>
       </c>
       <c r="I11" s="22">
@@ -2661,7 +2661,7 @@
         <v/>
       </c>
       <c r="K11" s="40">
-        <f>IF(AND(OR(A11&lt;&gt;"",B11&lt;&gt;"",C11&lt;&gt;"",D11&lt;&gt;"",E11&lt;&gt;"",F11&lt;&gt;""),OR(A11="",NOT(IF(ISNUMBER(C11),C11&gt;=0,FALSE)),NOT(IF(ISNUMBER(F11),F11&gt;0,FALSE)),AND(D11&lt;&gt;"Sim",D11&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(OR(A11&lt;&gt;"",B11&lt;&gt;"",C11&lt;&gt;"",D11&lt;&gt;"",E11&lt;&gt;"",F11&lt;&gt;""),OR(A11="",NOT(IF(ISNUMBER(C11),C11&gt;=0,FALSE)),NOT(IF(ISNUMBER(F11),F11&gt;0,FALSE)),AND(D11&lt;&gt;"Sim",D11&lt;&gt;"Não"),AND(ISNUMBER(E11),ISNUMBER(F11),N(F11)&gt;N(E11)))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2673,11 +2673,11 @@
       <c r="E12" s="39" t="n"/>
       <c r="F12" s="39" t="n"/>
       <c r="G12" s="28">
-        <f>IF(OR(A12="",NOT(IF(ISNUMBER(E12),E12&gt;0,FALSE)),NOT(IF(ISNUMBER(F12),F12&gt;=0,FALSE))),"",F12/E12)</f>
+        <f>IF(OR(A12="",NOT(IF(ISNUMBER(E12),E12&gt;0,FALSE)),NOT(IF(ISNUMBER(F12),F12&gt;=0,FALSE))),"",IF(F12&gt;E12,"faturáveis &gt; trabalho",F12/E12))</f>
         <v/>
       </c>
       <c r="H12" s="22">
-        <f>IF(NOT(OR(A12&lt;&gt;"",B12&lt;&gt;"",C12&lt;&gt;"",D12&lt;&gt;"",E12&lt;&gt;"",F12&lt;&gt;"")),"",IF(A12="","falta o nome",IF(NOT(IF(ISNUMBER(C12),C12&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D12&lt;&gt;"Sim",D12&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F12),F12&gt;0,FALSE)),"faltam as horas faturáveis",C12/F12)))))</f>
+        <f>IF(NOT(OR(A12&lt;&gt;"",B12&lt;&gt;"",C12&lt;&gt;"",D12&lt;&gt;"",E12&lt;&gt;"",F12&lt;&gt;"")),"",IF(A12="","falta o nome",IF(NOT(IF(ISNUMBER(C12),C12&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D12&lt;&gt;"Sim",D12&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F12),F12&gt;0,FALSE)),"faltam as horas faturáveis",IF(AND(ISNUMBER(E12),F12&gt;E12),"faturáveis acima das horas de trabalho",C12/F12))))))</f>
         <v/>
       </c>
       <c r="I12" s="22">
@@ -2689,7 +2689,7 @@
         <v/>
       </c>
       <c r="K12" s="40">
-        <f>IF(AND(OR(A12&lt;&gt;"",B12&lt;&gt;"",C12&lt;&gt;"",D12&lt;&gt;"",E12&lt;&gt;"",F12&lt;&gt;""),OR(A12="",NOT(IF(ISNUMBER(C12),C12&gt;=0,FALSE)),NOT(IF(ISNUMBER(F12),F12&gt;0,FALSE)),AND(D12&lt;&gt;"Sim",D12&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(OR(A12&lt;&gt;"",B12&lt;&gt;"",C12&lt;&gt;"",D12&lt;&gt;"",E12&lt;&gt;"",F12&lt;&gt;""),OR(A12="",NOT(IF(ISNUMBER(C12),C12&gt;=0,FALSE)),NOT(IF(ISNUMBER(F12),F12&gt;0,FALSE)),AND(D12&lt;&gt;"Sim",D12&lt;&gt;"Não"),AND(ISNUMBER(E12),ISNUMBER(F12),N(F12)&gt;N(E12)))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2701,11 +2701,11 @@
       <c r="E13" s="39" t="n"/>
       <c r="F13" s="39" t="n"/>
       <c r="G13" s="28">
-        <f>IF(OR(A13="",NOT(IF(ISNUMBER(E13),E13&gt;0,FALSE)),NOT(IF(ISNUMBER(F13),F13&gt;=0,FALSE))),"",F13/E13)</f>
+        <f>IF(OR(A13="",NOT(IF(ISNUMBER(E13),E13&gt;0,FALSE)),NOT(IF(ISNUMBER(F13),F13&gt;=0,FALSE))),"",IF(F13&gt;E13,"faturáveis &gt; trabalho",F13/E13))</f>
         <v/>
       </c>
       <c r="H13" s="22">
-        <f>IF(NOT(OR(A13&lt;&gt;"",B13&lt;&gt;"",C13&lt;&gt;"",D13&lt;&gt;"",E13&lt;&gt;"",F13&lt;&gt;"")),"",IF(A13="","falta o nome",IF(NOT(IF(ISNUMBER(C13),C13&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D13&lt;&gt;"Sim",D13&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F13),F13&gt;0,FALSE)),"faltam as horas faturáveis",C13/F13)))))</f>
+        <f>IF(NOT(OR(A13&lt;&gt;"",B13&lt;&gt;"",C13&lt;&gt;"",D13&lt;&gt;"",E13&lt;&gt;"",F13&lt;&gt;"")),"",IF(A13="","falta o nome",IF(NOT(IF(ISNUMBER(C13),C13&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D13&lt;&gt;"Sim",D13&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F13),F13&gt;0,FALSE)),"faltam as horas faturáveis",IF(AND(ISNUMBER(E13),F13&gt;E13),"faturáveis acima das horas de trabalho",C13/F13))))))</f>
         <v/>
       </c>
       <c r="I13" s="22">
@@ -2717,7 +2717,7 @@
         <v/>
       </c>
       <c r="K13" s="40">
-        <f>IF(AND(OR(A13&lt;&gt;"",B13&lt;&gt;"",C13&lt;&gt;"",D13&lt;&gt;"",E13&lt;&gt;"",F13&lt;&gt;""),OR(A13="",NOT(IF(ISNUMBER(C13),C13&gt;=0,FALSE)),NOT(IF(ISNUMBER(F13),F13&gt;0,FALSE)),AND(D13&lt;&gt;"Sim",D13&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(OR(A13&lt;&gt;"",B13&lt;&gt;"",C13&lt;&gt;"",D13&lt;&gt;"",E13&lt;&gt;"",F13&lt;&gt;""),OR(A13="",NOT(IF(ISNUMBER(C13),C13&gt;=0,FALSE)),NOT(IF(ISNUMBER(F13),F13&gt;0,FALSE)),AND(D13&lt;&gt;"Sim",D13&lt;&gt;"Não"),AND(ISNUMBER(E13),ISNUMBER(F13),N(F13)&gt;N(E13)))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2729,11 +2729,11 @@
       <c r="E14" s="39" t="n"/>
       <c r="F14" s="39" t="n"/>
       <c r="G14" s="28">
-        <f>IF(OR(A14="",NOT(IF(ISNUMBER(E14),E14&gt;0,FALSE)),NOT(IF(ISNUMBER(F14),F14&gt;=0,FALSE))),"",F14/E14)</f>
+        <f>IF(OR(A14="",NOT(IF(ISNUMBER(E14),E14&gt;0,FALSE)),NOT(IF(ISNUMBER(F14),F14&gt;=0,FALSE))),"",IF(F14&gt;E14,"faturáveis &gt; trabalho",F14/E14))</f>
         <v/>
       </c>
       <c r="H14" s="22">
-        <f>IF(NOT(OR(A14&lt;&gt;"",B14&lt;&gt;"",C14&lt;&gt;"",D14&lt;&gt;"",E14&lt;&gt;"",F14&lt;&gt;"")),"",IF(A14="","falta o nome",IF(NOT(IF(ISNUMBER(C14),C14&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D14&lt;&gt;"Sim",D14&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F14),F14&gt;0,FALSE)),"faltam as horas faturáveis",C14/F14)))))</f>
+        <f>IF(NOT(OR(A14&lt;&gt;"",B14&lt;&gt;"",C14&lt;&gt;"",D14&lt;&gt;"",E14&lt;&gt;"",F14&lt;&gt;"")),"",IF(A14="","falta o nome",IF(NOT(IF(ISNUMBER(C14),C14&gt;=0,FALSE)),"falta o pró-labore",IF(AND(D14&lt;&gt;"Sim",D14&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F14),F14&gt;0,FALSE)),"faltam as horas faturáveis",IF(AND(ISNUMBER(E14),F14&gt;E14),"faturáveis acima das horas de trabalho",C14/F14))))))</f>
         <v/>
       </c>
       <c r="I14" s="22">
@@ -2745,7 +2745,7 @@
         <v/>
       </c>
       <c r="K14" s="40">
-        <f>IF(AND(OR(A14&lt;&gt;"",B14&lt;&gt;"",C14&lt;&gt;"",D14&lt;&gt;"",E14&lt;&gt;"",F14&lt;&gt;""),OR(A14="",NOT(IF(ISNUMBER(C14),C14&gt;=0,FALSE)),NOT(IF(ISNUMBER(F14),F14&gt;0,FALSE)),AND(D14&lt;&gt;"Sim",D14&lt;&gt;"Não"))),1,0)</f>
+        <f>IF(AND(OR(A14&lt;&gt;"",B14&lt;&gt;"",C14&lt;&gt;"",D14&lt;&gt;"",E14&lt;&gt;"",F14&lt;&gt;""),OR(A14="",NOT(IF(ISNUMBER(C14),C14&gt;=0,FALSE)),NOT(IF(ISNUMBER(F14),F14&gt;0,FALSE)),AND(D14&lt;&gt;"Sim",D14&lt;&gt;"Não"),AND(ISNUMBER(E14),ISNUMBER(F14),N(F14)&gt;N(E14)))),1,0)</f>
         <v>0</v>
       </c>
     </row>
